--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Home Motors\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCA32568-4E51-44C7-B1B5-6F4E03154505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F7C9D0-814C-49F2-99F6-5C08AE403F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23295" windowHeight="13380" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Home Motors\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F7C9D0-814C-49F2-99F6-5C08AE403F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0777BD09-F621-43ED-9F9C-EDE94C6273F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8937,16 +8937,16 @@
         <v>24</v>
       </c>
       <c r="G309" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H309" s="2">
-        <v>0</v>
+        <v>4.7337962962962967E-3</v>
       </c>
       <c r="I309" s="1">
         <v>46083.77175925926</v>
       </c>
       <c r="J309">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K309" t="s">
         <v>11</v>
@@ -9027,7 +9027,7 @@
         <v>12</v>
       </c>
       <c r="H312" s="2">
-        <v>9.7222222222222219E-4</v>
+        <v>8.8541666666666664E-3</v>
       </c>
       <c r="I312" s="1">
         <v>46083.773148148146</v>
@@ -9098,7 +9098,7 @@
         <v>46083.752430555556</v>
       </c>
       <c r="J315">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K315" t="s">
         <v>11</v>
@@ -9156,7 +9156,7 @@
         <v>46083.753819444442</v>
       </c>
       <c r="J317">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K317" t="s">
         <v>11</v>
@@ -9176,16 +9176,16 @@
         <v>24</v>
       </c>
       <c r="G318" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H318" s="2">
-        <v>0</v>
+        <v>6.4814814814814813E-3</v>
       </c>
       <c r="I318" s="1">
         <v>46083.754513888889</v>
       </c>
       <c r="J318">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K318" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0777BD09-F621-43ED-9F9C-EDE94C6273F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8012C9E-FC66-4DF7-AF1B-BAD1DF7206C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$K$5929</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$K$5445</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -589,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K5929"/>
+  <dimension ref="B1:K5445"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -629,10 +629,10 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -658,10 +658,10 @@
       <c r="I2" s="1">
         <v>45446.708252314813</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       <c r="G240" t="s">
         <v>13</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240">
         <v>0</v>
       </c>
       <c r="I240" s="1">
@@ -7708,7 +7708,7 @@
       <c r="G262" t="s">
         <v>13</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262">
         <v>0</v>
       </c>
       <c r="I262" s="1">
@@ -8872,10 +8872,10 @@
         <v>24</v>
       </c>
       <c r="G306" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H306" s="2">
-        <v>0</v>
+        <v>4.6527777777777774E-3</v>
       </c>
       <c r="I306" s="1">
         <v>46083.770370370374</v>
@@ -8888,10 +8888,32 @@
       </c>
     </row>
     <row r="307" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H307" s="2"/>
-      <c r="I307" s="1"/>
+      <c r="B307" t="s">
+        <v>34</v>
+      </c>
+      <c r="C307">
+        <v>1819</v>
+      </c>
+      <c r="D307" t="s">
+        <v>38</v>
+      </c>
+      <c r="F307" t="s">
+        <v>24</v>
+      </c>
+      <c r="G307" t="s">
+        <v>10</v>
+      </c>
+      <c r="H307" s="2">
+        <v>4.5254629629629629E-3</v>
+      </c>
+      <c r="I307" s="1">
+        <v>46083.771064814813</v>
+      </c>
+      <c r="J307">
+        <v>1</v>
+      </c>
       <c r="K307" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="308" spans="2:11" x14ac:dyDescent="0.25">
@@ -8899,10 +8921,10 @@
         <v>34</v>
       </c>
       <c r="C308">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="D308" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F308" t="s">
         <v>24</v>
@@ -8911,13 +8933,13 @@
         <v>10</v>
       </c>
       <c r="H308" s="2">
-        <v>4.5254629629629629E-3</v>
+        <v>4.7337962962962967E-3</v>
       </c>
       <c r="I308" s="1">
-        <v>46083.771064814813</v>
+        <v>46083.77175925926</v>
       </c>
       <c r="J308">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K308" t="s">
         <v>11</v>
@@ -8928,10 +8950,10 @@
         <v>34</v>
       </c>
       <c r="C309">
-        <v>1815</v>
+        <v>4827</v>
       </c>
       <c r="D309" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F309" t="s">
         <v>24</v>
@@ -8940,13 +8962,13 @@
         <v>10</v>
       </c>
       <c r="H309" s="2">
-        <v>4.7337962962962967E-3</v>
+        <v>4.6990740740740743E-3</v>
       </c>
       <c r="I309" s="1">
-        <v>46083.77175925926</v>
+        <v>46083.772453703707</v>
       </c>
       <c r="J309">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K309" t="s">
         <v>11</v>
@@ -8957,10 +8979,10 @@
         <v>34</v>
       </c>
       <c r="C310">
-        <v>4827</v>
+        <v>1813</v>
       </c>
       <c r="D310" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F310" t="s">
         <v>24</v>
@@ -8969,13 +8991,13 @@
         <v>10</v>
       </c>
       <c r="H310" s="2">
-        <v>4.6990740740740743E-3</v>
+        <v>5.3587962962962964E-3</v>
       </c>
       <c r="I310" s="1">
         <v>46083.772453703707</v>
       </c>
       <c r="J310">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K310" t="s">
         <v>11</v>
@@ -8986,64 +9008,64 @@
         <v>34</v>
       </c>
       <c r="C311">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="D311" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F311" t="s">
         <v>24</v>
       </c>
       <c r="G311" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H311" s="2">
-        <v>5.3587962962962964E-3</v>
+        <v>8.9583333333333338E-3</v>
       </c>
       <c r="I311" s="1">
-        <v>46083.772453703707</v>
+        <v>46083.773148148146</v>
       </c>
       <c r="J311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K311" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="312" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B312" t="s">
+      <c r="H312" s="2"/>
+      <c r="I312" s="1"/>
+      <c r="K312" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B313" t="s">
         <v>34</v>
       </c>
-      <c r="C312">
-        <v>1812</v>
-      </c>
-      <c r="D312" t="s">
-        <v>41</v>
-      </c>
-      <c r="F312" t="s">
+      <c r="C313">
+        <v>4828</v>
+      </c>
+      <c r="D313" t="s">
+        <v>58</v>
+      </c>
+      <c r="F313" t="s">
         <v>24</v>
       </c>
-      <c r="G312" t="s">
-        <v>12</v>
-      </c>
-      <c r="H312" s="2">
-        <v>8.8541666666666664E-3</v>
-      </c>
-      <c r="I312" s="1">
+      <c r="G313" t="s">
+        <v>10</v>
+      </c>
+      <c r="H313" s="2">
+        <v>5.4861111111111109E-3</v>
+      </c>
+      <c r="I313" s="1">
         <v>46083.773148148146</v>
       </c>
-      <c r="J312">
-        <v>1</v>
-      </c>
-      <c r="K312" t="s">
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H313" s="2"/>
-      <c r="I313" s="1"/>
-      <c r="K313" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="314" spans="2:11" x14ac:dyDescent="0.25">
@@ -9051,57 +9073,35 @@
         <v>34</v>
       </c>
       <c r="C314">
-        <v>4828</v>
+        <v>3125</v>
       </c>
       <c r="D314" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F314" t="s">
         <v>24</v>
       </c>
       <c r="G314" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H314" s="2">
-        <v>5.4861111111111109E-3</v>
+        <v>0</v>
       </c>
       <c r="I314" s="1">
-        <v>46083.773148148146</v>
+        <v>46083.752430555556</v>
       </c>
       <c r="J314">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K314" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="315" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B315" t="s">
-        <v>34</v>
-      </c>
-      <c r="C315">
-        <v>3125</v>
-      </c>
-      <c r="D315" t="s">
-        <v>53</v>
-      </c>
-      <c r="F315" t="s">
-        <v>24</v>
-      </c>
-      <c r="G315" t="s">
-        <v>13</v>
-      </c>
-      <c r="H315" s="2">
-        <v>0</v>
-      </c>
-      <c r="I315" s="1">
-        <v>46083.752430555556</v>
-      </c>
-      <c r="J315">
-        <v>3</v>
-      </c>
+      <c r="H315" s="2"/>
+      <c r="I315" s="1"/>
       <c r="K315" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="316" spans="2:11" x14ac:dyDescent="0.25">
@@ -9468,7 +9468,6 @@
       <c r="I387" s="1"/>
     </row>
     <row r="388" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H388" s="2"/>
       <c r="I388" s="1"/>
     </row>
     <row r="389" spans="8:9" x14ac:dyDescent="0.25">
@@ -9496,7 +9495,6 @@
       <c r="I394" s="1"/>
     </row>
     <row r="395" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H395" s="2"/>
       <c r="I395" s="1"/>
     </row>
     <row r="396" spans="8:9" x14ac:dyDescent="0.25">
@@ -9608,7 +9606,6 @@
       <c r="I422" s="1"/>
     </row>
     <row r="423" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H423" s="2"/>
       <c r="I423" s="1"/>
     </row>
     <row r="424" spans="8:9" x14ac:dyDescent="0.25">
@@ -9712,7 +9709,6 @@
       <c r="I448" s="1"/>
     </row>
     <row r="449" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H449" s="2"/>
       <c r="I449" s="1"/>
     </row>
     <row r="450" spans="8:9" x14ac:dyDescent="0.25">
@@ -9728,7 +9724,6 @@
       <c r="I452" s="1"/>
     </row>
     <row r="453" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H453" s="2"/>
       <c r="I453" s="1"/>
     </row>
     <row r="454" spans="8:9" x14ac:dyDescent="0.25">
@@ -9876,7 +9871,6 @@
       <c r="I489" s="1"/>
     </row>
     <row r="490" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H490" s="2"/>
       <c r="I490" s="1"/>
     </row>
     <row r="491" spans="8:9" x14ac:dyDescent="0.25">
@@ -10040,7 +10034,6 @@
       <c r="I530" s="1"/>
     </row>
     <row r="531" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H531" s="2"/>
       <c r="I531" s="1"/>
     </row>
     <row r="532" spans="8:9" x14ac:dyDescent="0.25">
@@ -10100,7 +10093,6 @@
       <c r="I545" s="1"/>
     </row>
     <row r="546" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H546" s="2"/>
       <c r="I546" s="1"/>
     </row>
     <row r="547" spans="8:9" x14ac:dyDescent="0.25">
@@ -10372,6 +10364,7 @@
       <c r="I613" s="1"/>
     </row>
     <row r="614" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H614" s="2"/>
       <c r="I614" s="1"/>
     </row>
     <row r="615" spans="8:9" x14ac:dyDescent="0.25">
@@ -10391,7 +10384,6 @@
       <c r="I618" s="1"/>
     </row>
     <row r="619" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H619" s="2"/>
       <c r="I619" s="1"/>
     </row>
     <row r="620" spans="8:9" x14ac:dyDescent="0.25">
@@ -10775,7 +10767,6 @@
       <c r="I714" s="1"/>
     </row>
     <row r="715" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H715" s="2"/>
       <c r="I715" s="1"/>
     </row>
     <row r="716" spans="8:9" x14ac:dyDescent="0.25">
@@ -10811,6 +10802,7 @@
       <c r="I723" s="1"/>
     </row>
     <row r="724" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H724" s="2"/>
       <c r="I724" s="1"/>
     </row>
     <row r="725" spans="8:9" x14ac:dyDescent="0.25">
@@ -10898,6 +10890,7 @@
       <c r="I745" s="1"/>
     </row>
     <row r="746" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H746" s="2"/>
       <c r="I746" s="1"/>
     </row>
     <row r="747" spans="8:9" x14ac:dyDescent="0.25">
@@ -10969,7 +10962,6 @@
       <c r="I763" s="1"/>
     </row>
     <row r="764" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H764" s="2"/>
       <c r="I764" s="1"/>
     </row>
     <row r="765" spans="8:9" x14ac:dyDescent="0.25">
@@ -11009,7 +11001,6 @@
       <c r="I773" s="1"/>
     </row>
     <row r="774" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H774" s="2"/>
       <c r="I774" s="1"/>
     </row>
     <row r="775" spans="8:9" x14ac:dyDescent="0.25">
@@ -11021,7 +11012,6 @@
       <c r="I776" s="1"/>
     </row>
     <row r="777" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H777" s="2"/>
       <c r="I777" s="1"/>
     </row>
     <row r="778" spans="8:9" x14ac:dyDescent="0.25">
@@ -11041,6 +11031,7 @@
       <c r="I781" s="1"/>
     </row>
     <row r="782" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H782" s="2"/>
       <c r="I782" s="1"/>
     </row>
     <row r="783" spans="8:9" x14ac:dyDescent="0.25">
@@ -11072,7 +11063,6 @@
       <c r="I789" s="1"/>
     </row>
     <row r="790" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H790" s="2"/>
       <c r="I790" s="1"/>
     </row>
     <row r="791" spans="8:9" x14ac:dyDescent="0.25">
@@ -11104,6 +11094,7 @@
       <c r="I797" s="1"/>
     </row>
     <row r="798" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H798" s="2"/>
       <c r="I798" s="1"/>
     </row>
     <row r="799" spans="8:9" x14ac:dyDescent="0.25">
@@ -11175,7 +11166,6 @@
       <c r="I815" s="1"/>
     </row>
     <row r="816" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H816" s="2"/>
       <c r="I816" s="1"/>
     </row>
     <row r="817" spans="8:9" x14ac:dyDescent="0.25">
@@ -11275,7 +11265,6 @@
       <c r="I840" s="1"/>
     </row>
     <row r="841" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H841" s="2"/>
       <c r="I841" s="1"/>
     </row>
     <row r="842" spans="8:9" x14ac:dyDescent="0.25">
@@ -11355,7 +11344,6 @@
       <c r="I860" s="1"/>
     </row>
     <row r="861" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H861" s="2"/>
       <c r="I861" s="1"/>
     </row>
     <row r="862" spans="8:9" x14ac:dyDescent="0.25">
@@ -11387,7 +11375,6 @@
       <c r="I868" s="1"/>
     </row>
     <row r="869" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H869" s="2"/>
       <c r="I869" s="1"/>
     </row>
     <row r="870" spans="8:9" x14ac:dyDescent="0.25">
@@ -11399,6 +11386,7 @@
       <c r="I871" s="1"/>
     </row>
     <row r="872" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H872" s="2"/>
       <c r="I872" s="1"/>
     </row>
     <row r="873" spans="8:9" x14ac:dyDescent="0.25">
@@ -11410,7 +11398,6 @@
       <c r="I874" s="1"/>
     </row>
     <row r="875" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H875" s="2"/>
       <c r="I875" s="1"/>
     </row>
     <row r="876" spans="8:9" x14ac:dyDescent="0.25">
@@ -11426,6 +11413,7 @@
       <c r="I878" s="1"/>
     </row>
     <row r="879" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H879" s="2"/>
       <c r="I879" s="1"/>
     </row>
     <row r="880" spans="8:9" x14ac:dyDescent="0.25">
@@ -11469,7 +11457,6 @@
       <c r="I889" s="1"/>
     </row>
     <row r="890" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H890" s="2"/>
       <c r="I890" s="1"/>
     </row>
     <row r="891" spans="8:9" x14ac:dyDescent="0.25">
@@ -11481,7 +11468,6 @@
       <c r="I892" s="1"/>
     </row>
     <row r="893" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H893" s="2"/>
       <c r="I893" s="1"/>
     </row>
     <row r="894" spans="8:9" x14ac:dyDescent="0.25">
@@ -11509,7 +11495,6 @@
       <c r="I899" s="1"/>
     </row>
     <row r="900" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H900" s="2"/>
       <c r="I900" s="1"/>
     </row>
     <row r="901" spans="8:9" x14ac:dyDescent="0.25">
@@ -11525,7 +11510,6 @@
       <c r="I903" s="1"/>
     </row>
     <row r="904" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H904" s="2"/>
       <c r="I904" s="1"/>
     </row>
     <row r="905" spans="8:9" x14ac:dyDescent="0.25">
@@ -11537,6 +11521,7 @@
       <c r="I906" s="1"/>
     </row>
     <row r="907" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H907" s="2"/>
       <c r="I907" s="1"/>
     </row>
     <row r="908" spans="8:9" x14ac:dyDescent="0.25">
@@ -11544,7 +11529,6 @@
       <c r="I908" s="1"/>
     </row>
     <row r="909" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H909" s="2"/>
       <c r="I909" s="1"/>
     </row>
     <row r="910" spans="8:9" x14ac:dyDescent="0.25">
@@ -11564,7 +11548,6 @@
       <c r="I913" s="1"/>
     </row>
     <row r="914" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H914" s="2"/>
       <c r="I914" s="1"/>
     </row>
     <row r="915" spans="8:9" x14ac:dyDescent="0.25">
@@ -11628,7 +11611,6 @@
       <c r="I929" s="1"/>
     </row>
     <row r="930" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H930" s="2"/>
       <c r="I930" s="1"/>
     </row>
     <row r="931" spans="8:9" x14ac:dyDescent="0.25">
@@ -11640,6 +11622,7 @@
       <c r="I932" s="1"/>
     </row>
     <row r="933" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H933" s="2"/>
       <c r="I933" s="1"/>
     </row>
     <row r="934" spans="8:9" x14ac:dyDescent="0.25">
@@ -11655,6 +11638,7 @@
       <c r="I936" s="1"/>
     </row>
     <row r="937" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H937" s="2"/>
       <c r="I937" s="1"/>
     </row>
     <row r="938" spans="8:9" x14ac:dyDescent="0.25">
@@ -11698,7 +11682,6 @@
       <c r="I947" s="1"/>
     </row>
     <row r="948" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H948" s="2"/>
       <c r="I948" s="1"/>
     </row>
     <row r="949" spans="8:9" x14ac:dyDescent="0.25">
@@ -11746,7 +11729,6 @@
       <c r="I959" s="1"/>
     </row>
     <row r="960" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H960" s="2"/>
       <c r="I960" s="1"/>
     </row>
     <row r="961" spans="8:9" x14ac:dyDescent="0.25">
@@ -11802,6 +11784,7 @@
       <c r="I973" s="1"/>
     </row>
     <row r="974" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H974" s="2"/>
       <c r="I974" s="1"/>
     </row>
     <row r="975" spans="8:9" x14ac:dyDescent="0.25">
@@ -11877,11 +11860,9 @@
       <c r="I992" s="1"/>
     </row>
     <row r="993" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H993" s="2"/>
       <c r="I993" s="1"/>
     </row>
     <row r="994" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H994" s="2"/>
       <c r="I994" s="1"/>
     </row>
     <row r="995" spans="8:9" x14ac:dyDescent="0.25">
@@ -11941,7 +11922,6 @@
       <c r="I1008" s="1"/>
     </row>
     <row r="1009" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1009" s="2"/>
       <c r="I1009" s="1"/>
     </row>
     <row r="1010" spans="8:9" x14ac:dyDescent="0.25">
@@ -11965,6 +11945,7 @@
       <c r="I1014" s="1"/>
     </row>
     <row r="1015" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1015" s="2"/>
       <c r="I1015" s="1"/>
     </row>
     <row r="1016" spans="8:9" x14ac:dyDescent="0.25">
@@ -12024,6 +12005,7 @@
       <c r="I1029" s="1"/>
     </row>
     <row r="1030" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1030" s="2"/>
       <c r="I1030" s="1"/>
     </row>
     <row r="1031" spans="8:9" x14ac:dyDescent="0.25">
@@ -12131,7 +12113,6 @@
       <c r="I1056" s="1"/>
     </row>
     <row r="1057" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1057" s="2"/>
       <c r="I1057" s="1"/>
     </row>
     <row r="1058" spans="8:9" x14ac:dyDescent="0.25">
@@ -12175,7 +12156,6 @@
       <c r="I1067" s="1"/>
     </row>
     <row r="1068" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1068" s="2"/>
       <c r="I1068" s="1"/>
     </row>
     <row r="1069" spans="8:9" x14ac:dyDescent="0.25">
@@ -12207,7 +12187,6 @@
       <c r="I1075" s="1"/>
     </row>
     <row r="1076" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1076" s="2"/>
       <c r="I1076" s="1"/>
     </row>
     <row r="1077" spans="8:9" x14ac:dyDescent="0.25">
@@ -12243,7 +12222,6 @@
       <c r="I1084" s="1"/>
     </row>
     <row r="1085" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1085" s="2"/>
       <c r="I1085" s="1"/>
     </row>
     <row r="1086" spans="8:9" x14ac:dyDescent="0.25">
@@ -12267,7 +12245,6 @@
       <c r="I1090" s="1"/>
     </row>
     <row r="1091" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1091" s="2"/>
       <c r="I1091" s="1"/>
     </row>
     <row r="1092" spans="8:9" x14ac:dyDescent="0.25">
@@ -12315,6 +12292,7 @@
       <c r="I1102" s="1"/>
     </row>
     <row r="1103" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1103" s="2"/>
       <c r="I1103" s="1"/>
     </row>
     <row r="1104" spans="8:9" x14ac:dyDescent="0.25">
@@ -12346,11 +12324,9 @@
       <c r="I1110" s="1"/>
     </row>
     <row r="1111" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1111" s="2"/>
       <c r="I1111" s="1"/>
     </row>
     <row r="1112" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1112" s="2"/>
       <c r="I1112" s="1"/>
     </row>
     <row r="1113" spans="8:9" x14ac:dyDescent="0.25">
@@ -12374,7 +12350,6 @@
       <c r="I1117" s="1"/>
     </row>
     <row r="1118" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
     </row>
     <row r="1119" spans="8:9" x14ac:dyDescent="0.25">
@@ -12386,7 +12361,6 @@
       <c r="I1120" s="1"/>
     </row>
     <row r="1121" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1121" s="2"/>
       <c r="I1121" s="1"/>
     </row>
     <row r="1122" spans="8:9" x14ac:dyDescent="0.25">
@@ -12402,7 +12376,6 @@
       <c r="I1124" s="1"/>
     </row>
     <row r="1125" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1125" s="2"/>
       <c r="I1125" s="1"/>
     </row>
     <row r="1126" spans="8:9" x14ac:dyDescent="0.25">
@@ -12414,7 +12387,6 @@
       <c r="I1127" s="1"/>
     </row>
     <row r="1128" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1128" s="2"/>
       <c r="I1128" s="1"/>
     </row>
     <row r="1129" spans="8:9" x14ac:dyDescent="0.25">
@@ -12434,7 +12406,6 @@
       <c r="I1132" s="1"/>
     </row>
     <row r="1133" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1133" s="2"/>
       <c r="I1133" s="1"/>
     </row>
     <row r="1134" spans="8:9" x14ac:dyDescent="0.25">
@@ -12442,7 +12413,6 @@
       <c r="I1134" s="1"/>
     </row>
     <row r="1135" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1135" s="2"/>
       <c r="I1135" s="1"/>
     </row>
     <row r="1136" spans="8:9" x14ac:dyDescent="0.25">
@@ -12470,7 +12440,6 @@
       <c r="I1141" s="1"/>
     </row>
     <row r="1142" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1142" s="2"/>
       <c r="I1142" s="1"/>
     </row>
     <row r="1143" spans="8:9" x14ac:dyDescent="0.25">
@@ -12478,7 +12447,6 @@
       <c r="I1143" s="1"/>
     </row>
     <row r="1144" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
     </row>
     <row r="1145" spans="8:9" x14ac:dyDescent="0.25">
@@ -12486,7 +12454,6 @@
       <c r="I1145" s="1"/>
     </row>
     <row r="1146" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1146" s="2"/>
       <c r="I1146" s="1"/>
     </row>
     <row r="1147" spans="8:9" x14ac:dyDescent="0.25">
@@ -12506,7 +12473,6 @@
       <c r="I1150" s="1"/>
     </row>
     <row r="1151" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
     </row>
     <row r="1152" spans="8:9" x14ac:dyDescent="0.25">
@@ -12518,11 +12484,9 @@
       <c r="I1153" s="1"/>
     </row>
     <row r="1154" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
     </row>
     <row r="1155" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1155" s="2"/>
       <c r="I1155" s="1"/>
     </row>
     <row r="1156" spans="8:9" x14ac:dyDescent="0.25">
@@ -12582,7 +12546,6 @@
       <c r="I1169" s="1"/>
     </row>
     <row r="1170" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
     </row>
     <row r="1171" spans="8:9" x14ac:dyDescent="0.25">
@@ -12598,7 +12561,6 @@
       <c r="I1173" s="1"/>
     </row>
     <row r="1174" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1174" s="2"/>
       <c r="I1174" s="1"/>
     </row>
     <row r="1175" spans="8:9" x14ac:dyDescent="0.25">
@@ -12698,6 +12660,7 @@
       <c r="I1198" s="1"/>
     </row>
     <row r="1199" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1199" s="2"/>
       <c r="I1199" s="1"/>
     </row>
     <row r="1200" spans="8:9" x14ac:dyDescent="0.25">
@@ -12893,6 +12856,7 @@
       <c r="I1247" s="1"/>
     </row>
     <row r="1248" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1248" s="2"/>
       <c r="I1248" s="1"/>
     </row>
     <row r="1249" spans="8:9" x14ac:dyDescent="0.25">
@@ -12932,6 +12896,7 @@
       <c r="I1257" s="1"/>
     </row>
     <row r="1258" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1258" s="2"/>
       <c r="I1258" s="1"/>
     </row>
     <row r="1259" spans="8:9" x14ac:dyDescent="0.25">
@@ -12943,6 +12908,7 @@
       <c r="I1260" s="1"/>
     </row>
     <row r="1261" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1261" s="2"/>
       <c r="I1261" s="1"/>
     </row>
     <row r="1262" spans="8:9" x14ac:dyDescent="0.25">
@@ -12994,6 +12960,7 @@
       <c r="I1273" s="1"/>
     </row>
     <row r="1274" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1274" s="2"/>
       <c r="I1274" s="1"/>
     </row>
     <row r="1275" spans="8:9" x14ac:dyDescent="0.25">
@@ -13097,6 +13064,7 @@
       <c r="I1299" s="1"/>
     </row>
     <row r="1300" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1300" s="2"/>
       <c r="I1300" s="1"/>
     </row>
     <row r="1301" spans="8:9" x14ac:dyDescent="0.25">
@@ -13196,14 +13164,13 @@
       <c r="I1324" s="1"/>
     </row>
     <row r="1325" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1325" s="2"/>
       <c r="I1325" s="1"/>
     </row>
     <row r="1326" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1326" s="2"/>
       <c r="I1326" s="1"/>
     </row>
     <row r="1327" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1327" s="2"/>
       <c r="I1327" s="1"/>
     </row>
     <row r="1328" spans="8:9" x14ac:dyDescent="0.25">
@@ -13211,15 +13178,12 @@
       <c r="I1328" s="1"/>
     </row>
     <row r="1329" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1329" s="2"/>
       <c r="I1329" s="1"/>
     </row>
     <row r="1330" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1330" s="2"/>
       <c r="I1330" s="1"/>
     </row>
     <row r="1331" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1331" s="2"/>
       <c r="I1331" s="1"/>
     </row>
     <row r="1332" spans="8:9" x14ac:dyDescent="0.25">
@@ -13231,11 +13195,9 @@
       <c r="I1333" s="1"/>
     </row>
     <row r="1334" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1334" s="2"/>
       <c r="I1334" s="1"/>
     </row>
     <row r="1335" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1335" s="2"/>
       <c r="I1335" s="1"/>
     </row>
     <row r="1336" spans="8:9" x14ac:dyDescent="0.25">
@@ -13243,7 +13205,6 @@
       <c r="I1336" s="1"/>
     </row>
     <row r="1337" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1337" s="2"/>
       <c r="I1337" s="1"/>
     </row>
     <row r="1338" spans="8:9" x14ac:dyDescent="0.25">
@@ -13259,15 +13220,12 @@
       <c r="I1340" s="1"/>
     </row>
     <row r="1341" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1341" s="2"/>
       <c r="I1341" s="1"/>
     </row>
     <row r="1342" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1342" s="2"/>
       <c r="I1342" s="1"/>
     </row>
     <row r="1343" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1343" s="2"/>
       <c r="I1343" s="1"/>
     </row>
     <row r="1344" spans="8:9" x14ac:dyDescent="0.25">
@@ -13278,23 +13236,18 @@
       <c r="I1345" s="1"/>
     </row>
     <row r="1346" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1346" s="2"/>
       <c r="I1346" s="1"/>
     </row>
     <row r="1347" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1347" s="2"/>
       <c r="I1347" s="1"/>
     </row>
     <row r="1348" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1348" s="2"/>
       <c r="I1348" s="1"/>
     </row>
     <row r="1349" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1349" s="2"/>
       <c r="I1349" s="1"/>
     </row>
     <row r="1350" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1350" s="2"/>
       <c r="I1350" s="1"/>
     </row>
     <row r="1351" spans="8:9" x14ac:dyDescent="0.25">
@@ -13309,7 +13262,6 @@
       <c r="I1353" s="1"/>
     </row>
     <row r="1354" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1354" s="2"/>
       <c r="I1354" s="1"/>
     </row>
     <row r="1355" spans="8:9" x14ac:dyDescent="0.25">
@@ -13317,7 +13269,6 @@
       <c r="I1355" s="1"/>
     </row>
     <row r="1356" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1356" s="2"/>
       <c r="I1356" s="1"/>
     </row>
     <row r="1357" spans="8:9" x14ac:dyDescent="0.25">
@@ -13336,7 +13287,6 @@
       <c r="I1360" s="1"/>
     </row>
     <row r="1361" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1361" s="2"/>
       <c r="I1361" s="1"/>
     </row>
     <row r="1362" spans="8:9" x14ac:dyDescent="0.25">
@@ -13356,11 +13306,9 @@
       <c r="I1365" s="1"/>
     </row>
     <row r="1366" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1366" s="2"/>
       <c r="I1366" s="1"/>
     </row>
     <row r="1367" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
     </row>
     <row r="1368" spans="8:9" x14ac:dyDescent="0.25">
@@ -13376,11 +13324,9 @@
       <c r="I1370" s="1"/>
     </row>
     <row r="1371" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1371" s="2"/>
       <c r="I1371" s="1"/>
     </row>
     <row r="1372" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1372" s="2"/>
       <c r="I1372" s="1"/>
     </row>
     <row r="1373" spans="8:9" x14ac:dyDescent="0.25">
@@ -13395,14 +13341,12 @@
       <c r="I1375" s="1"/>
     </row>
     <row r="1376" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1376" s="2"/>
       <c r="I1376" s="1"/>
     </row>
     <row r="1377" spans="8:9" x14ac:dyDescent="0.25">
       <c r="I1377" s="1"/>
     </row>
     <row r="1378" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1378" s="2"/>
       <c r="I1378" s="1"/>
     </row>
     <row r="1379" spans="8:9" x14ac:dyDescent="0.25">
@@ -13414,7 +13358,6 @@
       <c r="I1380" s="1"/>
     </row>
     <row r="1381" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1381" s="2"/>
       <c r="I1381" s="1"/>
     </row>
     <row r="1382" spans="8:9" x14ac:dyDescent="0.25">
@@ -13426,6 +13369,7 @@
       <c r="I1383" s="1"/>
     </row>
     <row r="1384" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1384" s="2"/>
       <c r="I1384" s="1"/>
     </row>
     <row r="1385" spans="8:9" x14ac:dyDescent="0.25">
@@ -13433,18 +13377,16 @@
       <c r="I1385" s="1"/>
     </row>
     <row r="1386" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1386" s="2"/>
       <c r="I1386" s="1"/>
     </row>
     <row r="1387" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1387" s="2"/>
       <c r="I1387" s="1"/>
     </row>
     <row r="1388" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1388" s="2"/>
       <c r="I1388" s="1"/>
     </row>
     <row r="1389" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1389" s="2"/>
       <c r="I1389" s="1"/>
     </row>
     <row r="1390" spans="8:9" x14ac:dyDescent="0.25">
@@ -13452,7 +13394,6 @@
       <c r="I1390" s="1"/>
     </row>
     <row r="1391" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1391" s="2"/>
       <c r="I1391" s="1"/>
     </row>
     <row r="1392" spans="8:9" x14ac:dyDescent="0.25">
@@ -13460,18 +13401,16 @@
       <c r="I1392" s="1"/>
     </row>
     <row r="1393" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1393" s="2"/>
       <c r="I1393" s="1"/>
     </row>
     <row r="1394" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1394" s="2"/>
       <c r="I1394" s="1"/>
     </row>
     <row r="1395" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1395" s="2"/>
       <c r="I1395" s="1"/>
     </row>
     <row r="1396" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1396" s="2"/>
       <c r="I1396" s="1"/>
     </row>
     <row r="1397" spans="8:9" x14ac:dyDescent="0.25">
@@ -13479,10 +13418,10 @@
       <c r="I1397" s="1"/>
     </row>
     <row r="1398" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1398" s="2"/>
       <c r="I1398" s="1"/>
     </row>
     <row r="1399" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1399" s="2"/>
       <c r="I1399" s="1"/>
     </row>
     <row r="1400" spans="8:9" x14ac:dyDescent="0.25">
@@ -13490,11 +13429,9 @@
       <c r="I1400" s="1"/>
     </row>
     <row r="1401" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1401" s="2"/>
       <c r="I1401" s="1"/>
     </row>
     <row r="1402" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1402" s="2"/>
       <c r="I1402" s="1"/>
     </row>
     <row r="1403" spans="8:9" x14ac:dyDescent="0.25">
@@ -13506,15 +13443,12 @@
       <c r="I1404" s="1"/>
     </row>
     <row r="1405" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1405" s="2"/>
       <c r="I1405" s="1"/>
     </row>
     <row r="1406" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1406" s="2"/>
       <c r="I1406" s="1"/>
     </row>
     <row r="1407" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1407" s="2"/>
       <c r="I1407" s="1"/>
     </row>
     <row r="1408" spans="8:9" x14ac:dyDescent="0.25">
@@ -13526,11 +13460,9 @@
       <c r="I1409" s="1"/>
     </row>
     <row r="1410" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1410" s="2"/>
       <c r="I1410" s="1"/>
     </row>
     <row r="1411" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1411" s="2"/>
       <c r="I1411" s="1"/>
     </row>
     <row r="1412" spans="8:9" x14ac:dyDescent="0.25">
@@ -13542,6 +13474,7 @@
       <c r="I1413" s="1"/>
     </row>
     <row r="1414" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1414" s="2"/>
       <c r="I1414" s="1"/>
     </row>
     <row r="1415" spans="8:9" x14ac:dyDescent="0.25">
@@ -13553,7 +13486,6 @@
       <c r="I1416" s="1"/>
     </row>
     <row r="1417" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1417" s="2"/>
       <c r="I1417" s="1"/>
     </row>
     <row r="1418" spans="8:9" x14ac:dyDescent="0.25">
@@ -13565,7 +13497,6 @@
       <c r="I1419" s="1"/>
     </row>
     <row r="1420" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1420" s="2"/>
       <c r="I1420" s="1"/>
     </row>
     <row r="1421" spans="8:9" x14ac:dyDescent="0.25">
@@ -13581,7 +13512,6 @@
       <c r="I1423" s="1"/>
     </row>
     <row r="1424" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1424" s="2"/>
       <c r="I1424" s="1"/>
     </row>
     <row r="1425" spans="8:9" x14ac:dyDescent="0.25">
@@ -13613,6 +13543,7 @@
       <c r="I1431" s="1"/>
     </row>
     <row r="1432" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1432" s="2"/>
       <c r="I1432" s="1"/>
     </row>
     <row r="1433" spans="8:9" x14ac:dyDescent="0.25">
@@ -13660,6 +13591,7 @@
       <c r="I1443" s="1"/>
     </row>
     <row r="1444" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1444" s="2"/>
       <c r="I1444" s="1"/>
     </row>
     <row r="1445" spans="8:9" x14ac:dyDescent="0.25">
@@ -13667,7 +13599,6 @@
       <c r="I1445" s="1"/>
     </row>
     <row r="1446" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1446" s="2"/>
       <c r="I1446" s="1"/>
     </row>
     <row r="1447" spans="8:9" x14ac:dyDescent="0.25">
@@ -13675,7 +13606,6 @@
       <c r="I1447" s="1"/>
     </row>
     <row r="1448" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1448" s="2"/>
       <c r="I1448" s="1"/>
     </row>
     <row r="1449" spans="8:9" x14ac:dyDescent="0.25">
@@ -13683,11 +13613,9 @@
       <c r="I1449" s="1"/>
     </row>
     <row r="1450" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1450" s="2"/>
       <c r="I1450" s="1"/>
     </row>
     <row r="1451" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1451" s="2"/>
       <c r="I1451" s="1"/>
     </row>
     <row r="1452" spans="8:9" x14ac:dyDescent="0.25">
@@ -13699,7 +13627,6 @@
       <c r="I1453" s="1"/>
     </row>
     <row r="1454" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1454" s="2"/>
       <c r="I1454" s="1"/>
     </row>
     <row r="1455" spans="8:9" x14ac:dyDescent="0.25">
@@ -13707,11 +13634,9 @@
       <c r="I1455" s="1"/>
     </row>
     <row r="1456" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1456" s="2"/>
       <c r="I1456" s="1"/>
     </row>
     <row r="1457" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1457" s="2"/>
       <c r="I1457" s="1"/>
     </row>
     <row r="1458" spans="8:9" x14ac:dyDescent="0.25">
@@ -13723,19 +13648,15 @@
       <c r="I1459" s="1"/>
     </row>
     <row r="1460" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1460" s="2"/>
       <c r="I1460" s="1"/>
     </row>
     <row r="1461" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1461" s="2"/>
       <c r="I1461" s="1"/>
     </row>
     <row r="1462" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1462" s="2"/>
       <c r="I1462" s="1"/>
     </row>
     <row r="1463" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1463" s="2"/>
       <c r="I1463" s="1"/>
     </row>
     <row r="1464" spans="8:9" x14ac:dyDescent="0.25">
@@ -13743,7 +13664,6 @@
       <c r="I1464" s="1"/>
     </row>
     <row r="1465" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1465" s="2"/>
       <c r="I1465" s="1"/>
     </row>
     <row r="1466" spans="8:9" x14ac:dyDescent="0.25">
@@ -13759,7 +13679,6 @@
       <c r="I1468" s="1"/>
     </row>
     <row r="1469" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
     </row>
     <row r="1470" spans="8:9" x14ac:dyDescent="0.25">
@@ -13767,7 +13686,6 @@
       <c r="I1470" s="1"/>
     </row>
     <row r="1471" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1471" s="2"/>
       <c r="I1471" s="1"/>
     </row>
     <row r="1472" spans="8:9" x14ac:dyDescent="0.25">
@@ -13775,15 +13693,12 @@
       <c r="I1472" s="1"/>
     </row>
     <row r="1473" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1473" s="2"/>
       <c r="I1473" s="1"/>
     </row>
     <row r="1474" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1474" s="2"/>
       <c r="I1474" s="1"/>
     </row>
     <row r="1475" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1475" s="2"/>
       <c r="I1475" s="1"/>
     </row>
     <row r="1476" spans="8:9" x14ac:dyDescent="0.25">
@@ -13791,9 +13706,11 @@
       <c r="I1476" s="1"/>
     </row>
     <row r="1477" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1477" s="2"/>
       <c r="I1477" s="1"/>
     </row>
     <row r="1478" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1478" s="2"/>
       <c r="I1478" s="1"/>
     </row>
     <row r="1479" spans="8:9" x14ac:dyDescent="0.25">
@@ -13805,15 +13722,12 @@
       <c r="I1480" s="1"/>
     </row>
     <row r="1481" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1481" s="2"/>
       <c r="I1481" s="1"/>
     </row>
     <row r="1482" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1482" s="2"/>
       <c r="I1482" s="1"/>
     </row>
     <row r="1483" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1483" s="2"/>
       <c r="I1483" s="1"/>
     </row>
     <row r="1484" spans="8:9" x14ac:dyDescent="0.25">
@@ -13825,11 +13739,9 @@
       <c r="I1485" s="1"/>
     </row>
     <row r="1486" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1486" s="2"/>
       <c r="I1486" s="1"/>
     </row>
     <row r="1487" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1487" s="2"/>
       <c r="I1487" s="1"/>
     </row>
     <row r="1488" spans="8:9" x14ac:dyDescent="0.25">
@@ -13849,7 +13761,6 @@
       <c r="I1491" s="1"/>
     </row>
     <row r="1492" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1492" s="2"/>
       <c r="I1492" s="1"/>
     </row>
     <row r="1493" spans="8:9" x14ac:dyDescent="0.25">
@@ -13864,7 +13775,6 @@
       <c r="I1495" s="1"/>
     </row>
     <row r="1496" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1496" s="2"/>
       <c r="I1496" s="1"/>
     </row>
     <row r="1497" spans="8:9" x14ac:dyDescent="0.25">
@@ -13876,19 +13786,15 @@
       <c r="I1498" s="1"/>
     </row>
     <row r="1499" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1499" s="2"/>
       <c r="I1499" s="1"/>
     </row>
     <row r="1500" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1500" s="2"/>
       <c r="I1500" s="1"/>
     </row>
     <row r="1501" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
     </row>
     <row r="1502" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
     </row>
     <row r="1503" spans="8:9" x14ac:dyDescent="0.25">
@@ -13900,7 +13806,6 @@
       <c r="I1504" s="1"/>
     </row>
     <row r="1505" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1505" s="2"/>
       <c r="I1505" s="1"/>
     </row>
     <row r="1506" spans="8:9" x14ac:dyDescent="0.25">
@@ -13908,15 +13813,12 @@
       <c r="I1506" s="1"/>
     </row>
     <row r="1507" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1507" s="2"/>
       <c r="I1507" s="1"/>
     </row>
     <row r="1508" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1508" s="2"/>
       <c r="I1508" s="1"/>
     </row>
     <row r="1509" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1509" s="2"/>
       <c r="I1509" s="1"/>
     </row>
     <row r="1510" spans="8:9" x14ac:dyDescent="0.25">
@@ -13928,7 +13830,6 @@
       <c r="I1511" s="1"/>
     </row>
     <row r="1512" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1512" s="2"/>
       <c r="I1512" s="1"/>
     </row>
     <row r="1513" spans="8:9" x14ac:dyDescent="0.25">
@@ -13936,7 +13837,6 @@
       <c r="I1513" s="1"/>
     </row>
     <row r="1514" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1514" s="2"/>
       <c r="I1514" s="1"/>
     </row>
     <row r="1515" spans="8:9" x14ac:dyDescent="0.25">
@@ -13944,7 +13844,6 @@
       <c r="I1515" s="1"/>
     </row>
     <row r="1516" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1516" s="2"/>
       <c r="I1516" s="1"/>
     </row>
     <row r="1517" spans="8:9" x14ac:dyDescent="0.25">
@@ -13952,7 +13851,6 @@
       <c r="I1517" s="1"/>
     </row>
     <row r="1518" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1518" s="2"/>
       <c r="I1518" s="1"/>
     </row>
     <row r="1519" spans="8:9" x14ac:dyDescent="0.25">
@@ -13960,7 +13858,6 @@
       <c r="I1519" s="1"/>
     </row>
     <row r="1520" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1520" s="2"/>
       <c r="I1520" s="1"/>
     </row>
     <row r="1521" spans="8:9" x14ac:dyDescent="0.25">
@@ -13976,7 +13873,6 @@
       <c r="I1523" s="1"/>
     </row>
     <row r="1524" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1524" s="2"/>
       <c r="I1524" s="1"/>
     </row>
     <row r="1525" spans="8:9" x14ac:dyDescent="0.25">
@@ -13996,7 +13892,6 @@
       <c r="I1528" s="1"/>
     </row>
     <row r="1529" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1529" s="2"/>
       <c r="I1529" s="1"/>
     </row>
     <row r="1530" spans="8:9" x14ac:dyDescent="0.25">
@@ -14004,7 +13899,6 @@
       <c r="I1530" s="1"/>
     </row>
     <row r="1531" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1531" s="2"/>
       <c r="I1531" s="1"/>
     </row>
     <row r="1532" spans="8:9" x14ac:dyDescent="0.25">
@@ -14012,15 +13906,12 @@
       <c r="I1532" s="1"/>
     </row>
     <row r="1533" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1533" s="2"/>
       <c r="I1533" s="1"/>
     </row>
     <row r="1534" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1534" s="2"/>
       <c r="I1534" s="1"/>
     </row>
     <row r="1535" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
     </row>
     <row r="1536" spans="8:9" x14ac:dyDescent="0.25">
@@ -14028,7 +13919,6 @@
       <c r="I1536" s="1"/>
     </row>
     <row r="1537" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1537" s="2"/>
       <c r="I1537" s="1"/>
     </row>
     <row r="1538" spans="8:9" x14ac:dyDescent="0.25">
@@ -14040,10 +13930,10 @@
       <c r="I1539" s="1"/>
     </row>
     <row r="1540" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
     </row>
     <row r="1541" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1541" s="2"/>
       <c r="I1541" s="1"/>
     </row>
     <row r="1542" spans="8:9" x14ac:dyDescent="0.25">
@@ -14055,7 +13945,6 @@
       <c r="I1543" s="1"/>
     </row>
     <row r="1544" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1544" s="2"/>
       <c r="I1544" s="1"/>
     </row>
     <row r="1545" spans="8:9" x14ac:dyDescent="0.25">
@@ -14063,7 +13952,6 @@
       <c r="I1545" s="1"/>
     </row>
     <row r="1546" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1546" s="2"/>
       <c r="I1546" s="1"/>
     </row>
     <row r="1547" spans="8:9" x14ac:dyDescent="0.25">
@@ -14071,11 +13959,9 @@
       <c r="I1547" s="1"/>
     </row>
     <row r="1548" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1548" s="2"/>
       <c r="I1548" s="1"/>
     </row>
     <row r="1549" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1549" s="2"/>
       <c r="I1549" s="1"/>
     </row>
     <row r="1550" spans="8:9" x14ac:dyDescent="0.25">
@@ -14087,6 +13973,7 @@
       <c r="I1551" s="1"/>
     </row>
     <row r="1552" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1552" s="2"/>
       <c r="I1552" s="1"/>
     </row>
     <row r="1553" spans="8:9" x14ac:dyDescent="0.25">
@@ -14094,7 +13981,6 @@
       <c r="I1553" s="1"/>
     </row>
     <row r="1554" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1554" s="2"/>
       <c r="I1554" s="1"/>
     </row>
     <row r="1555" spans="8:9" x14ac:dyDescent="0.25">
@@ -14102,7 +13988,6 @@
       <c r="I1555" s="1"/>
     </row>
     <row r="1556" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1556" s="2"/>
       <c r="I1556" s="1"/>
     </row>
     <row r="1557" spans="8:9" x14ac:dyDescent="0.25">
@@ -14110,11 +13995,9 @@
       <c r="I1557" s="1"/>
     </row>
     <row r="1558" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1558" s="2"/>
       <c r="I1558" s="1"/>
     </row>
     <row r="1559" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1559" s="2"/>
       <c r="I1559" s="1"/>
     </row>
     <row r="1560" spans="8:9" x14ac:dyDescent="0.25">
@@ -14125,11 +14008,9 @@
       <c r="I1561" s="1"/>
     </row>
     <row r="1562" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1562" s="2"/>
       <c r="I1562" s="1"/>
     </row>
     <row r="1563" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1563" s="2"/>
       <c r="I1563" s="1"/>
     </row>
     <row r="1564" spans="8:9" x14ac:dyDescent="0.25">
@@ -14137,11 +14018,9 @@
       <c r="I1564" s="1"/>
     </row>
     <row r="1565" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
     </row>
     <row r="1566" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1566" s="2"/>
       <c r="I1566" s="1"/>
     </row>
     <row r="1567" spans="8:9" x14ac:dyDescent="0.25">
@@ -14149,10 +14028,10 @@
       <c r="I1567" s="1"/>
     </row>
     <row r="1568" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1568" s="2"/>
       <c r="I1568" s="1"/>
     </row>
     <row r="1569" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1569" s="2"/>
       <c r="I1569" s="1"/>
     </row>
     <row r="1570" spans="8:9" x14ac:dyDescent="0.25">
@@ -14164,11 +14043,9 @@
       <c r="I1571" s="1"/>
     </row>
     <row r="1572" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
     </row>
     <row r="1573" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1573" s="2"/>
       <c r="I1573" s="1"/>
     </row>
     <row r="1574" spans="8:9" x14ac:dyDescent="0.25">
@@ -14187,11 +14064,9 @@
       <c r="I1577" s="1"/>
     </row>
     <row r="1578" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1578" s="2"/>
       <c r="I1578" s="1"/>
     </row>
     <row r="1579" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1579" s="2"/>
       <c r="I1579" s="1"/>
     </row>
     <row r="1580" spans="8:9" x14ac:dyDescent="0.25">
@@ -14203,23 +14078,18 @@
       <c r="I1581" s="1"/>
     </row>
     <row r="1582" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1582" s="2"/>
       <c r="I1582" s="1"/>
     </row>
     <row r="1583" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1583" s="2"/>
       <c r="I1583" s="1"/>
     </row>
     <row r="1584" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1584" s="2"/>
       <c r="I1584" s="1"/>
     </row>
     <row r="1585" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1585" s="2"/>
       <c r="I1585" s="1"/>
     </row>
     <row r="1586" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1586" s="2"/>
       <c r="I1586" s="1"/>
     </row>
     <row r="1587" spans="8:9" x14ac:dyDescent="0.25">
@@ -14227,11 +14097,9 @@
       <c r="I1587" s="1"/>
     </row>
     <row r="1588" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1588" s="2"/>
       <c r="I1588" s="1"/>
     </row>
     <row r="1589" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1589" s="2"/>
       <c r="I1589" s="1"/>
     </row>
     <row r="1590" spans="8:9" x14ac:dyDescent="0.25">
@@ -14239,11 +14107,9 @@
       <c r="I1590" s="1"/>
     </row>
     <row r="1591" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1591" s="2"/>
       <c r="I1591" s="1"/>
     </row>
     <row r="1592" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
     </row>
     <row r="1593" spans="8:9" x14ac:dyDescent="0.25">
@@ -14258,6 +14124,7 @@
       <c r="I1595" s="1"/>
     </row>
     <row r="1596" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1596" s="2"/>
       <c r="I1596" s="1"/>
     </row>
     <row r="1597" spans="8:9" x14ac:dyDescent="0.25">
@@ -14265,22 +14132,19 @@
       <c r="I1597" s="1"/>
     </row>
     <row r="1598" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1598" s="2"/>
       <c r="I1598" s="1"/>
     </row>
     <row r="1599" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1599" s="2"/>
       <c r="I1599" s="1"/>
     </row>
     <row r="1600" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1600" s="2"/>
       <c r="I1600" s="1"/>
     </row>
     <row r="1601" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1601" s="2"/>
       <c r="I1601" s="1"/>
     </row>
     <row r="1602" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1602" s="2"/>
       <c r="I1602" s="1"/>
     </row>
     <row r="1603" spans="8:9" x14ac:dyDescent="0.25">
@@ -14292,14 +14156,13 @@
       <c r="I1604" s="1"/>
     </row>
     <row r="1605" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1605" s="2"/>
       <c r="I1605" s="1"/>
     </row>
     <row r="1606" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1606" s="2"/>
       <c r="I1606" s="1"/>
     </row>
     <row r="1607" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1607" s="2"/>
       <c r="I1607" s="1"/>
     </row>
     <row r="1608" spans="8:9" x14ac:dyDescent="0.25">
@@ -14310,7 +14173,6 @@
       <c r="I1609" s="1"/>
     </row>
     <row r="1610" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1610" s="2"/>
       <c r="I1610" s="1"/>
     </row>
     <row r="1611" spans="8:9" x14ac:dyDescent="0.25">
@@ -14321,7 +14183,6 @@
       <c r="I1612" s="1"/>
     </row>
     <row r="1613" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1613" s="2"/>
       <c r="I1613" s="1"/>
     </row>
     <row r="1614" spans="8:9" x14ac:dyDescent="0.25">
@@ -14337,6 +14198,7 @@
       <c r="I1616" s="1"/>
     </row>
     <row r="1617" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1617" s="2"/>
       <c r="I1617" s="1"/>
     </row>
     <row r="1618" spans="8:9" x14ac:dyDescent="0.25">
@@ -14344,6 +14206,7 @@
       <c r="I1618" s="1"/>
     </row>
     <row r="1619" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1619" s="2"/>
       <c r="I1619" s="1"/>
     </row>
     <row r="1620" spans="8:9" x14ac:dyDescent="0.25">
@@ -14351,7 +14214,6 @@
       <c r="I1620" s="1"/>
     </row>
     <row r="1621" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1621" s="2"/>
       <c r="I1621" s="1"/>
     </row>
     <row r="1622" spans="8:9" x14ac:dyDescent="0.25">
@@ -14363,18 +14225,16 @@
       <c r="I1623" s="1"/>
     </row>
     <row r="1624" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
     </row>
     <row r="1625" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1625" s="2"/>
       <c r="I1625" s="1"/>
     </row>
     <row r="1626" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1626" s="2"/>
       <c r="I1626" s="1"/>
     </row>
     <row r="1627" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1627" s="2"/>
       <c r="I1627" s="1"/>
     </row>
     <row r="1628" spans="8:9" x14ac:dyDescent="0.25">
@@ -14385,6 +14245,7 @@
       <c r="I1629" s="1"/>
     </row>
     <row r="1630" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1630" s="2"/>
       <c r="I1630" s="1"/>
     </row>
     <row r="1631" spans="8:9" x14ac:dyDescent="0.25">
@@ -14400,10 +14261,10 @@
       <c r="I1633" s="1"/>
     </row>
     <row r="1634" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1634" s="2"/>
       <c r="I1634" s="1"/>
     </row>
     <row r="1635" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1635" s="2"/>
       <c r="I1635" s="1"/>
     </row>
     <row r="1636" spans="8:9" x14ac:dyDescent="0.25">
@@ -14415,13 +14276,13 @@
       <c r="I1637" s="1"/>
     </row>
     <row r="1638" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1638" s="2"/>
       <c r="I1638" s="1"/>
     </row>
     <row r="1639" spans="8:9" x14ac:dyDescent="0.25">
       <c r="I1639" s="1"/>
     </row>
     <row r="1640" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1640" s="2"/>
       <c r="I1640" s="1"/>
     </row>
     <row r="1641" spans="8:9" x14ac:dyDescent="0.25">
@@ -14429,7 +14290,6 @@
       <c r="I1641" s="1"/>
     </row>
     <row r="1642" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1642" s="2"/>
       <c r="I1642" s="1"/>
     </row>
     <row r="1643" spans="8:9" x14ac:dyDescent="0.25">
@@ -14441,7 +14301,6 @@
       <c r="I1644" s="1"/>
     </row>
     <row r="1645" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1645" s="2"/>
       <c r="I1645" s="1"/>
     </row>
     <row r="1646" spans="8:9" x14ac:dyDescent="0.25">
@@ -14453,7 +14312,6 @@
       <c r="I1647" s="1"/>
     </row>
     <row r="1648" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1648" s="2"/>
       <c r="I1648" s="1"/>
     </row>
     <row r="1649" spans="8:9" x14ac:dyDescent="0.25">
@@ -14461,15 +14319,12 @@
       <c r="I1649" s="1"/>
     </row>
     <row r="1650" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1650" s="2"/>
       <c r="I1650" s="1"/>
     </row>
     <row r="1651" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1651" s="2"/>
       <c r="I1651" s="1"/>
     </row>
     <row r="1652" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1652" s="2"/>
       <c r="I1652" s="1"/>
     </row>
     <row r="1653" spans="8:9" x14ac:dyDescent="0.25">
@@ -14477,6 +14332,7 @@
       <c r="I1653" s="1"/>
     </row>
     <row r="1654" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1654" s="2"/>
       <c r="I1654" s="1"/>
     </row>
     <row r="1655" spans="8:9" x14ac:dyDescent="0.25">
@@ -14492,6 +14348,7 @@
       <c r="I1657" s="1"/>
     </row>
     <row r="1658" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1658" s="2"/>
       <c r="I1658" s="1"/>
     </row>
     <row r="1659" spans="8:9" x14ac:dyDescent="0.25">
@@ -14499,15 +14356,12 @@
       <c r="I1659" s="1"/>
     </row>
     <row r="1660" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1660" s="2"/>
       <c r="I1660" s="1"/>
     </row>
     <row r="1661" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1661" s="2"/>
       <c r="I1661" s="1"/>
     </row>
     <row r="1662" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
     </row>
     <row r="1663" spans="8:9" x14ac:dyDescent="0.25">
@@ -14515,7 +14369,6 @@
       <c r="I1663" s="1"/>
     </row>
     <row r="1664" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1664" s="2"/>
       <c r="I1664" s="1"/>
     </row>
     <row r="1665" spans="8:9" x14ac:dyDescent="0.25">
@@ -14523,7 +14376,6 @@
       <c r="I1665" s="1"/>
     </row>
     <row r="1666" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1666" s="2"/>
       <c r="I1666" s="1"/>
     </row>
     <row r="1667" spans="8:9" x14ac:dyDescent="0.25">
@@ -14531,7 +14383,6 @@
       <c r="I1667" s="1"/>
     </row>
     <row r="1668" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1668" s="2"/>
       <c r="I1668" s="1"/>
     </row>
     <row r="1669" spans="8:9" x14ac:dyDescent="0.25">
@@ -14547,23 +14398,18 @@
       <c r="I1671" s="1"/>
     </row>
     <row r="1672" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1672" s="2"/>
       <c r="I1672" s="1"/>
     </row>
     <row r="1673" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1673" s="2"/>
       <c r="I1673" s="1"/>
     </row>
     <row r="1674" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1674" s="2"/>
       <c r="I1674" s="1"/>
     </row>
     <row r="1675" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1675" s="2"/>
       <c r="I1675" s="1"/>
     </row>
     <row r="1676" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1676" s="2"/>
       <c r="I1676" s="1"/>
     </row>
     <row r="1677" spans="8:9" x14ac:dyDescent="0.25">
@@ -14571,7 +14417,6 @@
       <c r="I1677" s="1"/>
     </row>
     <row r="1678" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1678" s="2"/>
       <c r="I1678" s="1"/>
     </row>
     <row r="1679" spans="8:9" x14ac:dyDescent="0.25">
@@ -14579,7 +14424,6 @@
       <c r="I1679" s="1"/>
     </row>
     <row r="1680" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1680" s="2"/>
       <c r="I1680" s="1"/>
     </row>
     <row r="1681" spans="8:9" x14ac:dyDescent="0.25">
@@ -14587,7 +14431,6 @@
       <c r="I1681" s="1"/>
     </row>
     <row r="1682" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
     </row>
     <row r="1683" spans="8:9" x14ac:dyDescent="0.25">
@@ -14599,7 +14442,6 @@
       <c r="I1684" s="1"/>
     </row>
     <row r="1685" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1685" s="2"/>
       <c r="I1685" s="1"/>
     </row>
     <row r="1686" spans="8:9" x14ac:dyDescent="0.25">
@@ -14627,7 +14469,6 @@
       <c r="I1691" s="1"/>
     </row>
     <row r="1692" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1692" s="2"/>
       <c r="I1692" s="1"/>
     </row>
     <row r="1693" spans="8:9" x14ac:dyDescent="0.25">
@@ -14643,7 +14484,6 @@
       <c r="I1695" s="1"/>
     </row>
     <row r="1696" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
     </row>
     <row r="1697" spans="8:9" x14ac:dyDescent="0.25">
@@ -14683,7 +14523,6 @@
       <c r="I1705" s="1"/>
     </row>
     <row r="1706" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
     </row>
     <row r="1707" spans="8:9" x14ac:dyDescent="0.25">
@@ -14735,7 +14574,6 @@
       <c r="I1718" s="1"/>
     </row>
     <row r="1719" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1719" s="2"/>
       <c r="I1719" s="1"/>
     </row>
     <row r="1720" spans="8:9" x14ac:dyDescent="0.25">
@@ -14795,7 +14633,6 @@
       <c r="I1733" s="1"/>
     </row>
     <row r="1734" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1734" s="2"/>
       <c r="I1734" s="1"/>
     </row>
     <row r="1735" spans="8:9" x14ac:dyDescent="0.25">
@@ -14811,7 +14648,6 @@
       <c r="I1737" s="1"/>
     </row>
     <row r="1738" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1738" s="2"/>
       <c r="I1738" s="1"/>
     </row>
     <row r="1739" spans="8:9" x14ac:dyDescent="0.25">
@@ -14859,7 +14695,6 @@
       <c r="I1749" s="1"/>
     </row>
     <row r="1750" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1750" s="2"/>
       <c r="I1750" s="1"/>
     </row>
     <row r="1751" spans="8:9" x14ac:dyDescent="0.25">
@@ -14895,7 +14730,6 @@
       <c r="I1758" s="1"/>
     </row>
     <row r="1759" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1759" s="2"/>
       <c r="I1759" s="1"/>
     </row>
     <row r="1760" spans="8:9" x14ac:dyDescent="0.25">
@@ -14907,7 +14741,6 @@
       <c r="I1761" s="1"/>
     </row>
     <row r="1762" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1762" s="2"/>
       <c r="I1762" s="1"/>
     </row>
     <row r="1763" spans="8:9" x14ac:dyDescent="0.25">
@@ -14943,7 +14776,6 @@
       <c r="I1770" s="1"/>
     </row>
     <row r="1771" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1771" s="2"/>
       <c r="I1771" s="1"/>
     </row>
     <row r="1772" spans="8:9" x14ac:dyDescent="0.25">
@@ -14967,7 +14799,6 @@
       <c r="I1776" s="1"/>
     </row>
     <row r="1777" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1777" s="2"/>
       <c r="I1777" s="1"/>
     </row>
     <row r="1778" spans="8:9" x14ac:dyDescent="0.25">
@@ -15067,7 +14898,6 @@
       <c r="I1801" s="1"/>
     </row>
     <row r="1802" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1802" s="2"/>
       <c r="I1802" s="1"/>
     </row>
     <row r="1803" spans="8:9" x14ac:dyDescent="0.25">
@@ -15083,7 +14913,6 @@
       <c r="I1805" s="1"/>
     </row>
     <row r="1806" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1806" s="2"/>
       <c r="I1806" s="1"/>
     </row>
     <row r="1807" spans="8:9" x14ac:dyDescent="0.25">
@@ -15099,9 +14928,11 @@
       <c r="I1809" s="1"/>
     </row>
     <row r="1810" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1810" s="2"/>
       <c r="I1810" s="1"/>
     </row>
     <row r="1811" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1811" s="2"/>
       <c r="I1811" s="1"/>
     </row>
     <row r="1812" spans="8:9" x14ac:dyDescent="0.25">
@@ -15109,12 +14940,15 @@
       <c r="I1812" s="1"/>
     </row>
     <row r="1813" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1813" s="2"/>
       <c r="I1813" s="1"/>
     </row>
     <row r="1814" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1814" s="2"/>
       <c r="I1814" s="1"/>
     </row>
     <row r="1815" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1815" s="2"/>
       <c r="I1815" s="1"/>
     </row>
     <row r="1816" spans="8:9" x14ac:dyDescent="0.25">
@@ -15126,9 +14960,11 @@
       <c r="I1817" s="1"/>
     </row>
     <row r="1818" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1818" s="2"/>
       <c r="I1818" s="1"/>
     </row>
     <row r="1819" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1819" s="2"/>
       <c r="I1819" s="1"/>
     </row>
     <row r="1820" spans="8:9" x14ac:dyDescent="0.25">
@@ -15136,6 +14972,7 @@
       <c r="I1820" s="1"/>
     </row>
     <row r="1821" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1821" s="2"/>
       <c r="I1821" s="1"/>
     </row>
     <row r="1822" spans="8:9" x14ac:dyDescent="0.25">
@@ -15147,16 +14984,18 @@
       <c r="I1823" s="1"/>
     </row>
     <row r="1824" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1824" s="2"/>
       <c r="I1824" s="1"/>
     </row>
     <row r="1825" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1825" s="2"/>
       <c r="I1825" s="1"/>
     </row>
     <row r="1826" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1826" s="2"/>
       <c r="I1826" s="1"/>
     </row>
     <row r="1827" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1827" s="2"/>
       <c r="I1827" s="1"/>
     </row>
     <row r="1828" spans="8:9" x14ac:dyDescent="0.25">
@@ -15164,21 +15003,27 @@
       <c r="I1828" s="1"/>
     </row>
     <row r="1829" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1829" s="2"/>
       <c r="I1829" s="1"/>
     </row>
     <row r="1830" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1830" s="2"/>
       <c r="I1830" s="1"/>
     </row>
     <row r="1831" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1831" s="2"/>
       <c r="I1831" s="1"/>
     </row>
     <row r="1832" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1832" s="2"/>
       <c r="I1832" s="1"/>
     </row>
     <row r="1833" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1833" s="2"/>
       <c r="I1833" s="1"/>
     </row>
     <row r="1834" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1834" s="2"/>
       <c r="I1834" s="1"/>
     </row>
     <row r="1835" spans="8:9" x14ac:dyDescent="0.25">
@@ -15186,13 +15031,14 @@
       <c r="I1835" s="1"/>
     </row>
     <row r="1836" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1836" s="2"/>
       <c r="I1836" s="1"/>
     </row>
     <row r="1837" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1837" s="2"/>
       <c r="I1837" s="1"/>
     </row>
     <row r="1838" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1838" s="2"/>
       <c r="I1838" s="1"/>
     </row>
     <row r="1839" spans="8:9" x14ac:dyDescent="0.25">
@@ -15200,6 +15046,7 @@
       <c r="I1839" s="1"/>
     </row>
     <row r="1840" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1840" s="2"/>
       <c r="I1840" s="1"/>
     </row>
     <row r="1841" spans="8:9" x14ac:dyDescent="0.25">
@@ -15211,6 +15058,7 @@
       <c r="I1842" s="1"/>
     </row>
     <row r="1843" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1843" s="2"/>
       <c r="I1843" s="1"/>
     </row>
     <row r="1844" spans="8:9" x14ac:dyDescent="0.25">
@@ -15218,6 +15066,7 @@
       <c r="I1844" s="1"/>
     </row>
     <row r="1845" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1845" s="2"/>
       <c r="I1845" s="1"/>
     </row>
     <row r="1846" spans="8:9" x14ac:dyDescent="0.25">
@@ -15237,9 +15086,11 @@
       <c r="I1849" s="1"/>
     </row>
     <row r="1850" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1850" s="2"/>
       <c r="I1850" s="1"/>
     </row>
     <row r="1851" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1851" s="2"/>
       <c r="I1851" s="1"/>
     </row>
     <row r="1852" spans="8:9" x14ac:dyDescent="0.25">
@@ -15255,9 +15106,11 @@
       <c r="I1854" s="1"/>
     </row>
     <row r="1855" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1855" s="2"/>
       <c r="I1855" s="1"/>
     </row>
     <row r="1856" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1856" s="2"/>
       <c r="I1856" s="1"/>
     </row>
     <row r="1857" spans="8:9" x14ac:dyDescent="0.25">
@@ -15265,6 +15118,7 @@
       <c r="I1857" s="1"/>
     </row>
     <row r="1858" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1858" s="2"/>
       <c r="I1858" s="1"/>
     </row>
     <row r="1859" spans="8:9" x14ac:dyDescent="0.25">
@@ -15272,16 +15126,17 @@
       <c r="I1859" s="1"/>
     </row>
     <row r="1860" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1860" s="2"/>
       <c r="I1860" s="1"/>
     </row>
     <row r="1861" spans="8:9" x14ac:dyDescent="0.25">
       <c r="I1861" s="1"/>
     </row>
     <row r="1862" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1862" s="2"/>
       <c r="I1862" s="1"/>
     </row>
     <row r="1863" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1863" s="2"/>
       <c r="I1863" s="1"/>
     </row>
     <row r="1864" spans="8:9" x14ac:dyDescent="0.25">
@@ -15289,6 +15144,7 @@
       <c r="I1864" s="1"/>
     </row>
     <row r="1865" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1865" s="2"/>
       <c r="I1865" s="1"/>
     </row>
     <row r="1866" spans="8:9" x14ac:dyDescent="0.25">
@@ -15308,9 +15164,11 @@
       <c r="I1869" s="1"/>
     </row>
     <row r="1870" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1870" s="2"/>
       <c r="I1870" s="1"/>
     </row>
     <row r="1871" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1871" s="2"/>
       <c r="I1871" s="1"/>
     </row>
     <row r="1872" spans="8:9" x14ac:dyDescent="0.25">
@@ -15318,6 +15176,7 @@
       <c r="I1872" s="1"/>
     </row>
     <row r="1873" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1873" s="2"/>
       <c r="I1873" s="1"/>
     </row>
     <row r="1874" spans="8:9" x14ac:dyDescent="0.25">
@@ -15325,6 +15184,7 @@
       <c r="I1874" s="1"/>
     </row>
     <row r="1875" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1875" s="2"/>
       <c r="I1875" s="1"/>
     </row>
     <row r="1876" spans="8:9" x14ac:dyDescent="0.25">
@@ -15336,9 +15196,11 @@
       <c r="I1877" s="1"/>
     </row>
     <row r="1878" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1878" s="2"/>
       <c r="I1878" s="1"/>
     </row>
     <row r="1879" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1879" s="2"/>
       <c r="I1879" s="1"/>
     </row>
     <row r="1880" spans="8:9" x14ac:dyDescent="0.25">
@@ -15353,6 +15215,7 @@
       <c r="I1882" s="1"/>
     </row>
     <row r="1883" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1883" s="2"/>
       <c r="I1883" s="1"/>
     </row>
     <row r="1884" spans="8:9" x14ac:dyDescent="0.25">
@@ -15360,9 +15223,11 @@
       <c r="I1884" s="1"/>
     </row>
     <row r="1885" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1885" s="2"/>
       <c r="I1885" s="1"/>
     </row>
     <row r="1886" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1886" s="2"/>
       <c r="I1886" s="1"/>
     </row>
     <row r="1887" spans="8:9" x14ac:dyDescent="0.25">
@@ -15374,12 +15239,15 @@
       <c r="I1888" s="1"/>
     </row>
     <row r="1889" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1889" s="2"/>
       <c r="I1889" s="1"/>
     </row>
     <row r="1890" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1890" s="2"/>
       <c r="I1890" s="1"/>
     </row>
     <row r="1891" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1891" s="2"/>
       <c r="I1891" s="1"/>
     </row>
     <row r="1892" spans="8:9" x14ac:dyDescent="0.25">
@@ -15391,9 +15259,11 @@
       <c r="I1893" s="1"/>
     </row>
     <row r="1894" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1894" s="2"/>
       <c r="I1894" s="1"/>
     </row>
     <row r="1895" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1895" s="2"/>
       <c r="I1895" s="1"/>
     </row>
     <row r="1896" spans="8:9" x14ac:dyDescent="0.25">
@@ -15409,7 +15279,6 @@
       <c r="I1898" s="1"/>
     </row>
     <row r="1899" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1899" s="2"/>
       <c r="I1899" s="1"/>
     </row>
     <row r="1900" spans="8:9" x14ac:dyDescent="0.25">
@@ -15417,6 +15286,7 @@
       <c r="I1900" s="1"/>
     </row>
     <row r="1901" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1901" s="2"/>
       <c r="I1901" s="1"/>
     </row>
     <row r="1902" spans="8:9" x14ac:dyDescent="0.25">
@@ -15428,6 +15298,7 @@
       <c r="I1903" s="1"/>
     </row>
     <row r="1904" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1904" s="2"/>
       <c r="I1904" s="1"/>
     </row>
     <row r="1905" spans="8:9" x14ac:dyDescent="0.25">
@@ -15443,6 +15314,7 @@
       <c r="I1907" s="1"/>
     </row>
     <row r="1908" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1908" s="2"/>
       <c r="I1908" s="1"/>
     </row>
     <row r="1909" spans="8:9" x14ac:dyDescent="0.25">
@@ -15462,7 +15334,6 @@
       <c r="I1912" s="1"/>
     </row>
     <row r="1913" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1913" s="2"/>
       <c r="I1913" s="1"/>
     </row>
     <row r="1914" spans="8:9" x14ac:dyDescent="0.25">
@@ -15514,7 +15385,6 @@
       <c r="I1925" s="1"/>
     </row>
     <row r="1926" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1926" s="2"/>
       <c r="I1926" s="1"/>
     </row>
     <row r="1927" spans="8:9" x14ac:dyDescent="0.25">
@@ -15530,13 +15400,14 @@
       <c r="I1929" s="1"/>
     </row>
     <row r="1930" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1930" s="2"/>
       <c r="I1930" s="1"/>
     </row>
     <row r="1931" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1931" s="2"/>
       <c r="I1931" s="1"/>
     </row>
     <row r="1932" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1932" s="2"/>
       <c r="I1932" s="1"/>
     </row>
     <row r="1933" spans="8:9" x14ac:dyDescent="0.25">
@@ -15547,6 +15418,7 @@
       <c r="I1934" s="1"/>
     </row>
     <row r="1935" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1935" s="2"/>
       <c r="I1935" s="1"/>
     </row>
     <row r="1936" spans="8:9" x14ac:dyDescent="0.25">
@@ -15554,10 +15426,10 @@
       <c r="I1936" s="1"/>
     </row>
     <row r="1937" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
     </row>
     <row r="1938" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1938" s="2"/>
       <c r="I1938" s="1"/>
     </row>
     <row r="1939" spans="8:9" x14ac:dyDescent="0.25">
@@ -15565,6 +15437,7 @@
       <c r="I1939" s="1"/>
     </row>
     <row r="1940" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1940" s="2"/>
       <c r="I1940" s="1"/>
     </row>
     <row r="1941" spans="8:9" x14ac:dyDescent="0.25">
@@ -15579,22 +15452,25 @@
       <c r="I1943" s="1"/>
     </row>
     <row r="1944" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1944" s="2"/>
       <c r="I1944" s="1"/>
     </row>
     <row r="1945" spans="8:9" x14ac:dyDescent="0.25">
       <c r="I1945" s="1"/>
     </row>
     <row r="1946" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1946" s="2"/>
       <c r="I1946" s="1"/>
     </row>
     <row r="1947" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1947" s="2"/>
       <c r="I1947" s="1"/>
     </row>
     <row r="1948" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1948" s="2"/>
       <c r="I1948" s="1"/>
     </row>
     <row r="1949" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1949" s="2"/>
       <c r="I1949" s="1"/>
     </row>
     <row r="1950" spans="8:9" x14ac:dyDescent="0.25">
@@ -15610,6 +15486,7 @@
       <c r="I1952" s="1"/>
     </row>
     <row r="1953" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1953" s="2"/>
       <c r="I1953" s="1"/>
     </row>
     <row r="1954" spans="8:9" x14ac:dyDescent="0.25">
@@ -15617,6 +15494,7 @@
       <c r="I1954" s="1"/>
     </row>
     <row r="1955" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1955" s="2"/>
       <c r="I1955" s="1"/>
     </row>
     <row r="1956" spans="8:9" x14ac:dyDescent="0.25">
@@ -15653,12 +15531,15 @@
       <c r="I1964" s="1"/>
     </row>
     <row r="1965" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
     </row>
     <row r="1966" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1966" s="2"/>
       <c r="I1966" s="1"/>
     </row>
     <row r="1967" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1967" s="2"/>
       <c r="I1967" s="1"/>
     </row>
     <row r="1968" spans="8:9" x14ac:dyDescent="0.25">
@@ -15670,9 +15551,11 @@
       <c r="I1969" s="1"/>
     </row>
     <row r="1970" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1970" s="2"/>
       <c r="I1970" s="1"/>
     </row>
     <row r="1971" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1971" s="2"/>
       <c r="I1971" s="1"/>
     </row>
     <row r="1972" spans="8:9" x14ac:dyDescent="0.25">
@@ -15692,9 +15575,11 @@
       <c r="I1975" s="1"/>
     </row>
     <row r="1976" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1976" s="2"/>
       <c r="I1976" s="1"/>
     </row>
     <row r="1977" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:9" x14ac:dyDescent="0.25">
@@ -15702,10 +15587,10 @@
       <c r="I1978" s="1"/>
     </row>
     <row r="1979" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1979" s="2"/>
       <c r="I1979" s="1"/>
     </row>
     <row r="1980" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1980" s="2"/>
       <c r="I1980" s="1"/>
     </row>
     <row r="1981" spans="8:9" x14ac:dyDescent="0.25">
@@ -15717,15 +15602,19 @@
       <c r="I1982" s="1"/>
     </row>
     <row r="1983" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
     </row>
     <row r="1984" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
     </row>
     <row r="1985" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1985" s="2"/>
       <c r="I1985" s="1"/>
     </row>
     <row r="1986" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
     </row>
     <row r="1987" spans="8:9" x14ac:dyDescent="0.25">
@@ -15737,6 +15626,7 @@
       <c r="I1988" s="1"/>
     </row>
     <row r="1989" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1989" s="2"/>
       <c r="I1989" s="1"/>
     </row>
     <row r="1990" spans="8:9" x14ac:dyDescent="0.25">
@@ -15744,12 +15634,14 @@
       <c r="I1990" s="1"/>
     </row>
     <row r="1991" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1991" s="2"/>
       <c r="I1991" s="1"/>
     </row>
     <row r="1992" spans="8:9" x14ac:dyDescent="0.25">
       <c r="I1992" s="1"/>
     </row>
     <row r="1993" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:9" x14ac:dyDescent="0.25">
@@ -15761,6 +15653,7 @@
       <c r="I1995" s="1"/>
     </row>
     <row r="1996" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1996" s="2"/>
       <c r="I1996" s="1"/>
     </row>
     <row r="1997" spans="8:9" x14ac:dyDescent="0.25">
@@ -15768,6 +15661,7 @@
       <c r="I1997" s="1"/>
     </row>
     <row r="1998" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H1998" s="2"/>
       <c r="I1998" s="1"/>
     </row>
     <row r="1999" spans="8:9" x14ac:dyDescent="0.25">
@@ -15775,6 +15669,7 @@
       <c r="I1999" s="1"/>
     </row>
     <row r="2000" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
     </row>
     <row r="2001" spans="8:9" x14ac:dyDescent="0.25">
@@ -15782,13 +15677,14 @@
       <c r="I2001" s="1"/>
     </row>
     <row r="2002" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2003" s="2"/>
       <c r="I2003" s="1"/>
     </row>
     <row r="2004" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2004" s="2"/>
       <c r="I2004" s="1"/>
     </row>
     <row r="2005" spans="8:9" x14ac:dyDescent="0.25">
@@ -15823,10 +15719,10 @@
       <c r="I2012" s="1"/>
     </row>
     <row r="2013" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2013" s="2"/>
       <c r="I2013" s="1"/>
     </row>
     <row r="2014" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2014" s="2"/>
       <c r="I2014" s="1"/>
     </row>
     <row r="2015" spans="8:9" x14ac:dyDescent="0.25">
@@ -15837,12 +15733,15 @@
       <c r="I2016" s="1"/>
     </row>
     <row r="2017" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2017" s="2"/>
       <c r="I2017" s="1"/>
     </row>
     <row r="2018" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2018" s="2"/>
       <c r="I2018" s="1"/>
     </row>
     <row r="2019" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2019" s="2"/>
       <c r="I2019" s="1"/>
     </row>
     <row r="2020" spans="8:9" x14ac:dyDescent="0.25">
@@ -15850,6 +15749,7 @@
       <c r="I2020" s="1"/>
     </row>
     <row r="2021" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2021" s="2"/>
       <c r="I2021" s="1"/>
     </row>
     <row r="2022" spans="8:9" x14ac:dyDescent="0.25">
@@ -15861,6 +15761,7 @@
       <c r="I2023" s="1"/>
     </row>
     <row r="2024" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2024" s="2"/>
       <c r="I2024" s="1"/>
     </row>
     <row r="2025" spans="8:9" x14ac:dyDescent="0.25">
@@ -15876,6 +15777,7 @@
       <c r="I2027" s="1"/>
     </row>
     <row r="2028" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2028" s="2"/>
       <c r="I2028" s="1"/>
     </row>
     <row r="2029" spans="8:9" x14ac:dyDescent="0.25">
@@ -15890,9 +15792,11 @@
       <c r="I2031" s="1"/>
     </row>
     <row r="2032" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2032" s="2"/>
       <c r="I2032" s="1"/>
     </row>
     <row r="2033" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2033" s="2"/>
       <c r="I2033" s="1"/>
     </row>
     <row r="2034" spans="8:9" x14ac:dyDescent="0.25">
@@ -15912,6 +15816,7 @@
       <c r="I2037" s="1"/>
     </row>
     <row r="2038" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2038" s="2"/>
       <c r="I2038" s="1"/>
     </row>
     <row r="2039" spans="8:9" x14ac:dyDescent="0.25">
@@ -15919,6 +15824,7 @@
       <c r="I2039" s="1"/>
     </row>
     <row r="2040" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2040" s="2"/>
       <c r="I2040" s="1"/>
     </row>
     <row r="2041" spans="8:9" x14ac:dyDescent="0.25">
@@ -15926,22 +15832,26 @@
       <c r="I2041" s="1"/>
     </row>
     <row r="2042" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2042" s="2"/>
       <c r="I2042" s="1"/>
     </row>
     <row r="2043" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2043" s="2"/>
       <c r="I2043" s="1"/>
     </row>
     <row r="2044" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2044" s="2"/>
       <c r="I2044" s="1"/>
     </row>
     <row r="2045" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2045" s="2"/>
       <c r="I2045" s="1"/>
     </row>
     <row r="2046" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2046" s="2"/>
       <c r="I2046" s="1"/>
     </row>
     <row r="2047" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2047" s="2"/>
       <c r="I2047" s="1"/>
     </row>
     <row r="2048" spans="8:9" x14ac:dyDescent="0.25">
@@ -15949,9 +15859,11 @@
       <c r="I2048" s="1"/>
     </row>
     <row r="2049" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2049" s="2"/>
       <c r="I2049" s="1"/>
     </row>
     <row r="2050" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2050" s="2"/>
       <c r="I2050" s="1"/>
     </row>
     <row r="2051" spans="8:9" x14ac:dyDescent="0.25">
@@ -15959,6 +15871,7 @@
       <c r="I2051" s="1"/>
     </row>
     <row r="2052" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2052" s="2"/>
       <c r="I2052" s="1"/>
     </row>
     <row r="2053" spans="8:9" x14ac:dyDescent="0.25">
@@ -15974,16 +15887,18 @@
       <c r="I2055" s="1"/>
     </row>
     <row r="2056" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2056" s="2"/>
       <c r="I2056" s="1"/>
     </row>
     <row r="2057" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2057" s="2"/>
       <c r="I2057" s="1"/>
     </row>
     <row r="2058" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2058" s="2"/>
       <c r="I2058" s="1"/>
     </row>
     <row r="2059" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2059" s="2"/>
       <c r="I2059" s="1"/>
     </row>
     <row r="2060" spans="8:9" x14ac:dyDescent="0.25">
@@ -15991,13 +15906,14 @@
       <c r="I2060" s="1"/>
     </row>
     <row r="2061" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2061" s="2"/>
       <c r="I2061" s="1"/>
     </row>
     <row r="2062" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2062" s="2"/>
       <c r="I2062" s="1"/>
     </row>
     <row r="2063" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2063" s="2"/>
       <c r="I2063" s="1"/>
     </row>
     <row r="2064" spans="8:9" x14ac:dyDescent="0.25">
@@ -16009,18 +15925,23 @@
       <c r="I2065" s="1"/>
     </row>
     <row r="2066" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2066" s="2"/>
       <c r="I2066" s="1"/>
     </row>
     <row r="2067" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2067" s="2"/>
       <c r="I2067" s="1"/>
     </row>
     <row r="2068" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2068" s="2"/>
       <c r="I2068" s="1"/>
     </row>
     <row r="2069" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2069" s="2"/>
       <c r="I2069" s="1"/>
     </row>
     <row r="2070" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2070" s="2"/>
       <c r="I2070" s="1"/>
     </row>
     <row r="2071" spans="8:9" x14ac:dyDescent="0.25">
@@ -16028,9 +15949,11 @@
       <c r="I2071" s="1"/>
     </row>
     <row r="2072" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2072" s="2"/>
       <c r="I2072" s="1"/>
     </row>
     <row r="2073" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2073" s="2"/>
       <c r="I2073" s="1"/>
     </row>
     <row r="2074" spans="8:9" x14ac:dyDescent="0.25">
@@ -16041,6 +15964,7 @@
       <c r="I2075" s="1"/>
     </row>
     <row r="2076" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2076" s="2"/>
       <c r="I2076" s="1"/>
     </row>
     <row r="2077" spans="8:9" x14ac:dyDescent="0.25">
@@ -16052,10 +15976,10 @@
       <c r="I2078" s="1"/>
     </row>
     <row r="2079" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2079" s="2"/>
       <c r="I2079" s="1"/>
     </row>
     <row r="2080" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2080" s="2"/>
       <c r="I2080" s="1"/>
     </row>
     <row r="2081" spans="8:9" x14ac:dyDescent="0.25">
@@ -16063,15 +15987,18 @@
       <c r="I2081" s="1"/>
     </row>
     <row r="2082" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2082" s="2"/>
       <c r="I2082" s="1"/>
     </row>
     <row r="2083" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2083" s="2"/>
       <c r="I2083" s="1"/>
     </row>
     <row r="2084" spans="8:9" x14ac:dyDescent="0.25">
       <c r="I2084" s="1"/>
     </row>
     <row r="2085" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2085" s="2"/>
       <c r="I2085" s="1"/>
     </row>
     <row r="2086" spans="8:9" x14ac:dyDescent="0.25">
@@ -16091,9 +16018,11 @@
       <c r="I2089" s="1"/>
     </row>
     <row r="2090" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2090" s="2"/>
       <c r="I2090" s="1"/>
     </row>
     <row r="2091" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2091" s="2"/>
       <c r="I2091" s="1"/>
     </row>
     <row r="2092" spans="8:9" x14ac:dyDescent="0.25">
@@ -16101,9 +16030,11 @@
       <c r="I2092" s="1"/>
     </row>
     <row r="2093" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2093" s="2"/>
       <c r="I2093" s="1"/>
     </row>
     <row r="2094" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2094" s="2"/>
       <c r="I2094" s="1"/>
     </row>
     <row r="2095" spans="8:9" x14ac:dyDescent="0.25">
@@ -16111,6 +16042,7 @@
       <c r="I2095" s="1"/>
     </row>
     <row r="2096" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2096" s="2"/>
       <c r="I2096" s="1"/>
     </row>
     <row r="2097" spans="8:9" x14ac:dyDescent="0.25">
@@ -16145,6 +16077,7 @@
       <c r="I2104" s="1"/>
     </row>
     <row r="2105" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2105" s="2"/>
       <c r="I2105" s="1"/>
     </row>
     <row r="2106" spans="8:9" x14ac:dyDescent="0.25">
@@ -16156,16 +16089,18 @@
       <c r="I2107" s="1"/>
     </row>
     <row r="2108" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2108" s="2"/>
       <c r="I2108" s="1"/>
     </row>
     <row r="2109" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2109" s="2"/>
       <c r="I2109" s="1"/>
     </row>
     <row r="2110" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2110" s="2"/>
       <c r="I2110" s="1"/>
     </row>
     <row r="2111" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2111" s="2"/>
       <c r="I2111" s="1"/>
     </row>
     <row r="2112" spans="8:9" x14ac:dyDescent="0.25">
@@ -16192,10 +16127,10 @@
       <c r="I2117" s="1"/>
     </row>
     <row r="2118" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2118" s="2"/>
       <c r="I2118" s="1"/>
     </row>
     <row r="2119" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2119" s="2"/>
       <c r="I2119" s="1"/>
     </row>
     <row r="2120" spans="8:9" x14ac:dyDescent="0.25">
@@ -16211,9 +16146,11 @@
       <c r="I2122" s="1"/>
     </row>
     <row r="2123" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2123" s="2"/>
       <c r="I2123" s="1"/>
     </row>
     <row r="2124" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2124" s="2"/>
       <c r="I2124" s="1"/>
     </row>
     <row r="2125" spans="8:9" x14ac:dyDescent="0.25">
@@ -16221,6 +16158,7 @@
       <c r="I2125" s="1"/>
     </row>
     <row r="2126" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2126" s="2"/>
       <c r="I2126" s="1"/>
     </row>
     <row r="2127" spans="8:9" x14ac:dyDescent="0.25">
@@ -16243,6 +16181,7 @@
       <c r="I2131" s="1"/>
     </row>
     <row r="2132" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2132" s="2"/>
       <c r="I2132" s="1"/>
     </row>
     <row r="2133" spans="8:9" x14ac:dyDescent="0.25">
@@ -16250,12 +16189,15 @@
       <c r="I2133" s="1"/>
     </row>
     <row r="2134" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2134" s="2"/>
       <c r="I2134" s="1"/>
     </row>
     <row r="2135" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2135" s="2"/>
       <c r="I2135" s="1"/>
     </row>
     <row r="2136" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2136" s="2"/>
       <c r="I2136" s="1"/>
     </row>
     <row r="2137" spans="8:9" x14ac:dyDescent="0.25">
@@ -16287,12 +16229,15 @@
       <c r="I2143" s="1"/>
     </row>
     <row r="2144" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2144" s="2"/>
       <c r="I2144" s="1"/>
     </row>
     <row r="2145" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2145" s="2"/>
       <c r="I2145" s="1"/>
     </row>
     <row r="2146" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2146" s="2"/>
       <c r="I2146" s="1"/>
     </row>
     <row r="2147" spans="8:9" x14ac:dyDescent="0.25">
@@ -16300,13 +16245,14 @@
       <c r="I2147" s="1"/>
     </row>
     <row r="2148" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2148" s="2"/>
       <c r="I2148" s="1"/>
     </row>
     <row r="2149" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2149" s="2"/>
       <c r="I2149" s="1"/>
     </row>
     <row r="2150" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2150" s="2"/>
       <c r="I2150" s="1"/>
     </row>
     <row r="2151" spans="8:9" x14ac:dyDescent="0.25">
@@ -16329,25 +16275,30 @@
       <c r="I2155" s="1"/>
     </row>
     <row r="2156" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2156" s="2"/>
       <c r="I2156" s="1"/>
     </row>
     <row r="2157" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2157" s="2"/>
       <c r="I2157" s="1"/>
     </row>
     <row r="2158" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2158" s="2"/>
       <c r="I2158" s="1"/>
     </row>
     <row r="2159" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2159" s="2"/>
       <c r="I2159" s="1"/>
     </row>
     <row r="2160" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2160" s="2"/>
       <c r="I2160" s="1"/>
     </row>
     <row r="2161" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2161" s="2"/>
       <c r="I2161" s="1"/>
     </row>
     <row r="2162" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2162" s="2"/>
       <c r="I2162" s="1"/>
     </row>
     <row r="2163" spans="8:9" x14ac:dyDescent="0.25">
@@ -16355,6 +16306,7 @@
       <c r="I2163" s="1"/>
     </row>
     <row r="2164" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2164" s="2"/>
       <c r="I2164" s="1"/>
     </row>
     <row r="2165" spans="8:9" x14ac:dyDescent="0.25">
@@ -16362,6 +16314,7 @@
       <c r="I2165" s="1"/>
     </row>
     <row r="2166" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2166" s="2"/>
       <c r="I2166" s="1"/>
     </row>
     <row r="2167" spans="8:9" x14ac:dyDescent="0.25">
@@ -16373,10 +16326,10 @@
       <c r="I2168" s="1"/>
     </row>
     <row r="2169" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2169" s="2"/>
       <c r="I2169" s="1"/>
     </row>
     <row r="2170" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2170" s="2"/>
       <c r="I2170" s="1"/>
     </row>
     <row r="2171" spans="8:9" x14ac:dyDescent="0.25">
@@ -16384,7 +16337,6 @@
       <c r="I2171" s="1"/>
     </row>
     <row r="2172" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2172" s="2"/>
       <c r="I2172" s="1"/>
     </row>
     <row r="2173" spans="8:9" x14ac:dyDescent="0.25">
@@ -16400,6 +16352,7 @@
       <c r="I2175" s="1"/>
     </row>
     <row r="2176" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2176" s="2"/>
       <c r="I2176" s="1"/>
     </row>
     <row r="2177" spans="8:9" x14ac:dyDescent="0.25">
@@ -16411,10 +16364,10 @@
       <c r="I2178" s="1"/>
     </row>
     <row r="2179" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2179" s="2"/>
       <c r="I2179" s="1"/>
     </row>
     <row r="2180" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2180" s="2"/>
       <c r="I2180" s="1"/>
     </row>
     <row r="2181" spans="8:9" x14ac:dyDescent="0.25">
@@ -16422,7 +16375,6 @@
       <c r="I2181" s="1"/>
     </row>
     <row r="2182" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2182" s="2"/>
       <c r="I2182" s="1"/>
     </row>
     <row r="2183" spans="8:9" x14ac:dyDescent="0.25">
@@ -16457,7 +16409,6 @@
       <c r="I2190" s="1"/>
     </row>
     <row r="2191" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2191" s="2"/>
       <c r="I2191" s="1"/>
     </row>
     <row r="2192" spans="8:9" x14ac:dyDescent="0.25">
@@ -16528,7 +16479,6 @@
       <c r="I2208" s="1"/>
     </row>
     <row r="2209" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2209" s="2"/>
       <c r="I2209" s="1"/>
     </row>
     <row r="2210" spans="8:9" x14ac:dyDescent="0.25">
@@ -16564,6 +16514,7 @@
       <c r="I2217" s="1"/>
     </row>
     <row r="2218" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2218" s="2"/>
       <c r="I2218" s="1"/>
     </row>
     <row r="2219" spans="8:9" x14ac:dyDescent="0.25">
@@ -16579,6 +16530,7 @@
       <c r="I2221" s="1"/>
     </row>
     <row r="2222" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2222" s="2"/>
       <c r="I2222" s="1"/>
     </row>
     <row r="2223" spans="8:9" x14ac:dyDescent="0.25">
@@ -16594,7 +16546,6 @@
       <c r="I2225" s="1"/>
     </row>
     <row r="2226" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2226" s="2"/>
       <c r="I2226" s="1"/>
     </row>
     <row r="2227" spans="8:9" x14ac:dyDescent="0.25">
@@ -16626,10 +16577,10 @@
       <c r="I2233" s="1"/>
     </row>
     <row r="2234" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2234" s="2"/>
       <c r="I2234" s="1"/>
     </row>
     <row r="2235" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2235" s="2"/>
       <c r="I2235" s="1"/>
     </row>
     <row r="2236" spans="8:9" x14ac:dyDescent="0.25">
@@ -16661,6 +16612,7 @@
       <c r="I2242" s="1"/>
     </row>
     <row r="2243" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2243" s="2"/>
       <c r="I2243" s="1"/>
     </row>
     <row r="2244" spans="8:9" x14ac:dyDescent="0.25">
@@ -16672,10 +16624,10 @@
       <c r="I2245" s="1"/>
     </row>
     <row r="2246" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2246" s="2"/>
       <c r="I2246" s="1"/>
     </row>
     <row r="2247" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2247" s="2"/>
       <c r="I2247" s="1"/>
     </row>
     <row r="2248" spans="8:9" x14ac:dyDescent="0.25">
@@ -16707,6 +16659,7 @@
       <c r="I2254" s="1"/>
     </row>
     <row r="2255" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2255" s="2"/>
       <c r="I2255" s="1"/>
     </row>
     <row r="2256" spans="8:9" x14ac:dyDescent="0.25">
@@ -16730,6 +16683,7 @@
       <c r="I2260" s="1"/>
     </row>
     <row r="2261" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2261" s="2"/>
       <c r="I2261" s="1"/>
     </row>
     <row r="2262" spans="8:9" x14ac:dyDescent="0.25">
@@ -16749,7 +16703,6 @@
       <c r="I2265" s="1"/>
     </row>
     <row r="2266" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2266" s="2"/>
       <c r="I2266" s="1"/>
     </row>
     <row r="2267" spans="8:9" x14ac:dyDescent="0.25">
@@ -16769,7 +16722,6 @@
       <c r="I2270" s="1"/>
     </row>
     <row r="2271" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2271" s="2"/>
       <c r="I2271" s="1"/>
     </row>
     <row r="2272" spans="8:9" x14ac:dyDescent="0.25">
@@ -16829,6 +16781,7 @@
       <c r="I2285" s="1"/>
     </row>
     <row r="2286" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2286" s="2"/>
       <c r="I2286" s="1"/>
     </row>
     <row r="2287" spans="8:9" x14ac:dyDescent="0.25">
@@ -16844,6 +16797,7 @@
       <c r="I2289" s="1"/>
     </row>
     <row r="2290" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2290" s="2"/>
       <c r="I2290" s="1"/>
     </row>
     <row r="2291" spans="8:9" x14ac:dyDescent="0.25">
@@ -16887,7 +16841,6 @@
       <c r="I2300" s="1"/>
     </row>
     <row r="2301" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2301" s="2"/>
       <c r="I2301" s="1"/>
     </row>
     <row r="2302" spans="8:9" x14ac:dyDescent="0.25">
@@ -16915,6 +16868,7 @@
       <c r="I2307" s="1"/>
     </row>
     <row r="2308" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2308" s="2"/>
       <c r="I2308" s="1"/>
     </row>
     <row r="2309" spans="8:9" x14ac:dyDescent="0.25">
@@ -16950,11 +16904,9 @@
       <c r="I2316" s="1"/>
     </row>
     <row r="2317" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2317" s="2"/>
       <c r="I2317" s="1"/>
     </row>
     <row r="2318" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2318" s="2"/>
       <c r="I2318" s="1"/>
     </row>
     <row r="2319" spans="8:9" x14ac:dyDescent="0.25">
@@ -16962,6 +16914,7 @@
       <c r="I2319" s="1"/>
     </row>
     <row r="2320" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2320" s="2"/>
       <c r="I2320" s="1"/>
     </row>
     <row r="2321" spans="8:9" x14ac:dyDescent="0.25">
@@ -16985,11 +16938,9 @@
       <c r="I2325" s="1"/>
     </row>
     <row r="2326" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2326" s="2"/>
       <c r="I2326" s="1"/>
     </row>
     <row r="2327" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2327" s="2"/>
       <c r="I2327" s="1"/>
     </row>
     <row r="2328" spans="8:9" x14ac:dyDescent="0.25">
@@ -17061,6 +17012,7 @@
       <c r="I2344" s="1"/>
     </row>
     <row r="2345" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2345" s="2"/>
       <c r="I2345" s="1"/>
     </row>
     <row r="2346" spans="8:9" x14ac:dyDescent="0.25">
@@ -17068,6 +17020,7 @@
       <c r="I2346" s="1"/>
     </row>
     <row r="2347" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2347" s="2"/>
       <c r="I2347" s="1"/>
     </row>
     <row r="2348" spans="8:9" x14ac:dyDescent="0.25">
@@ -17091,7 +17044,6 @@
       <c r="I2352" s="1"/>
     </row>
     <row r="2353" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2353" s="2"/>
       <c r="I2353" s="1"/>
     </row>
     <row r="2354" spans="8:9" x14ac:dyDescent="0.25">
@@ -17119,7 +17071,6 @@
       <c r="I2359" s="1"/>
     </row>
     <row r="2360" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2360" s="2"/>
       <c r="I2360" s="1"/>
     </row>
     <row r="2361" spans="8:9" x14ac:dyDescent="0.25">
@@ -17135,6 +17086,7 @@
       <c r="I2363" s="1"/>
     </row>
     <row r="2364" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2364" s="2"/>
       <c r="I2364" s="1"/>
     </row>
     <row r="2365" spans="8:9" x14ac:dyDescent="0.25">
@@ -17210,6 +17162,7 @@
       <c r="I2382" s="1"/>
     </row>
     <row r="2383" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2383" s="2"/>
       <c r="I2383" s="1"/>
     </row>
     <row r="2384" spans="8:9" x14ac:dyDescent="0.25">
@@ -17265,6 +17218,7 @@
       <c r="I2396" s="1"/>
     </row>
     <row r="2397" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2397" s="2"/>
       <c r="I2397" s="1"/>
     </row>
     <row r="2398" spans="8:9" x14ac:dyDescent="0.25">
@@ -17288,7 +17242,6 @@
       <c r="I2402" s="1"/>
     </row>
     <row r="2403" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2403" s="2"/>
       <c r="I2403" s="1"/>
     </row>
     <row r="2404" spans="8:9" x14ac:dyDescent="0.25">
@@ -17316,6 +17269,7 @@
       <c r="I2409" s="1"/>
     </row>
     <row r="2410" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2410" s="2"/>
       <c r="I2410" s="1"/>
     </row>
     <row r="2411" spans="8:9" x14ac:dyDescent="0.25">
@@ -17323,7 +17277,6 @@
       <c r="I2411" s="1"/>
     </row>
     <row r="2412" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2412" s="2"/>
       <c r="I2412" s="1"/>
     </row>
     <row r="2413" spans="8:9" x14ac:dyDescent="0.25">
@@ -17331,7 +17284,6 @@
       <c r="I2413" s="1"/>
     </row>
     <row r="2414" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2414" s="2"/>
       <c r="I2414" s="1"/>
     </row>
     <row r="2415" spans="8:9" x14ac:dyDescent="0.25">
@@ -17346,6 +17298,7 @@
       <c r="I2417" s="1"/>
     </row>
     <row r="2418" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2418" s="2"/>
       <c r="I2418" s="1"/>
     </row>
     <row r="2419" spans="8:9" x14ac:dyDescent="0.25">
@@ -17357,6 +17310,7 @@
       <c r="I2420" s="1"/>
     </row>
     <row r="2421" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2421" s="2"/>
       <c r="I2421" s="1"/>
     </row>
     <row r="2422" spans="8:9" x14ac:dyDescent="0.25">
@@ -17364,7 +17318,6 @@
       <c r="I2422" s="1"/>
     </row>
     <row r="2423" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2423" s="2"/>
       <c r="I2423" s="1"/>
     </row>
     <row r="2424" spans="8:9" x14ac:dyDescent="0.25">
@@ -17372,6 +17325,7 @@
       <c r="I2424" s="1"/>
     </row>
     <row r="2425" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2425" s="2"/>
       <c r="I2425" s="1"/>
     </row>
     <row r="2426" spans="8:9" x14ac:dyDescent="0.25">
@@ -17379,7 +17333,6 @@
       <c r="I2426" s="1"/>
     </row>
     <row r="2427" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2427" s="2"/>
       <c r="I2427" s="1"/>
     </row>
     <row r="2428" spans="8:9" x14ac:dyDescent="0.25">
@@ -17387,6 +17340,7 @@
       <c r="I2428" s="1"/>
     </row>
     <row r="2429" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2429" s="2"/>
       <c r="I2429" s="1"/>
     </row>
     <row r="2430" spans="8:9" x14ac:dyDescent="0.25">
@@ -17398,6 +17352,7 @@
       <c r="I2431" s="1"/>
     </row>
     <row r="2432" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2432" s="2"/>
       <c r="I2432" s="1"/>
     </row>
     <row r="2433" spans="8:9" x14ac:dyDescent="0.25">
@@ -17417,7 +17372,6 @@
       <c r="I2436" s="1"/>
     </row>
     <row r="2437" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2437" s="2"/>
       <c r="I2437" s="1"/>
     </row>
     <row r="2438" spans="8:9" x14ac:dyDescent="0.25">
@@ -17429,16 +17383,18 @@
       <c r="I2439" s="1"/>
     </row>
     <row r="2440" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2440" s="2"/>
       <c r="I2440" s="1"/>
     </row>
     <row r="2441" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2441" s="2"/>
       <c r="I2441" s="1"/>
     </row>
     <row r="2442" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2442" s="2"/>
       <c r="I2442" s="1"/>
     </row>
     <row r="2443" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2443" s="2"/>
       <c r="I2443" s="1"/>
     </row>
     <row r="2444" spans="8:9" x14ac:dyDescent="0.25">
@@ -17518,6 +17474,7 @@
       <c r="I2462" s="1"/>
     </row>
     <row r="2463" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2463" s="2"/>
       <c r="I2463" s="1"/>
     </row>
     <row r="2464" spans="8:9" x14ac:dyDescent="0.25">
@@ -17612,6 +17569,7 @@
       <c r="I2486" s="1"/>
     </row>
     <row r="2487" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2487" s="2"/>
       <c r="I2487" s="1"/>
     </row>
     <row r="2488" spans="8:9" x14ac:dyDescent="0.25">
@@ -17631,6 +17589,7 @@
       <c r="I2491" s="1"/>
     </row>
     <row r="2492" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2492" s="2"/>
       <c r="I2492" s="1"/>
     </row>
     <row r="2493" spans="8:9" x14ac:dyDescent="0.25">
@@ -17650,13 +17609,14 @@
       <c r="I2496" s="1"/>
     </row>
     <row r="2497" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2497" s="2"/>
       <c r="I2497" s="1"/>
     </row>
     <row r="2498" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2498" s="2"/>
       <c r="I2498" s="1"/>
     </row>
     <row r="2499" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2499" s="2"/>
       <c r="I2499" s="1"/>
     </row>
     <row r="2500" spans="8:9" x14ac:dyDescent="0.25">
@@ -17700,7 +17660,6 @@
       <c r="I2509" s="1"/>
     </row>
     <row r="2510" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2510" s="2"/>
       <c r="I2510" s="1"/>
     </row>
     <row r="2511" spans="8:9" x14ac:dyDescent="0.25">
@@ -17716,6 +17675,7 @@
       <c r="I2513" s="1"/>
     </row>
     <row r="2514" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2514" s="2"/>
       <c r="I2514" s="1"/>
     </row>
     <row r="2515" spans="8:9" x14ac:dyDescent="0.25">
@@ -17775,6 +17735,7 @@
       <c r="I2528" s="1"/>
     </row>
     <row r="2529" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2529" s="2"/>
       <c r="I2529" s="1"/>
     </row>
     <row r="2530" spans="8:9" x14ac:dyDescent="0.25">
@@ -17826,6 +17787,7 @@
       <c r="I2541" s="1"/>
     </row>
     <row r="2542" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2542" s="2"/>
       <c r="I2542" s="1"/>
     </row>
     <row r="2543" spans="8:9" x14ac:dyDescent="0.25">
@@ -17837,6 +17799,7 @@
       <c r="I2544" s="1"/>
     </row>
     <row r="2545" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2545" s="2"/>
       <c r="I2545" s="1"/>
     </row>
     <row r="2546" spans="8:9" x14ac:dyDescent="0.25">
@@ -17856,7 +17819,6 @@
       <c r="I2549" s="1"/>
     </row>
     <row r="2550" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2550" s="2"/>
       <c r="I2550" s="1"/>
     </row>
     <row r="2551" spans="8:9" x14ac:dyDescent="0.25">
@@ -17892,6 +17854,7 @@
       <c r="I2558" s="1"/>
     </row>
     <row r="2559" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2559" s="2"/>
       <c r="I2559" s="1"/>
     </row>
     <row r="2560" spans="8:9" x14ac:dyDescent="0.25">
@@ -17911,10 +17874,10 @@
       <c r="I2563" s="1"/>
     </row>
     <row r="2564" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2564" s="2"/>
       <c r="I2564" s="1"/>
     </row>
     <row r="2565" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2565" s="2"/>
       <c r="I2565" s="1"/>
     </row>
     <row r="2566" spans="8:9" x14ac:dyDescent="0.25">
@@ -17926,6 +17889,7 @@
       <c r="I2567" s="1"/>
     </row>
     <row r="2568" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2568" s="2"/>
       <c r="I2568" s="1"/>
     </row>
     <row r="2569" spans="8:9" x14ac:dyDescent="0.25">
@@ -17977,6 +17941,7 @@
       <c r="I2580" s="1"/>
     </row>
     <row r="2581" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2581" s="2"/>
       <c r="I2581" s="1"/>
     </row>
     <row r="2582" spans="8:9" x14ac:dyDescent="0.25">
@@ -18028,6 +17993,7 @@
       <c r="I2593" s="1"/>
     </row>
     <row r="2594" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2594" s="2"/>
       <c r="I2594" s="1"/>
     </row>
     <row r="2595" spans="8:9" x14ac:dyDescent="0.25">
@@ -18035,6 +18001,7 @@
       <c r="I2595" s="1"/>
     </row>
     <row r="2596" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2596" s="2"/>
       <c r="I2596" s="1"/>
     </row>
     <row r="2597" spans="8:9" x14ac:dyDescent="0.25">
@@ -18054,7 +18021,6 @@
       <c r="I2600" s="1"/>
     </row>
     <row r="2601" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2601" s="2"/>
       <c r="I2601" s="1"/>
     </row>
     <row r="2602" spans="8:9" x14ac:dyDescent="0.25">
@@ -18062,6 +18028,7 @@
       <c r="I2602" s="1"/>
     </row>
     <row r="2603" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2603" s="2"/>
       <c r="I2603" s="1"/>
     </row>
     <row r="2604" spans="8:9" x14ac:dyDescent="0.25">
@@ -18101,6 +18068,7 @@
       <c r="I2612" s="1"/>
     </row>
     <row r="2613" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2613" s="2"/>
       <c r="I2613" s="1"/>
     </row>
     <row r="2614" spans="8:9" x14ac:dyDescent="0.25">
@@ -18172,7 +18140,6 @@
       <c r="I2630" s="1"/>
     </row>
     <row r="2631" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2631" s="2"/>
       <c r="I2631" s="1"/>
     </row>
     <row r="2632" spans="8:9" x14ac:dyDescent="0.25">
@@ -18180,6 +18147,7 @@
       <c r="I2632" s="1"/>
     </row>
     <row r="2633" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2633" s="2"/>
       <c r="I2633" s="1"/>
     </row>
     <row r="2634" spans="8:9" x14ac:dyDescent="0.25">
@@ -18191,6 +18159,7 @@
       <c r="I2635" s="1"/>
     </row>
     <row r="2636" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2636" s="2"/>
       <c r="I2636" s="1"/>
     </row>
     <row r="2637" spans="8:9" x14ac:dyDescent="0.25">
@@ -18226,6 +18195,7 @@
       <c r="I2644" s="1"/>
     </row>
     <row r="2645" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2645" s="2"/>
       <c r="I2645" s="1"/>
     </row>
     <row r="2646" spans="8:9" x14ac:dyDescent="0.25">
@@ -18261,6 +18231,7 @@
       <c r="I2653" s="1"/>
     </row>
     <row r="2654" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2654" s="2"/>
       <c r="I2654" s="1"/>
     </row>
     <row r="2655" spans="8:9" x14ac:dyDescent="0.25">
@@ -18268,6 +18239,7 @@
       <c r="I2655" s="1"/>
     </row>
     <row r="2656" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2656" s="2"/>
       <c r="I2656" s="1"/>
     </row>
     <row r="2657" spans="8:9" x14ac:dyDescent="0.25">
@@ -18295,10 +18267,10 @@
       <c r="I2662" s="1"/>
     </row>
     <row r="2663" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2663" s="2"/>
       <c r="I2663" s="1"/>
     </row>
     <row r="2664" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2664" s="2"/>
       <c r="I2664" s="1"/>
     </row>
     <row r="2665" spans="8:9" x14ac:dyDescent="0.25">
@@ -18306,6 +18278,7 @@
       <c r="I2665" s="1"/>
     </row>
     <row r="2666" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2666" s="2"/>
       <c r="I2666" s="1"/>
     </row>
     <row r="2667" spans="8:9" x14ac:dyDescent="0.25">
@@ -18317,7 +18290,6 @@
       <c r="I2668" s="1"/>
     </row>
     <row r="2669" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2669" s="2"/>
       <c r="I2669" s="1"/>
     </row>
     <row r="2670" spans="8:9" x14ac:dyDescent="0.25">
@@ -18329,7 +18301,6 @@
       <c r="I2671" s="1"/>
     </row>
     <row r="2672" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2672" s="2"/>
       <c r="I2672" s="1"/>
     </row>
     <row r="2673" spans="8:9" x14ac:dyDescent="0.25">
@@ -18337,9 +18308,11 @@
       <c r="I2673" s="1"/>
     </row>
     <row r="2674" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2674" s="2"/>
       <c r="I2674" s="1"/>
     </row>
     <row r="2675" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2675" s="2"/>
       <c r="I2675" s="1"/>
     </row>
     <row r="2676" spans="8:9" x14ac:dyDescent="0.25">
@@ -18351,7 +18324,6 @@
       <c r="I2677" s="1"/>
     </row>
     <row r="2678" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2678" s="2"/>
       <c r="I2678" s="1"/>
     </row>
     <row r="2679" spans="8:9" x14ac:dyDescent="0.25">
@@ -18387,10 +18359,10 @@
       <c r="I2686" s="1"/>
     </row>
     <row r="2687" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2687" s="2"/>
       <c r="I2687" s="1"/>
     </row>
     <row r="2688" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2688" s="2"/>
       <c r="I2688" s="1"/>
     </row>
     <row r="2689" spans="8:9" x14ac:dyDescent="0.25">
@@ -18410,6 +18382,7 @@
       <c r="I2692" s="1"/>
     </row>
     <row r="2693" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2693" s="2"/>
       <c r="I2693" s="1"/>
     </row>
     <row r="2694" spans="8:9" x14ac:dyDescent="0.25">
@@ -18477,6 +18450,7 @@
       <c r="I2709" s="1"/>
     </row>
     <row r="2710" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2710" s="2"/>
       <c r="I2710" s="1"/>
     </row>
     <row r="2711" spans="8:9" x14ac:dyDescent="0.25">
@@ -18512,6 +18486,7 @@
       <c r="I2718" s="1"/>
     </row>
     <row r="2719" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2719" s="2"/>
       <c r="I2719" s="1"/>
     </row>
     <row r="2720" spans="8:9" x14ac:dyDescent="0.25">
@@ -18559,6 +18534,7 @@
       <c r="I2730" s="1"/>
     </row>
     <row r="2731" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2731" s="2"/>
       <c r="I2731" s="1"/>
     </row>
     <row r="2732" spans="8:9" x14ac:dyDescent="0.25">
@@ -18634,6 +18610,7 @@
       <c r="I2749" s="1"/>
     </row>
     <row r="2750" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2750" s="2"/>
       <c r="I2750" s="1"/>
     </row>
     <row r="2751" spans="8:9" x14ac:dyDescent="0.25">
@@ -18653,6 +18630,7 @@
       <c r="I2754" s="1"/>
     </row>
     <row r="2755" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2755" s="2"/>
       <c r="I2755" s="1"/>
     </row>
     <row r="2756" spans="8:9" x14ac:dyDescent="0.25">
@@ -18772,6 +18750,7 @@
       <c r="I2784" s="1"/>
     </row>
     <row r="2785" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2785" s="2"/>
       <c r="I2785" s="1"/>
     </row>
     <row r="2786" spans="8:9" x14ac:dyDescent="0.25">
@@ -18835,9 +18814,11 @@
       <c r="I2800" s="1"/>
     </row>
     <row r="2801" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2801" s="2"/>
       <c r="I2801" s="1"/>
     </row>
     <row r="2802" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2802" s="2"/>
       <c r="I2802" s="1"/>
     </row>
     <row r="2803" spans="8:9" x14ac:dyDescent="0.25">
@@ -18869,9 +18850,11 @@
       <c r="I2809" s="1"/>
     </row>
     <row r="2810" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2810" s="2"/>
       <c r="I2810" s="1"/>
     </row>
     <row r="2811" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2811" s="2"/>
       <c r="I2811" s="1"/>
     </row>
     <row r="2812" spans="8:9" x14ac:dyDescent="0.25">
@@ -18899,7 +18882,6 @@
       <c r="I2817" s="1"/>
     </row>
     <row r="2818" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2818" s="2"/>
       <c r="I2818" s="1"/>
     </row>
     <row r="2819" spans="8:9" x14ac:dyDescent="0.25">
@@ -18975,6 +18957,7 @@
       <c r="I2836" s="1"/>
     </row>
     <row r="2837" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2837" s="2"/>
       <c r="I2837" s="1"/>
     </row>
     <row r="2838" spans="8:9" x14ac:dyDescent="0.25">
@@ -19002,6 +18985,7 @@
       <c r="I2843" s="1"/>
     </row>
     <row r="2844" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2844" s="2"/>
       <c r="I2844" s="1"/>
     </row>
     <row r="2845" spans="8:9" x14ac:dyDescent="0.25">
@@ -19037,7 +19021,6 @@
       <c r="I2852" s="1"/>
     </row>
     <row r="2853" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2853" s="2"/>
       <c r="I2853" s="1"/>
     </row>
     <row r="2854" spans="8:9" x14ac:dyDescent="0.25">
@@ -19161,7 +19144,6 @@
       <c r="I2883" s="1"/>
     </row>
     <row r="2884" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2884" s="2"/>
       <c r="I2884" s="1"/>
     </row>
     <row r="2885" spans="8:9" x14ac:dyDescent="0.25">
@@ -19173,6 +19155,7 @@
       <c r="I2886" s="1"/>
     </row>
     <row r="2887" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2887" s="2"/>
       <c r="I2887" s="1"/>
     </row>
     <row r="2888" spans="8:9" x14ac:dyDescent="0.25">
@@ -19196,7 +19179,6 @@
       <c r="I2892" s="1"/>
     </row>
     <row r="2893" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2893" s="2"/>
       <c r="I2893" s="1"/>
     </row>
     <row r="2894" spans="8:9" x14ac:dyDescent="0.25">
@@ -19208,6 +19190,7 @@
       <c r="I2895" s="1"/>
     </row>
     <row r="2896" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2896" s="2"/>
       <c r="I2896" s="1"/>
     </row>
     <row r="2897" spans="8:9" x14ac:dyDescent="0.25">
@@ -19215,9 +19198,11 @@
       <c r="I2897" s="1"/>
     </row>
     <row r="2898" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2898" s="2"/>
       <c r="I2898" s="1"/>
     </row>
     <row r="2899" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2899" s="2"/>
       <c r="I2899" s="1"/>
     </row>
     <row r="2900" spans="8:9" x14ac:dyDescent="0.25">
@@ -19249,6 +19234,7 @@
       <c r="I2906" s="1"/>
     </row>
     <row r="2907" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2907" s="2"/>
       <c r="I2907" s="1"/>
     </row>
     <row r="2908" spans="8:9" x14ac:dyDescent="0.25">
@@ -19264,6 +19250,7 @@
       <c r="I2910" s="1"/>
     </row>
     <row r="2911" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2911" s="2"/>
       <c r="I2911" s="1"/>
     </row>
     <row r="2912" spans="8:9" x14ac:dyDescent="0.25">
@@ -19303,6 +19290,7 @@
       <c r="I2920" s="1"/>
     </row>
     <row r="2921" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2921" s="2"/>
       <c r="I2921" s="1"/>
     </row>
     <row r="2922" spans="8:9" x14ac:dyDescent="0.25">
@@ -19314,6 +19302,7 @@
       <c r="I2923" s="1"/>
     </row>
     <row r="2924" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2924" s="2"/>
       <c r="I2924" s="1"/>
     </row>
     <row r="2925" spans="8:9" x14ac:dyDescent="0.25">
@@ -19321,7 +19310,6 @@
       <c r="I2925" s="1"/>
     </row>
     <row r="2926" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2926" s="2"/>
       <c r="I2926" s="1"/>
     </row>
     <row r="2927" spans="8:9" x14ac:dyDescent="0.25">
@@ -19345,7 +19333,6 @@
       <c r="I2931" s="1"/>
     </row>
     <row r="2932" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H2932" s="2"/>
       <c r="I2932" s="1"/>
     </row>
     <row r="2933" spans="8:9" x14ac:dyDescent="0.25">
@@ -19457,6 +19444,7 @@
       <c r="I2959" s="1"/>
     </row>
     <row r="2960" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2960" s="2"/>
       <c r="I2960" s="1"/>
     </row>
     <row r="2961" spans="8:9" x14ac:dyDescent="0.25">
@@ -19540,6 +19528,7 @@
       <c r="I2980" s="1"/>
     </row>
     <row r="2981" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2981" s="2"/>
       <c r="I2981" s="1"/>
     </row>
     <row r="2982" spans="8:9" x14ac:dyDescent="0.25">
@@ -19591,6 +19580,7 @@
       <c r="I2993" s="1"/>
     </row>
     <row r="2994" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H2994" s="2"/>
       <c r="I2994" s="1"/>
     </row>
     <row r="2995" spans="8:9" x14ac:dyDescent="0.25">
@@ -19750,6 +19740,7 @@
       <c r="I3033" s="1"/>
     </row>
     <row r="3034" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3034" s="2"/>
       <c r="I3034" s="1"/>
     </row>
     <row r="3035" spans="8:9" x14ac:dyDescent="0.25">
@@ -19797,7 +19788,6 @@
       <c r="I3045" s="1"/>
     </row>
     <row r="3046" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3046" s="2"/>
       <c r="I3046" s="1"/>
     </row>
     <row r="3047" spans="8:9" x14ac:dyDescent="0.25">
@@ -19809,6 +19799,7 @@
       <c r="I3048" s="1"/>
     </row>
     <row r="3049" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3049" s="2"/>
       <c r="I3049" s="1"/>
     </row>
     <row r="3050" spans="8:9" x14ac:dyDescent="0.25">
@@ -19860,7 +19851,6 @@
       <c r="I3061" s="1"/>
     </row>
     <row r="3062" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3062" s="2"/>
       <c r="I3062" s="1"/>
     </row>
     <row r="3063" spans="8:9" x14ac:dyDescent="0.25">
@@ -19952,6 +19942,7 @@
       <c r="I3084" s="1"/>
     </row>
     <row r="3085" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3085" s="2"/>
       <c r="I3085" s="1"/>
     </row>
     <row r="3086" spans="8:9" x14ac:dyDescent="0.25">
@@ -19995,7 +19986,6 @@
       <c r="I3095" s="1"/>
     </row>
     <row r="3096" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3096" s="2"/>
       <c r="I3096" s="1"/>
     </row>
     <row r="3097" spans="8:9" x14ac:dyDescent="0.25">
@@ -20071,6 +20061,7 @@
       <c r="I3114" s="1"/>
     </row>
     <row r="3115" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3115" s="2"/>
       <c r="I3115" s="1"/>
     </row>
     <row r="3116" spans="8:9" x14ac:dyDescent="0.25">
@@ -20118,7 +20109,6 @@
       <c r="I3126" s="1"/>
     </row>
     <row r="3127" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3127" s="2"/>
       <c r="I3127" s="1"/>
     </row>
     <row r="3128" spans="8:9" x14ac:dyDescent="0.25">
@@ -20202,6 +20192,7 @@
       <c r="I3147" s="1"/>
     </row>
     <row r="3148" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3148" s="2"/>
       <c r="I3148" s="1"/>
     </row>
     <row r="3149" spans="8:9" x14ac:dyDescent="0.25">
@@ -20221,6 +20212,7 @@
       <c r="I3152" s="1"/>
     </row>
     <row r="3153" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3153" s="2"/>
       <c r="I3153" s="1"/>
     </row>
     <row r="3154" spans="8:9" x14ac:dyDescent="0.25">
@@ -20235,7 +20227,6 @@
       <c r="I3156" s="1"/>
     </row>
     <row r="3157" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3157" s="2"/>
       <c r="I3157" s="1"/>
     </row>
     <row r="3158" spans="8:9" x14ac:dyDescent="0.25">
@@ -20255,6 +20246,7 @@
       <c r="I3161" s="1"/>
     </row>
     <row r="3162" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3162" s="2"/>
       <c r="I3162" s="1"/>
     </row>
     <row r="3163" spans="8:9" x14ac:dyDescent="0.25">
@@ -20262,11 +20254,9 @@
       <c r="I3163" s="1"/>
     </row>
     <row r="3164" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3164" s="2"/>
       <c r="I3164" s="1"/>
     </row>
     <row r="3165" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3165" s="2"/>
       <c r="I3165" s="1"/>
     </row>
     <row r="3166" spans="8:9" x14ac:dyDescent="0.25">
@@ -20274,7 +20264,6 @@
       <c r="I3166" s="1"/>
     </row>
     <row r="3167" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3167" s="2"/>
       <c r="I3167" s="1"/>
     </row>
     <row r="3168" spans="8:9" x14ac:dyDescent="0.25">
@@ -20294,6 +20283,7 @@
       <c r="I3171" s="1"/>
     </row>
     <row r="3172" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3172" s="2"/>
       <c r="I3172" s="1"/>
     </row>
     <row r="3173" spans="8:9" x14ac:dyDescent="0.25">
@@ -20541,7 +20531,6 @@
       <c r="I3233" s="1"/>
     </row>
     <row r="3234" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3234" s="2"/>
       <c r="I3234" s="1"/>
     </row>
     <row r="3235" spans="8:9" x14ac:dyDescent="0.25">
@@ -20797,7 +20786,6 @@
       <c r="I3297" s="1"/>
     </row>
     <row r="3298" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3298" s="2"/>
       <c r="I3298" s="1"/>
     </row>
     <row r="3299" spans="8:9" x14ac:dyDescent="0.25">
@@ -20813,6 +20801,7 @@
       <c r="I3301" s="1"/>
     </row>
     <row r="3302" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3302" s="2"/>
       <c r="I3302" s="1"/>
     </row>
     <row r="3303" spans="8:9" x14ac:dyDescent="0.25">
@@ -20844,7 +20833,6 @@
       <c r="I3309" s="1"/>
     </row>
     <row r="3310" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3310" s="2"/>
       <c r="I3310" s="1"/>
     </row>
     <row r="3311" spans="8:9" x14ac:dyDescent="0.25">
@@ -20880,7 +20868,6 @@
       <c r="I3318" s="1"/>
     </row>
     <row r="3319" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3319" s="2"/>
       <c r="I3319" s="1"/>
     </row>
     <row r="3320" spans="8:9" x14ac:dyDescent="0.25">
@@ -20952,6 +20939,7 @@
       <c r="I3336" s="1"/>
     </row>
     <row r="3337" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3337" s="2"/>
       <c r="I3337" s="1"/>
     </row>
     <row r="3338" spans="8:9" x14ac:dyDescent="0.25">
@@ -21075,6 +21063,7 @@
       <c r="I3367" s="1"/>
     </row>
     <row r="3368" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3368" s="2"/>
       <c r="I3368" s="1"/>
     </row>
     <row r="3369" spans="8:9" x14ac:dyDescent="0.25">
@@ -21102,7 +21091,6 @@
       <c r="I3374" s="1"/>
     </row>
     <row r="3375" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3375" s="2"/>
       <c r="I3375" s="1"/>
     </row>
     <row r="3376" spans="8:9" x14ac:dyDescent="0.25">
@@ -21110,6 +21098,7 @@
       <c r="I3376" s="1"/>
     </row>
     <row r="3377" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3377" s="2"/>
       <c r="I3377" s="1"/>
     </row>
     <row r="3378" spans="8:9" x14ac:dyDescent="0.25">
@@ -21217,7 +21206,6 @@
       <c r="I3403" s="1"/>
     </row>
     <row r="3404" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3404" s="2"/>
       <c r="I3404" s="1"/>
     </row>
     <row r="3405" spans="8:9" x14ac:dyDescent="0.25">
@@ -21241,10 +21229,10 @@
       <c r="I3409" s="1"/>
     </row>
     <row r="3410" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3410" s="2"/>
       <c r="I3410" s="1"/>
     </row>
     <row r="3411" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3411" s="2"/>
       <c r="I3411" s="1"/>
     </row>
     <row r="3412" spans="8:9" x14ac:dyDescent="0.25">
@@ -21264,6 +21252,7 @@
       <c r="I3415" s="1"/>
     </row>
     <row r="3416" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3416" s="2"/>
       <c r="I3416" s="1"/>
     </row>
     <row r="3417" spans="8:9" x14ac:dyDescent="0.25">
@@ -21391,7 +21380,6 @@
       <c r="I3447" s="1"/>
     </row>
     <row r="3448" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3448" s="2"/>
       <c r="I3448" s="1"/>
     </row>
     <row r="3449" spans="8:9" x14ac:dyDescent="0.25">
@@ -21711,7 +21699,6 @@
       <c r="I3527" s="1"/>
     </row>
     <row r="3528" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3528" s="2"/>
       <c r="I3528" s="1"/>
     </row>
     <row r="3529" spans="8:9" x14ac:dyDescent="0.25">
@@ -21719,6 +21706,7 @@
       <c r="I3529" s="1"/>
     </row>
     <row r="3530" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3530" s="2"/>
       <c r="I3530" s="1"/>
     </row>
     <row r="3531" spans="8:9" x14ac:dyDescent="0.25">
@@ -21782,6 +21770,7 @@
       <c r="I3545" s="1"/>
     </row>
     <row r="3546" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3546" s="2"/>
       <c r="I3546" s="1"/>
     </row>
     <row r="3547" spans="8:9" x14ac:dyDescent="0.25">
@@ -21829,7 +21818,6 @@
       <c r="I3557" s="1"/>
     </row>
     <row r="3558" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3558" s="2"/>
       <c r="I3558" s="1"/>
     </row>
     <row r="3559" spans="8:9" x14ac:dyDescent="0.25">
@@ -21905,7 +21893,6 @@
       <c r="I3576" s="1"/>
     </row>
     <row r="3577" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3577" s="2"/>
       <c r="I3577" s="1"/>
     </row>
     <row r="3578" spans="8:9" x14ac:dyDescent="0.25">
@@ -21917,6 +21904,7 @@
       <c r="I3579" s="1"/>
     </row>
     <row r="3580" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3580" s="2"/>
       <c r="I3580" s="1"/>
     </row>
     <row r="3581" spans="8:9" x14ac:dyDescent="0.25">
@@ -22040,6 +22028,7 @@
       <c r="I3610" s="1"/>
     </row>
     <row r="3611" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3611" s="2"/>
       <c r="I3611" s="1"/>
     </row>
     <row r="3612" spans="8:9" x14ac:dyDescent="0.25">
@@ -22075,7 +22064,6 @@
       <c r="I3619" s="1"/>
     </row>
     <row r="3620" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3620" s="2"/>
       <c r="I3620" s="1"/>
     </row>
     <row r="3621" spans="8:9" x14ac:dyDescent="0.25">
@@ -22155,9 +22143,11 @@
       <c r="I3639" s="1"/>
     </row>
     <row r="3640" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3640" s="2"/>
       <c r="I3640" s="1"/>
     </row>
     <row r="3641" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3641" s="2"/>
       <c r="I3641" s="1"/>
     </row>
     <row r="3642" spans="8:9" x14ac:dyDescent="0.25">
@@ -22185,9 +22175,11 @@
       <c r="I3647" s="1"/>
     </row>
     <row r="3648" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3648" s="2"/>
       <c r="I3648" s="1"/>
     </row>
     <row r="3649" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3649" s="2"/>
       <c r="I3649" s="1"/>
     </row>
     <row r="3650" spans="8:9" x14ac:dyDescent="0.25">
@@ -22195,10 +22187,10 @@
       <c r="I3650" s="1"/>
     </row>
     <row r="3651" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3651" s="2"/>
       <c r="I3651" s="1"/>
     </row>
     <row r="3652" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3652" s="2"/>
       <c r="I3652" s="1"/>
     </row>
     <row r="3653" spans="8:9" x14ac:dyDescent="0.25">
@@ -22210,7 +22202,6 @@
       <c r="I3654" s="1"/>
     </row>
     <row r="3655" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3655" s="2"/>
       <c r="I3655" s="1"/>
     </row>
     <row r="3656" spans="8:9" x14ac:dyDescent="0.25">
@@ -22238,7 +22229,6 @@
       <c r="I3661" s="1"/>
     </row>
     <row r="3662" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3662" s="2"/>
       <c r="I3662" s="1"/>
     </row>
     <row r="3663" spans="8:9" x14ac:dyDescent="0.25">
@@ -22462,6 +22452,7 @@
       <c r="I3717" s="1"/>
     </row>
     <row r="3718" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3718" s="2"/>
       <c r="I3718" s="1"/>
     </row>
     <row r="3719" spans="8:9" x14ac:dyDescent="0.25">
@@ -22717,6 +22708,7 @@
       <c r="I3781" s="1"/>
     </row>
     <row r="3782" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3782" s="2"/>
       <c r="I3782" s="1"/>
     </row>
     <row r="3783" spans="8:9" x14ac:dyDescent="0.25">
@@ -22764,6 +22756,7 @@
       <c r="I3793" s="1"/>
     </row>
     <row r="3794" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3794" s="2"/>
       <c r="I3794" s="1"/>
     </row>
     <row r="3795" spans="8:9" x14ac:dyDescent="0.25">
@@ -22771,7 +22764,6 @@
       <c r="I3795" s="1"/>
     </row>
     <row r="3796" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3796" s="2"/>
       <c r="I3796" s="1"/>
     </row>
     <row r="3797" spans="8:9" x14ac:dyDescent="0.25">
@@ -23022,6 +23014,7 @@
       <c r="I3858" s="1"/>
     </row>
     <row r="3859" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3859" s="2"/>
       <c r="I3859" s="1"/>
     </row>
     <row r="3860" spans="8:9" x14ac:dyDescent="0.25">
@@ -23093,7 +23086,6 @@
       <c r="I3876" s="1"/>
     </row>
     <row r="3877" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3877" s="2"/>
       <c r="I3877" s="1"/>
     </row>
     <row r="3878" spans="8:9" x14ac:dyDescent="0.25">
@@ -23137,6 +23129,7 @@
       <c r="I3887" s="1"/>
     </row>
     <row r="3888" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3888" s="2"/>
       <c r="I3888" s="1"/>
     </row>
     <row r="3889" spans="8:9" x14ac:dyDescent="0.25">
@@ -23164,6 +23157,7 @@
       <c r="I3894" s="1"/>
     </row>
     <row r="3895" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3895" s="2"/>
       <c r="I3895" s="1"/>
     </row>
     <row r="3896" spans="8:9" x14ac:dyDescent="0.25">
@@ -23235,11 +23229,9 @@
       <c r="I3912" s="1"/>
     </row>
     <row r="3913" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3913" s="2"/>
       <c r="I3913" s="1"/>
     </row>
     <row r="3914" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3914" s="2"/>
       <c r="I3914" s="1"/>
     </row>
     <row r="3915" spans="8:9" x14ac:dyDescent="0.25">
@@ -23287,7 +23279,6 @@
       <c r="I3925" s="1"/>
     </row>
     <row r="3926" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3926" s="2"/>
       <c r="I3926" s="1"/>
     </row>
     <row r="3927" spans="8:9" x14ac:dyDescent="0.25">
@@ -23311,10 +23302,10 @@
       <c r="I3931" s="1"/>
     </row>
     <row r="3932" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H3932" s="2"/>
       <c r="I3932" s="1"/>
     </row>
     <row r="3933" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3933" s="2"/>
       <c r="I3933" s="1"/>
     </row>
     <row r="3934" spans="8:9" x14ac:dyDescent="0.25">
@@ -23630,6 +23621,7 @@
       <c r="I4011" s="1"/>
     </row>
     <row r="4012" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4012" s="2"/>
       <c r="I4012" s="1"/>
     </row>
     <row r="4013" spans="8:9" x14ac:dyDescent="0.25">
@@ -23653,7 +23645,6 @@
       <c r="I4017" s="1"/>
     </row>
     <row r="4018" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4018" s="2"/>
       <c r="I4018" s="1"/>
     </row>
     <row r="4019" spans="8:9" x14ac:dyDescent="0.25">
@@ -23697,7 +23688,6 @@
       <c r="I4028" s="1"/>
     </row>
     <row r="4029" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4029" s="2"/>
       <c r="I4029" s="1"/>
     </row>
     <row r="4030" spans="8:9" x14ac:dyDescent="0.25">
@@ -23749,6 +23739,7 @@
       <c r="I4041" s="1"/>
     </row>
     <row r="4042" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4042" s="2"/>
       <c r="I4042" s="1"/>
     </row>
     <row r="4043" spans="8:9" x14ac:dyDescent="0.25">
@@ -23800,7 +23791,6 @@
       <c r="I4054" s="1"/>
     </row>
     <row r="4055" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4055" s="2"/>
       <c r="I4055" s="1"/>
     </row>
     <row r="4056" spans="8:9" x14ac:dyDescent="0.25">
@@ -23824,6 +23814,7 @@
       <c r="I4060" s="1"/>
     </row>
     <row r="4061" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4061" s="2"/>
       <c r="I4061" s="1"/>
     </row>
     <row r="4062" spans="8:9" x14ac:dyDescent="0.25">
@@ -23851,7 +23842,6 @@
       <c r="I4067" s="1"/>
     </row>
     <row r="4068" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4068" s="2"/>
       <c r="I4068" s="1"/>
     </row>
     <row r="4069" spans="8:9" x14ac:dyDescent="0.25">
@@ -23995,6 +23985,7 @@
       <c r="I4103" s="1"/>
     </row>
     <row r="4104" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4104" s="2"/>
       <c r="I4104" s="1"/>
     </row>
     <row r="4105" spans="8:9" x14ac:dyDescent="0.25">
@@ -24122,6 +24113,7 @@
       <c r="I4135" s="1"/>
     </row>
     <row r="4136" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4136" s="2"/>
       <c r="I4136" s="1"/>
     </row>
     <row r="4137" spans="8:9" x14ac:dyDescent="0.25">
@@ -24133,6 +24125,7 @@
       <c r="I4138" s="1"/>
     </row>
     <row r="4139" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4139" s="2"/>
       <c r="I4139" s="1"/>
     </row>
     <row r="4140" spans="8:9" x14ac:dyDescent="0.25">
@@ -24160,6 +24153,7 @@
       <c r="I4145" s="1"/>
     </row>
     <row r="4146" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4146" s="2"/>
       <c r="I4146" s="1"/>
     </row>
     <row r="4147" spans="8:9" x14ac:dyDescent="0.25">
@@ -24207,7 +24201,6 @@
       <c r="I4157" s="1"/>
     </row>
     <row r="4158" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4158" s="2"/>
       <c r="I4158" s="1"/>
     </row>
     <row r="4159" spans="8:9" x14ac:dyDescent="0.25">
@@ -24219,7 +24212,6 @@
       <c r="I4160" s="1"/>
     </row>
     <row r="4161" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4161" s="2"/>
       <c r="I4161" s="1"/>
     </row>
     <row r="4162" spans="8:9" x14ac:dyDescent="0.25">
@@ -24343,7 +24335,6 @@
       <c r="I4191" s="1"/>
     </row>
     <row r="4192" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4192" s="2"/>
       <c r="I4192" s="1"/>
     </row>
     <row r="4193" spans="8:9" x14ac:dyDescent="0.25">
@@ -24435,7 +24426,6 @@
       <c r="I4214" s="1"/>
     </row>
     <row r="4215" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4215" s="2"/>
       <c r="I4215" s="1"/>
     </row>
     <row r="4216" spans="8:9" x14ac:dyDescent="0.25">
@@ -24695,6 +24685,7 @@
       <c r="I4279" s="1"/>
     </row>
     <row r="4280" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4280" s="2"/>
       <c r="I4280" s="1"/>
     </row>
     <row r="4281" spans="8:9" x14ac:dyDescent="0.25">
@@ -24710,7 +24701,6 @@
       <c r="I4283" s="1"/>
     </row>
     <row r="4284" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4284" s="2"/>
       <c r="I4284" s="1"/>
     </row>
     <row r="4285" spans="8:9" x14ac:dyDescent="0.25">
@@ -24722,6 +24712,7 @@
       <c r="I4286" s="1"/>
     </row>
     <row r="4287" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4287" s="2"/>
       <c r="I4287" s="1"/>
     </row>
     <row r="4288" spans="8:9" x14ac:dyDescent="0.25">
@@ -24865,7 +24856,6 @@
       <c r="I4322" s="1"/>
     </row>
     <row r="4323" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4323" s="2"/>
       <c r="I4323" s="1"/>
     </row>
     <row r="4324" spans="8:9" x14ac:dyDescent="0.25">
@@ -24917,7 +24907,6 @@
       <c r="I4335" s="1"/>
     </row>
     <row r="4336" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4336" s="2"/>
       <c r="I4336" s="1"/>
     </row>
     <row r="4337" spans="8:9" x14ac:dyDescent="0.25">
@@ -25017,6 +25006,7 @@
       <c r="I4360" s="1"/>
     </row>
     <row r="4361" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4361" s="2"/>
       <c r="I4361" s="1"/>
     </row>
     <row r="4362" spans="8:9" x14ac:dyDescent="0.25">
@@ -25072,7 +25062,6 @@
       <c r="I4374" s="1"/>
     </row>
     <row r="4375" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4375" s="2"/>
       <c r="I4375" s="1"/>
     </row>
     <row r="4376" spans="8:9" x14ac:dyDescent="0.25">
@@ -25136,7 +25125,6 @@
       <c r="I4390" s="1"/>
     </row>
     <row r="4391" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4391" s="2"/>
       <c r="I4391" s="1"/>
     </row>
     <row r="4392" spans="8:9" x14ac:dyDescent="0.25">
@@ -25160,9 +25148,11 @@
       <c r="I4396" s="1"/>
     </row>
     <row r="4397" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4397" s="2"/>
       <c r="I4397" s="1"/>
     </row>
     <row r="4398" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4398" s="2"/>
       <c r="I4398" s="1"/>
     </row>
     <row r="4399" spans="8:9" x14ac:dyDescent="0.25">
@@ -25210,6 +25200,7 @@
       <c r="I4409" s="1"/>
     </row>
     <row r="4410" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4410" s="2"/>
       <c r="I4410" s="1"/>
     </row>
     <row r="4411" spans="8:9" x14ac:dyDescent="0.25">
@@ -25217,7 +25208,6 @@
       <c r="I4411" s="1"/>
     </row>
     <row r="4412" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4412" s="2"/>
       <c r="I4412" s="1"/>
     </row>
     <row r="4413" spans="8:9" x14ac:dyDescent="0.25">
@@ -25237,6 +25227,7 @@
       <c r="I4416" s="1"/>
     </row>
     <row r="4417" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4417" s="2"/>
       <c r="I4417" s="1"/>
     </row>
     <row r="4418" spans="8:9" x14ac:dyDescent="0.25">
@@ -25264,7 +25255,6 @@
       <c r="I4423" s="1"/>
     </row>
     <row r="4424" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4424" s="2"/>
       <c r="I4424" s="1"/>
     </row>
     <row r="4425" spans="8:9" x14ac:dyDescent="0.25">
@@ -25276,7 +25266,6 @@
       <c r="I4426" s="1"/>
     </row>
     <row r="4427" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4427" s="2"/>
       <c r="I4427" s="1"/>
     </row>
     <row r="4428" spans="8:9" x14ac:dyDescent="0.25">
@@ -25360,7 +25349,6 @@
       <c r="I4447" s="1"/>
     </row>
     <row r="4448" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4448" s="2"/>
       <c r="I4448" s="1"/>
     </row>
     <row r="4449" spans="8:9" x14ac:dyDescent="0.25">
@@ -25576,6 +25564,7 @@
       <c r="I4501" s="1"/>
     </row>
     <row r="4502" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4502" s="2"/>
       <c r="I4502" s="1"/>
     </row>
     <row r="4503" spans="8:9" x14ac:dyDescent="0.25">
@@ -25619,6 +25608,7 @@
       <c r="I4512" s="1"/>
     </row>
     <row r="4513" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4513" s="2"/>
       <c r="I4513" s="1"/>
     </row>
     <row r="4514" spans="8:9" x14ac:dyDescent="0.25">
@@ -25638,7 +25628,6 @@
       <c r="I4517" s="1"/>
     </row>
     <row r="4518" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4518" s="2"/>
       <c r="I4518" s="1"/>
     </row>
     <row r="4519" spans="8:9" x14ac:dyDescent="0.25">
@@ -25718,10 +25707,10 @@
       <c r="I4537" s="1"/>
     </row>
     <row r="4538" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4538" s="2"/>
       <c r="I4538" s="1"/>
     </row>
     <row r="4539" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4539" s="2"/>
       <c r="I4539" s="1"/>
     </row>
     <row r="4540" spans="8:9" x14ac:dyDescent="0.25">
@@ -25765,7 +25754,6 @@
       <c r="I4549" s="1"/>
     </row>
     <row r="4550" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4550" s="2"/>
       <c r="I4550" s="1"/>
     </row>
     <row r="4551" spans="8:9" x14ac:dyDescent="0.25">
@@ -25773,6 +25761,7 @@
       <c r="I4551" s="1"/>
     </row>
     <row r="4552" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4552" s="2"/>
       <c r="I4552" s="1"/>
     </row>
     <row r="4553" spans="8:9" x14ac:dyDescent="0.25">
@@ -25868,7 +25857,6 @@
       <c r="I4575" s="1"/>
     </row>
     <row r="4576" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4576" s="2"/>
       <c r="I4576" s="1"/>
     </row>
     <row r="4577" spans="8:9" x14ac:dyDescent="0.25">
@@ -25916,7 +25904,6 @@
       <c r="I4587" s="1"/>
     </row>
     <row r="4588" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4588" s="2"/>
       <c r="I4588" s="1"/>
     </row>
     <row r="4589" spans="8:9" x14ac:dyDescent="0.25">
@@ -25948,7 +25935,6 @@
       <c r="I4595" s="1"/>
     </row>
     <row r="4596" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4596" s="2"/>
       <c r="I4596" s="1"/>
     </row>
     <row r="4597" spans="8:9" x14ac:dyDescent="0.25">
@@ -26080,7 +26066,6 @@
       <c r="I4628" s="1"/>
     </row>
     <row r="4629" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4629" s="2"/>
       <c r="I4629" s="1"/>
     </row>
     <row r="4630" spans="8:9" x14ac:dyDescent="0.25">
@@ -26132,6 +26117,7 @@
       <c r="I4641" s="1"/>
     </row>
     <row r="4642" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4642" s="2"/>
       <c r="I4642" s="1"/>
     </row>
     <row r="4643" spans="8:9" x14ac:dyDescent="0.25">
@@ -26143,6 +26129,7 @@
       <c r="I4644" s="1"/>
     </row>
     <row r="4645" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4645" s="2"/>
       <c r="I4645" s="1"/>
     </row>
     <row r="4646" spans="8:9" x14ac:dyDescent="0.25">
@@ -26266,6 +26253,7 @@
       <c r="I4675" s="1"/>
     </row>
     <row r="4676" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4676" s="2"/>
       <c r="I4676" s="1"/>
     </row>
     <row r="4677" spans="8:9" x14ac:dyDescent="0.25">
@@ -26297,7 +26285,6 @@
       <c r="I4683" s="1"/>
     </row>
     <row r="4684" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4684" s="2"/>
       <c r="I4684" s="1"/>
     </row>
     <row r="4685" spans="8:9" x14ac:dyDescent="0.25">
@@ -26357,6 +26344,7 @@
       <c r="I4698" s="1"/>
     </row>
     <row r="4699" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4699" s="2"/>
       <c r="I4699" s="1"/>
     </row>
     <row r="4700" spans="8:9" x14ac:dyDescent="0.25">
@@ -26628,10 +26616,10 @@
       <c r="I4766" s="1"/>
     </row>
     <row r="4767" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4767" s="2"/>
       <c r="I4767" s="1"/>
     </row>
     <row r="4768" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4768" s="2"/>
       <c r="I4768" s="1"/>
     </row>
     <row r="4769" spans="8:9" x14ac:dyDescent="0.25">
@@ -26659,7 +26647,6 @@
       <c r="I4774" s="1"/>
     </row>
     <row r="4775" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4775" s="2"/>
       <c r="I4775" s="1"/>
     </row>
     <row r="4776" spans="8:9" x14ac:dyDescent="0.25">
@@ -26667,7 +26654,6 @@
       <c r="I4776" s="1"/>
     </row>
     <row r="4777" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4777" s="2"/>
       <c r="I4777" s="1"/>
     </row>
     <row r="4778" spans="8:9" x14ac:dyDescent="0.25">
@@ -26787,6 +26773,7 @@
       <c r="I4806" s="1"/>
     </row>
     <row r="4807" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4807" s="2"/>
       <c r="I4807" s="1"/>
     </row>
     <row r="4808" spans="8:9" x14ac:dyDescent="0.25">
@@ -26838,6 +26825,7 @@
       <c r="I4819" s="1"/>
     </row>
     <row r="4820" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4820" s="2"/>
       <c r="I4820" s="1"/>
     </row>
     <row r="4821" spans="8:9" x14ac:dyDescent="0.25">
@@ -26853,7 +26841,6 @@
       <c r="I4823" s="1"/>
     </row>
     <row r="4824" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4824" s="2"/>
       <c r="I4824" s="1"/>
     </row>
     <row r="4825" spans="8:9" x14ac:dyDescent="0.25">
@@ -26893,7 +26880,6 @@
       <c r="I4833" s="1"/>
     </row>
     <row r="4834" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4834" s="2"/>
       <c r="I4834" s="1"/>
     </row>
     <row r="4835" spans="8:9" x14ac:dyDescent="0.25">
@@ -26993,6 +26979,7 @@
       <c r="I4858" s="1"/>
     </row>
     <row r="4859" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4859" s="2"/>
       <c r="I4859" s="1"/>
     </row>
     <row r="4860" spans="8:9" x14ac:dyDescent="0.25">
@@ -27056,6 +27043,7 @@
       <c r="I4874" s="1"/>
     </row>
     <row r="4875" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4875" s="2"/>
       <c r="I4875" s="1"/>
     </row>
     <row r="4876" spans="8:9" x14ac:dyDescent="0.25">
@@ -27139,6 +27127,7 @@
       <c r="I4895" s="1"/>
     </row>
     <row r="4896" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4896" s="2"/>
       <c r="I4896" s="1"/>
     </row>
     <row r="4897" spans="8:9" x14ac:dyDescent="0.25">
@@ -27186,6 +27175,7 @@
       <c r="I4907" s="1"/>
     </row>
     <row r="4908" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4908" s="2"/>
       <c r="I4908" s="1"/>
     </row>
     <row r="4909" spans="8:9" x14ac:dyDescent="0.25">
@@ -27197,6 +27187,7 @@
       <c r="I4910" s="1"/>
     </row>
     <row r="4911" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4911" s="2"/>
       <c r="I4911" s="1"/>
     </row>
     <row r="4912" spans="8:9" x14ac:dyDescent="0.25">
@@ -27280,10 +27271,10 @@
       <c r="I4931" s="1"/>
     </row>
     <row r="4932" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H4932" s="2"/>
       <c r="I4932" s="1"/>
     </row>
     <row r="4933" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4933" s="2"/>
       <c r="I4933" s="1"/>
     </row>
     <row r="4934" spans="8:9" x14ac:dyDescent="0.25">
@@ -27303,15 +27294,12 @@
       <c r="I4937" s="1"/>
     </row>
     <row r="4938" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4938" s="2"/>
       <c r="I4938" s="1"/>
     </row>
     <row r="4939" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4939" s="2"/>
       <c r="I4939" s="1"/>
     </row>
     <row r="4940" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4940" s="2"/>
       <c r="I4940" s="1"/>
     </row>
     <row r="4941" spans="8:9" x14ac:dyDescent="0.25">
@@ -27327,7 +27315,6 @@
       <c r="I4943" s="1"/>
     </row>
     <row r="4944" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4944" s="2"/>
       <c r="I4944" s="1"/>
     </row>
     <row r="4945" spans="8:9" x14ac:dyDescent="0.25">
@@ -27559,6 +27546,7 @@
       <c r="I5001" s="1"/>
     </row>
     <row r="5002" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5002" s="2"/>
       <c r="I5002" s="1"/>
     </row>
     <row r="5003" spans="8:9" x14ac:dyDescent="0.25">
@@ -27638,6 +27626,7 @@
       <c r="I5021" s="1"/>
     </row>
     <row r="5022" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5022" s="2"/>
       <c r="I5022" s="1"/>
     </row>
     <row r="5023" spans="8:9" x14ac:dyDescent="0.25">
@@ -27673,7 +27662,6 @@
       <c r="I5030" s="1"/>
     </row>
     <row r="5031" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5031" s="2"/>
       <c r="I5031" s="1"/>
     </row>
     <row r="5032" spans="8:9" x14ac:dyDescent="0.25">
@@ -27748,7 +27736,6 @@
       <c r="I5049" s="1"/>
     </row>
     <row r="5050" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5050" s="2"/>
       <c r="I5050" s="1"/>
     </row>
     <row r="5051" spans="8:9" x14ac:dyDescent="0.25">
@@ -27788,6 +27775,7 @@
       <c r="I5059" s="1"/>
     </row>
     <row r="5060" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5060" s="2"/>
       <c r="I5060" s="1"/>
     </row>
     <row r="5061" spans="8:9" x14ac:dyDescent="0.25">
@@ -27795,7 +27783,6 @@
       <c r="I5061" s="1"/>
     </row>
     <row r="5062" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5062" s="2"/>
       <c r="I5062" s="1"/>
     </row>
     <row r="5063" spans="8:9" x14ac:dyDescent="0.25">
@@ -27815,7 +27802,6 @@
       <c r="I5066" s="1"/>
     </row>
     <row r="5067" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5067" s="2"/>
       <c r="I5067" s="1"/>
     </row>
     <row r="5068" spans="8:9" x14ac:dyDescent="0.25">
@@ -27835,6 +27821,7 @@
       <c r="I5071" s="1"/>
     </row>
     <row r="5072" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5072" s="2"/>
       <c r="I5072" s="1"/>
     </row>
     <row r="5073" spans="8:9" x14ac:dyDescent="0.25">
@@ -27866,6 +27853,7 @@
       <c r="I5079" s="1"/>
     </row>
     <row r="5080" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5080" s="2"/>
       <c r="I5080" s="1"/>
     </row>
     <row r="5081" spans="8:9" x14ac:dyDescent="0.25">
@@ -27905,7 +27893,6 @@
       <c r="I5089" s="1"/>
     </row>
     <row r="5090" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5090" s="2"/>
       <c r="I5090" s="1"/>
     </row>
     <row r="5091" spans="8:9" x14ac:dyDescent="0.25">
@@ -27997,6 +27984,7 @@
       <c r="I5112" s="1"/>
     </row>
     <row r="5113" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5113" s="2"/>
       <c r="I5113" s="1"/>
     </row>
     <row r="5114" spans="8:9" x14ac:dyDescent="0.25">
@@ -28168,7 +28156,6 @@
       <c r="I5155" s="1"/>
     </row>
     <row r="5156" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5156" s="2"/>
       <c r="I5156" s="1"/>
     </row>
     <row r="5157" spans="8:9" x14ac:dyDescent="0.25">
@@ -28216,6 +28203,7 @@
       <c r="I5167" s="1"/>
     </row>
     <row r="5168" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5168" s="2"/>
       <c r="I5168" s="1"/>
     </row>
     <row r="5169" spans="8:9" x14ac:dyDescent="0.25">
@@ -28323,7 +28311,6 @@
       <c r="I5194" s="1"/>
     </row>
     <row r="5195" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5195" s="2"/>
       <c r="I5195" s="1"/>
     </row>
     <row r="5196" spans="8:9" x14ac:dyDescent="0.25">
@@ -28363,11 +28350,9 @@
       <c r="I5204" s="1"/>
     </row>
     <row r="5205" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5205" s="2"/>
       <c r="I5205" s="1"/>
     </row>
     <row r="5206" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5206" s="2"/>
       <c r="I5206" s="1"/>
     </row>
     <row r="5207" spans="8:9" x14ac:dyDescent="0.25">
@@ -28479,7 +28464,6 @@
       <c r="I5233" s="1"/>
     </row>
     <row r="5234" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5234" s="2"/>
       <c r="I5234" s="1"/>
     </row>
     <row r="5235" spans="8:9" x14ac:dyDescent="0.25">
@@ -28547,6 +28531,7 @@
       <c r="I5250" s="1"/>
     </row>
     <row r="5251" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5251" s="2"/>
       <c r="I5251" s="1"/>
     </row>
     <row r="5252" spans="8:9" x14ac:dyDescent="0.25">
@@ -28554,7 +28539,6 @@
       <c r="I5252" s="1"/>
     </row>
     <row r="5253" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5253" s="2"/>
       <c r="I5253" s="1"/>
     </row>
     <row r="5254" spans="8:9" x14ac:dyDescent="0.25">
@@ -28578,6 +28562,7 @@
       <c r="I5258" s="1"/>
     </row>
     <row r="5259" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5259" s="2"/>
       <c r="I5259" s="1"/>
     </row>
     <row r="5260" spans="8:9" x14ac:dyDescent="0.25">
@@ -28585,6 +28570,7 @@
       <c r="I5260" s="1"/>
     </row>
     <row r="5261" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5261" s="2"/>
       <c r="I5261" s="1"/>
     </row>
     <row r="5262" spans="8:9" x14ac:dyDescent="0.25">
@@ -28604,7 +28590,6 @@
       <c r="I5265" s="1"/>
     </row>
     <row r="5266" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5266" s="2"/>
       <c r="I5266" s="1"/>
     </row>
     <row r="5267" spans="8:9" x14ac:dyDescent="0.25">
@@ -28648,11 +28633,9 @@
       <c r="I5276" s="1"/>
     </row>
     <row r="5277" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5277" s="2"/>
       <c r="I5277" s="1"/>
     </row>
     <row r="5278" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5278" s="2"/>
       <c r="I5278" s="1"/>
     </row>
     <row r="5279" spans="8:9" x14ac:dyDescent="0.25">
@@ -28672,7 +28655,6 @@
       <c r="I5282" s="1"/>
     </row>
     <row r="5283" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5283" s="2"/>
       <c r="I5283" s="1"/>
     </row>
     <row r="5284" spans="8:9" x14ac:dyDescent="0.25">
@@ -28748,11 +28730,9 @@
       <c r="I5301" s="1"/>
     </row>
     <row r="5302" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5302" s="2"/>
       <c r="I5302" s="1"/>
     </row>
     <row r="5303" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5303" s="2"/>
       <c r="I5303" s="1"/>
     </row>
     <row r="5304" spans="8:9" x14ac:dyDescent="0.25">
@@ -28772,6 +28752,7 @@
       <c r="I5307" s="1"/>
     </row>
     <row r="5308" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5308" s="2"/>
       <c r="I5308" s="1"/>
     </row>
     <row r="5309" spans="8:9" x14ac:dyDescent="0.25">
@@ -28811,10 +28792,10 @@
       <c r="I5317" s="1"/>
     </row>
     <row r="5318" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5318" s="2"/>
       <c r="I5318" s="1"/>
     </row>
     <row r="5319" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5319" s="2"/>
       <c r="I5319" s="1"/>
     </row>
     <row r="5320" spans="8:9" x14ac:dyDescent="0.25">
@@ -28834,7 +28815,6 @@
       <c r="I5323" s="1"/>
     </row>
     <row r="5324" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5324" s="2"/>
       <c r="I5324" s="1"/>
     </row>
     <row r="5325" spans="8:9" x14ac:dyDescent="0.25">
@@ -28866,7 +28846,6 @@
       <c r="I5331" s="1"/>
     </row>
     <row r="5332" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5332" s="2"/>
       <c r="I5332" s="1"/>
     </row>
     <row r="5333" spans="8:9" x14ac:dyDescent="0.25">
@@ -28970,7 +28949,6 @@
       <c r="I5357" s="1"/>
     </row>
     <row r="5358" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5358" s="2"/>
       <c r="I5358" s="1"/>
     </row>
     <row r="5359" spans="8:9" x14ac:dyDescent="0.25">
@@ -29010,7 +28988,6 @@
       <c r="I5367" s="1"/>
     </row>
     <row r="5368" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5368" s="2"/>
       <c r="I5368" s="1"/>
     </row>
     <row r="5369" spans="8:9" x14ac:dyDescent="0.25">
@@ -29026,7 +29003,6 @@
       <c r="I5371" s="1"/>
     </row>
     <row r="5372" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5372" s="2"/>
       <c r="I5372" s="1"/>
     </row>
     <row r="5373" spans="8:9" x14ac:dyDescent="0.25">
@@ -29042,7 +29018,6 @@
       <c r="I5375" s="1"/>
     </row>
     <row r="5376" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5376" s="2"/>
       <c r="I5376" s="1"/>
     </row>
     <row r="5377" spans="8:9" x14ac:dyDescent="0.25">
@@ -29066,7 +29041,6 @@
       <c r="I5381" s="1"/>
     </row>
     <row r="5382" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5382" s="2"/>
       <c r="I5382" s="1"/>
     </row>
     <row r="5383" spans="8:9" x14ac:dyDescent="0.25">
@@ -29098,7 +29072,6 @@
       <c r="I5389" s="1"/>
     </row>
     <row r="5390" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5390" s="2"/>
       <c r="I5390" s="1"/>
     </row>
     <row r="5391" spans="8:9" x14ac:dyDescent="0.25">
@@ -29122,7 +29095,6 @@
       <c r="I5395" s="1"/>
     </row>
     <row r="5396" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5396" s="2"/>
       <c r="I5396" s="1"/>
     </row>
     <row r="5397" spans="8:9" x14ac:dyDescent="0.25">
@@ -29194,7 +29166,6 @@
       <c r="I5413" s="1"/>
     </row>
     <row r="5414" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5414" s="2"/>
       <c r="I5414" s="1"/>
     </row>
     <row r="5415" spans="8:9" x14ac:dyDescent="0.25">
@@ -29206,6 +29177,7 @@
       <c r="I5416" s="1"/>
     </row>
     <row r="5417" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5417" s="2"/>
       <c r="I5417" s="1"/>
     </row>
     <row r="5418" spans="8:9" x14ac:dyDescent="0.25">
@@ -29225,12 +29197,15 @@
       <c r="I5421" s="1"/>
     </row>
     <row r="5422" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5422" s="2"/>
       <c r="I5422" s="1"/>
     </row>
     <row r="5423" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5423" s="2"/>
       <c r="I5423" s="1"/>
     </row>
     <row r="5424" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H5424" s="2"/>
       <c r="I5424" s="1"/>
     </row>
     <row r="5425" spans="8:9" x14ac:dyDescent="0.25">
@@ -29289,11 +29264,9 @@
       <c r="I5438" s="1"/>
     </row>
     <row r="5439" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5439" s="2"/>
       <c r="I5439" s="1"/>
     </row>
     <row r="5440" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5440" s="2"/>
       <c r="I5440" s="1"/>
     </row>
     <row r="5441" spans="8:9" x14ac:dyDescent="0.25">
@@ -29305,1920 +29278,17 @@
       <c r="I5442" s="1"/>
     </row>
     <row r="5443" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5443" s="2"/>
       <c r="I5443" s="1"/>
     </row>
     <row r="5444" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5444" s="2"/>
       <c r="I5444" s="1"/>
     </row>
     <row r="5445" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H5445" s="2"/>
       <c r="I5445" s="1"/>
     </row>
-    <row r="5446" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5446" s="2"/>
-      <c r="I5446" s="1"/>
-    </row>
-    <row r="5447" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5447" s="2"/>
-      <c r="I5447" s="1"/>
-    </row>
-    <row r="5448" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5448" s="2"/>
-      <c r="I5448" s="1"/>
-    </row>
-    <row r="5449" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5449" s="2"/>
-      <c r="I5449" s="1"/>
-    </row>
-    <row r="5450" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5450" s="2"/>
-      <c r="I5450" s="1"/>
-    </row>
-    <row r="5451" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5451" s="2"/>
-      <c r="I5451" s="1"/>
-    </row>
-    <row r="5452" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5452" s="2"/>
-      <c r="I5452" s="1"/>
-    </row>
-    <row r="5453" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5453" s="2"/>
-      <c r="I5453" s="1"/>
-    </row>
-    <row r="5454" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5454" s="2"/>
-      <c r="I5454" s="1"/>
-    </row>
-    <row r="5455" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5455" s="2"/>
-      <c r="I5455" s="1"/>
-    </row>
-    <row r="5456" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5456" s="2"/>
-      <c r="I5456" s="1"/>
-    </row>
-    <row r="5457" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5457" s="2"/>
-      <c r="I5457" s="1"/>
-    </row>
-    <row r="5458" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5458" s="2"/>
-      <c r="I5458" s="1"/>
-    </row>
-    <row r="5459" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5459" s="2"/>
-      <c r="I5459" s="1"/>
-    </row>
-    <row r="5460" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5460" s="2"/>
-      <c r="I5460" s="1"/>
-    </row>
-    <row r="5461" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5461" s="2"/>
-      <c r="I5461" s="1"/>
-    </row>
-    <row r="5462" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5462" s="2"/>
-      <c r="I5462" s="1"/>
-    </row>
-    <row r="5463" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5463" s="2"/>
-      <c r="I5463" s="1"/>
-    </row>
-    <row r="5464" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5464" s="2"/>
-      <c r="I5464" s="1"/>
-    </row>
-    <row r="5465" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5465" s="2"/>
-      <c r="I5465" s="1"/>
-    </row>
-    <row r="5466" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5466" s="2"/>
-      <c r="I5466" s="1"/>
-    </row>
-    <row r="5467" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5467" s="2"/>
-      <c r="I5467" s="1"/>
-    </row>
-    <row r="5468" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5468" s="2"/>
-      <c r="I5468" s="1"/>
-    </row>
-    <row r="5469" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5469" s="2"/>
-      <c r="I5469" s="1"/>
-    </row>
-    <row r="5470" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5470" s="2"/>
-      <c r="I5470" s="1"/>
-    </row>
-    <row r="5471" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5471" s="2"/>
-      <c r="I5471" s="1"/>
-    </row>
-    <row r="5472" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5472" s="2"/>
-      <c r="I5472" s="1"/>
-    </row>
-    <row r="5473" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5473" s="2"/>
-      <c r="I5473" s="1"/>
-    </row>
-    <row r="5474" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5474" s="2"/>
-      <c r="I5474" s="1"/>
-    </row>
-    <row r="5475" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5475" s="2"/>
-      <c r="I5475" s="1"/>
-    </row>
-    <row r="5476" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5476" s="2"/>
-      <c r="I5476" s="1"/>
-    </row>
-    <row r="5477" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5477" s="2"/>
-      <c r="I5477" s="1"/>
-    </row>
-    <row r="5478" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5478" s="2"/>
-      <c r="I5478" s="1"/>
-    </row>
-    <row r="5479" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5479" s="2"/>
-      <c r="I5479" s="1"/>
-    </row>
-    <row r="5480" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5480" s="2"/>
-      <c r="I5480" s="1"/>
-    </row>
-    <row r="5481" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5481" s="2"/>
-      <c r="I5481" s="1"/>
-    </row>
-    <row r="5482" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5482" s="2"/>
-      <c r="I5482" s="1"/>
-    </row>
-    <row r="5483" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5483" s="2"/>
-      <c r="I5483" s="1"/>
-    </row>
-    <row r="5484" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5484" s="2"/>
-      <c r="I5484" s="1"/>
-    </row>
-    <row r="5485" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5485" s="2"/>
-      <c r="I5485" s="1"/>
-    </row>
-    <row r="5486" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5486" s="2"/>
-      <c r="I5486" s="1"/>
-    </row>
-    <row r="5487" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5487" s="2"/>
-      <c r="I5487" s="1"/>
-    </row>
-    <row r="5488" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5488" s="2"/>
-      <c r="I5488" s="1"/>
-    </row>
-    <row r="5489" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5489" s="2"/>
-      <c r="I5489" s="1"/>
-    </row>
-    <row r="5490" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5490" s="2"/>
-      <c r="I5490" s="1"/>
-    </row>
-    <row r="5491" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5491" s="2"/>
-      <c r="I5491" s="1"/>
-    </row>
-    <row r="5492" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5492" s="2"/>
-      <c r="I5492" s="1"/>
-    </row>
-    <row r="5493" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5493" s="2"/>
-      <c r="I5493" s="1"/>
-    </row>
-    <row r="5494" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5494" s="2"/>
-      <c r="I5494" s="1"/>
-    </row>
-    <row r="5495" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5495" s="2"/>
-      <c r="I5495" s="1"/>
-    </row>
-    <row r="5496" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5496" s="2"/>
-      <c r="I5496" s="1"/>
-    </row>
-    <row r="5497" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5497" s="2"/>
-      <c r="I5497" s="1"/>
-    </row>
-    <row r="5498" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5498" s="2"/>
-      <c r="I5498" s="1"/>
-    </row>
-    <row r="5499" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5499" s="2"/>
-      <c r="I5499" s="1"/>
-    </row>
-    <row r="5500" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5500" s="2"/>
-      <c r="I5500" s="1"/>
-    </row>
-    <row r="5501" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5501" s="2"/>
-      <c r="I5501" s="1"/>
-    </row>
-    <row r="5502" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5502" s="2"/>
-      <c r="I5502" s="1"/>
-    </row>
-    <row r="5503" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5503" s="2"/>
-      <c r="I5503" s="1"/>
-    </row>
-    <row r="5504" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5504" s="2"/>
-      <c r="I5504" s="1"/>
-    </row>
-    <row r="5505" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5505" s="2"/>
-      <c r="I5505" s="1"/>
-    </row>
-    <row r="5506" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5506" s="2"/>
-      <c r="I5506" s="1"/>
-    </row>
-    <row r="5507" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5507" s="2"/>
-      <c r="I5507" s="1"/>
-    </row>
-    <row r="5508" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5508" s="2"/>
-      <c r="I5508" s="1"/>
-    </row>
-    <row r="5509" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5509" s="2"/>
-      <c r="I5509" s="1"/>
-    </row>
-    <row r="5510" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5510" s="2"/>
-      <c r="I5510" s="1"/>
-    </row>
-    <row r="5511" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5511" s="2"/>
-      <c r="I5511" s="1"/>
-    </row>
-    <row r="5512" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5512" s="2"/>
-      <c r="I5512" s="1"/>
-    </row>
-    <row r="5513" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5513" s="2"/>
-      <c r="I5513" s="1"/>
-    </row>
-    <row r="5514" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5514" s="2"/>
-      <c r="I5514" s="1"/>
-    </row>
-    <row r="5515" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5515" s="1"/>
-    </row>
-    <row r="5516" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5516" s="2"/>
-      <c r="I5516" s="1"/>
-    </row>
-    <row r="5517" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5517" s="2"/>
-      <c r="I5517" s="1"/>
-    </row>
-    <row r="5518" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5518" s="1"/>
-    </row>
-    <row r="5519" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5519" s="2"/>
-      <c r="I5519" s="1"/>
-    </row>
-    <row r="5520" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5520" s="2"/>
-      <c r="I5520" s="1"/>
-    </row>
-    <row r="5521" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5521" s="2"/>
-      <c r="I5521" s="1"/>
-    </row>
-    <row r="5522" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5522" s="2"/>
-      <c r="I5522" s="1"/>
-    </row>
-    <row r="5523" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5523" s="2"/>
-      <c r="I5523" s="1"/>
-    </row>
-    <row r="5524" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5524" s="2"/>
-      <c r="I5524" s="1"/>
-    </row>
-    <row r="5525" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5525" s="2"/>
-      <c r="I5525" s="1"/>
-    </row>
-    <row r="5526" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5526" s="2"/>
-      <c r="I5526" s="1"/>
-    </row>
-    <row r="5527" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5527" s="2"/>
-      <c r="I5527" s="1"/>
-    </row>
-    <row r="5528" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5528" s="2"/>
-      <c r="I5528" s="1"/>
-    </row>
-    <row r="5529" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5529" s="2"/>
-      <c r="I5529" s="1"/>
-    </row>
-    <row r="5530" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5530" s="2"/>
-      <c r="I5530" s="1"/>
-    </row>
-    <row r="5531" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5531" s="2"/>
-      <c r="I5531" s="1"/>
-    </row>
-    <row r="5532" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5532" s="2"/>
-      <c r="I5532" s="1"/>
-    </row>
-    <row r="5533" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5533" s="2"/>
-      <c r="I5533" s="1"/>
-    </row>
-    <row r="5534" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5534" s="1"/>
-    </row>
-    <row r="5535" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5535" s="2"/>
-      <c r="I5535" s="1"/>
-    </row>
-    <row r="5536" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5536" s="2"/>
-      <c r="I5536" s="1"/>
-    </row>
-    <row r="5537" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5537" s="2"/>
-      <c r="I5537" s="1"/>
-    </row>
-    <row r="5538" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5538" s="2"/>
-      <c r="I5538" s="1"/>
-    </row>
-    <row r="5539" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5539" s="2"/>
-      <c r="I5539" s="1"/>
-    </row>
-    <row r="5540" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5540" s="2"/>
-      <c r="I5540" s="1"/>
-    </row>
-    <row r="5541" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5541" s="2"/>
-      <c r="I5541" s="1"/>
-    </row>
-    <row r="5542" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5542" s="2"/>
-      <c r="I5542" s="1"/>
-    </row>
-    <row r="5543" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5543" s="2"/>
-      <c r="I5543" s="1"/>
-    </row>
-    <row r="5544" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5544" s="2"/>
-      <c r="I5544" s="1"/>
-    </row>
-    <row r="5545" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5545" s="2"/>
-      <c r="I5545" s="1"/>
-    </row>
-    <row r="5546" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5546" s="1"/>
-    </row>
-    <row r="5547" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5547" s="2"/>
-      <c r="I5547" s="1"/>
-    </row>
-    <row r="5548" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5548" s="2"/>
-      <c r="I5548" s="1"/>
-    </row>
-    <row r="5549" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5549" s="2"/>
-      <c r="I5549" s="1"/>
-    </row>
-    <row r="5550" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5550" s="2"/>
-      <c r="I5550" s="1"/>
-    </row>
-    <row r="5551" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5551" s="1"/>
-    </row>
-    <row r="5552" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5552" s="2"/>
-      <c r="I5552" s="1"/>
-    </row>
-    <row r="5553" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5553" s="2"/>
-      <c r="I5553" s="1"/>
-    </row>
-    <row r="5554" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5554" s="2"/>
-      <c r="I5554" s="1"/>
-    </row>
-    <row r="5555" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5555" s="2"/>
-      <c r="I5555" s="1"/>
-    </row>
-    <row r="5556" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5556" s="2"/>
-      <c r="I5556" s="1"/>
-    </row>
-    <row r="5557" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5557" s="2"/>
-      <c r="I5557" s="1"/>
-    </row>
-    <row r="5558" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5558" s="2"/>
-      <c r="I5558" s="1"/>
-    </row>
-    <row r="5559" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5559" s="2"/>
-      <c r="I5559" s="1"/>
-    </row>
-    <row r="5560" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5560" s="2"/>
-      <c r="I5560" s="1"/>
-    </row>
-    <row r="5561" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5561" s="2"/>
-      <c r="I5561" s="1"/>
-    </row>
-    <row r="5562" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5562" s="2"/>
-      <c r="I5562" s="1"/>
-    </row>
-    <row r="5563" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5563" s="2"/>
-      <c r="I5563" s="1"/>
-    </row>
-    <row r="5564" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5564" s="2"/>
-      <c r="I5564" s="1"/>
-    </row>
-    <row r="5565" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5565" s="2"/>
-      <c r="I5565" s="1"/>
-    </row>
-    <row r="5566" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5566" s="2"/>
-      <c r="I5566" s="1"/>
-    </row>
-    <row r="5567" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5567" s="2"/>
-      <c r="I5567" s="1"/>
-    </row>
-    <row r="5568" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5568" s="2"/>
-      <c r="I5568" s="1"/>
-    </row>
-    <row r="5569" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5569" s="2"/>
-      <c r="I5569" s="1"/>
-    </row>
-    <row r="5570" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5570" s="2"/>
-      <c r="I5570" s="1"/>
-    </row>
-    <row r="5571" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5571" s="2"/>
-      <c r="I5571" s="1"/>
-    </row>
-    <row r="5572" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5572" s="2"/>
-      <c r="I5572" s="1"/>
-    </row>
-    <row r="5573" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5573" s="2"/>
-      <c r="I5573" s="1"/>
-    </row>
-    <row r="5574" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5574" s="1"/>
-    </row>
-    <row r="5575" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5575" s="2"/>
-      <c r="I5575" s="1"/>
-    </row>
-    <row r="5576" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5576" s="2"/>
-      <c r="I5576" s="1"/>
-    </row>
-    <row r="5577" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5577" s="2"/>
-      <c r="I5577" s="1"/>
-    </row>
-    <row r="5578" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5578" s="2"/>
-      <c r="I5578" s="1"/>
-    </row>
-    <row r="5579" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5579" s="2"/>
-      <c r="I5579" s="1"/>
-    </row>
-    <row r="5580" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5580" s="2"/>
-      <c r="I5580" s="1"/>
-    </row>
-    <row r="5581" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5581" s="2"/>
-      <c r="I5581" s="1"/>
-    </row>
-    <row r="5582" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5582" s="2"/>
-      <c r="I5582" s="1"/>
-    </row>
-    <row r="5583" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5583" s="2"/>
-      <c r="I5583" s="1"/>
-    </row>
-    <row r="5584" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5584" s="2"/>
-      <c r="I5584" s="1"/>
-    </row>
-    <row r="5585" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5585" s="2"/>
-      <c r="I5585" s="1"/>
-    </row>
-    <row r="5586" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5586" s="2"/>
-      <c r="I5586" s="1"/>
-    </row>
-    <row r="5587" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5587" s="2"/>
-      <c r="I5587" s="1"/>
-    </row>
-    <row r="5588" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5588" s="2"/>
-      <c r="I5588" s="1"/>
-    </row>
-    <row r="5589" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5589" s="2"/>
-      <c r="I5589" s="1"/>
-    </row>
-    <row r="5590" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5590" s="2"/>
-      <c r="I5590" s="1"/>
-    </row>
-    <row r="5591" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5591" s="2"/>
-      <c r="I5591" s="1"/>
-    </row>
-    <row r="5592" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5592" s="2"/>
-      <c r="I5592" s="1"/>
-    </row>
-    <row r="5593" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5593" s="2"/>
-      <c r="I5593" s="1"/>
-    </row>
-    <row r="5594" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5594" s="2"/>
-      <c r="I5594" s="1"/>
-    </row>
-    <row r="5595" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5595" s="2"/>
-      <c r="I5595" s="1"/>
-    </row>
-    <row r="5596" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5596" s="2"/>
-      <c r="I5596" s="1"/>
-    </row>
-    <row r="5597" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5597" s="2"/>
-      <c r="I5597" s="1"/>
-    </row>
-    <row r="5598" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5598" s="2"/>
-      <c r="I5598" s="1"/>
-    </row>
-    <row r="5599" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5599" s="2"/>
-      <c r="I5599" s="1"/>
-    </row>
-    <row r="5600" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5600" s="2"/>
-      <c r="I5600" s="1"/>
-    </row>
-    <row r="5601" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5601" s="2"/>
-      <c r="I5601" s="1"/>
-    </row>
-    <row r="5602" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5602" s="2"/>
-      <c r="I5602" s="1"/>
-    </row>
-    <row r="5603" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5603" s="2"/>
-      <c r="I5603" s="1"/>
-    </row>
-    <row r="5604" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5604" s="2"/>
-      <c r="I5604" s="1"/>
-    </row>
-    <row r="5605" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5605" s="2"/>
-      <c r="I5605" s="1"/>
-    </row>
-    <row r="5606" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5606" s="2"/>
-      <c r="I5606" s="1"/>
-    </row>
-    <row r="5607" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5607" s="2"/>
-      <c r="I5607" s="1"/>
-    </row>
-    <row r="5608" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5608" s="2"/>
-      <c r="I5608" s="1"/>
-    </row>
-    <row r="5609" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5609" s="2"/>
-      <c r="I5609" s="1"/>
-    </row>
-    <row r="5610" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5610" s="2"/>
-      <c r="I5610" s="1"/>
-    </row>
-    <row r="5611" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5611" s="2"/>
-      <c r="I5611" s="1"/>
-    </row>
-    <row r="5612" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5612" s="2"/>
-      <c r="I5612" s="1"/>
-    </row>
-    <row r="5613" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5613" s="2"/>
-      <c r="I5613" s="1"/>
-    </row>
-    <row r="5614" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5614" s="2"/>
-      <c r="I5614" s="1"/>
-    </row>
-    <row r="5615" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5615" s="2"/>
-      <c r="I5615" s="1"/>
-    </row>
-    <row r="5616" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5616" s="2"/>
-      <c r="I5616" s="1"/>
-    </row>
-    <row r="5617" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5617" s="2"/>
-      <c r="I5617" s="1"/>
-    </row>
-    <row r="5618" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5618" s="2"/>
-      <c r="I5618" s="1"/>
-    </row>
-    <row r="5619" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5619" s="2"/>
-      <c r="I5619" s="1"/>
-    </row>
-    <row r="5620" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5620" s="2"/>
-      <c r="I5620" s="1"/>
-    </row>
-    <row r="5621" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5621" s="2"/>
-      <c r="I5621" s="1"/>
-    </row>
-    <row r="5622" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5622" s="2"/>
-      <c r="I5622" s="1"/>
-    </row>
-    <row r="5623" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5623" s="2"/>
-      <c r="I5623" s="1"/>
-    </row>
-    <row r="5624" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5624" s="2"/>
-      <c r="I5624" s="1"/>
-    </row>
-    <row r="5625" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5625" s="2"/>
-      <c r="I5625" s="1"/>
-    </row>
-    <row r="5626" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5626" s="2"/>
-      <c r="I5626" s="1"/>
-    </row>
-    <row r="5627" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5627" s="2"/>
-      <c r="I5627" s="1"/>
-    </row>
-    <row r="5628" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5628" s="2"/>
-      <c r="I5628" s="1"/>
-    </row>
-    <row r="5629" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5629" s="2"/>
-      <c r="I5629" s="1"/>
-    </row>
-    <row r="5630" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5630" s="2"/>
-      <c r="I5630" s="1"/>
-    </row>
-    <row r="5631" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5631" s="2"/>
-      <c r="I5631" s="1"/>
-    </row>
-    <row r="5632" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5632" s="2"/>
-      <c r="I5632" s="1"/>
-    </row>
-    <row r="5633" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5633" s="2"/>
-      <c r="I5633" s="1"/>
-    </row>
-    <row r="5634" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5634" s="2"/>
-      <c r="I5634" s="1"/>
-    </row>
-    <row r="5635" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5635" s="2"/>
-      <c r="I5635" s="1"/>
-    </row>
-    <row r="5636" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5636" s="2"/>
-      <c r="I5636" s="1"/>
-    </row>
-    <row r="5637" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5637" s="2"/>
-      <c r="I5637" s="1"/>
-    </row>
-    <row r="5638" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5638" s="2"/>
-      <c r="I5638" s="1"/>
-    </row>
-    <row r="5639" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5639" s="2"/>
-      <c r="I5639" s="1"/>
-    </row>
-    <row r="5640" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5640" s="1"/>
-    </row>
-    <row r="5641" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5641" s="2"/>
-      <c r="I5641" s="1"/>
-    </row>
-    <row r="5642" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5642" s="2"/>
-      <c r="I5642" s="1"/>
-    </row>
-    <row r="5643" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5643" s="2"/>
-      <c r="I5643" s="1"/>
-    </row>
-    <row r="5644" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5644" s="2"/>
-      <c r="I5644" s="1"/>
-    </row>
-    <row r="5645" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5645" s="2"/>
-      <c r="I5645" s="1"/>
-    </row>
-    <row r="5646" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5646" s="2"/>
-      <c r="I5646" s="1"/>
-    </row>
-    <row r="5647" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5647" s="2"/>
-      <c r="I5647" s="1"/>
-    </row>
-    <row r="5648" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5648" s="2"/>
-      <c r="I5648" s="1"/>
-    </row>
-    <row r="5649" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5649" s="2"/>
-      <c r="I5649" s="1"/>
-    </row>
-    <row r="5650" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5650" s="2"/>
-      <c r="I5650" s="1"/>
-    </row>
-    <row r="5651" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5651" s="2"/>
-      <c r="I5651" s="1"/>
-    </row>
-    <row r="5652" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5652" s="2"/>
-      <c r="I5652" s="1"/>
-    </row>
-    <row r="5653" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5653" s="2"/>
-      <c r="I5653" s="1"/>
-    </row>
-    <row r="5654" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5654" s="2"/>
-      <c r="I5654" s="1"/>
-    </row>
-    <row r="5655" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5655" s="2"/>
-      <c r="I5655" s="1"/>
-    </row>
-    <row r="5656" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5656" s="2"/>
-      <c r="I5656" s="1"/>
-    </row>
-    <row r="5657" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5657" s="2"/>
-      <c r="I5657" s="1"/>
-    </row>
-    <row r="5658" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5658" s="2"/>
-      <c r="I5658" s="1"/>
-    </row>
-    <row r="5659" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5659" s="2"/>
-      <c r="I5659" s="1"/>
-    </row>
-    <row r="5660" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5660" s="2"/>
-      <c r="I5660" s="1"/>
-    </row>
-    <row r="5661" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5661" s="2"/>
-      <c r="I5661" s="1"/>
-    </row>
-    <row r="5662" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5662" s="2"/>
-      <c r="I5662" s="1"/>
-    </row>
-    <row r="5663" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5663" s="2"/>
-      <c r="I5663" s="1"/>
-    </row>
-    <row r="5664" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5664" s="2"/>
-      <c r="I5664" s="1"/>
-    </row>
-    <row r="5665" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5665" s="2"/>
-      <c r="I5665" s="1"/>
-    </row>
-    <row r="5666" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5666" s="2"/>
-      <c r="I5666" s="1"/>
-    </row>
-    <row r="5667" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5667" s="2"/>
-      <c r="I5667" s="1"/>
-    </row>
-    <row r="5668" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5668" s="2"/>
-      <c r="I5668" s="1"/>
-    </row>
-    <row r="5669" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5669" s="2"/>
-      <c r="I5669" s="1"/>
-    </row>
-    <row r="5670" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5670" s="2"/>
-      <c r="I5670" s="1"/>
-    </row>
-    <row r="5671" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5671" s="2"/>
-      <c r="I5671" s="1"/>
-    </row>
-    <row r="5672" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5672" s="2"/>
-      <c r="I5672" s="1"/>
-    </row>
-    <row r="5673" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5673" s="2"/>
-      <c r="I5673" s="1"/>
-    </row>
-    <row r="5674" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5674" s="2"/>
-      <c r="I5674" s="1"/>
-    </row>
-    <row r="5675" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5675" s="2"/>
-      <c r="I5675" s="1"/>
-    </row>
-    <row r="5676" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5676" s="2"/>
-      <c r="I5676" s="1"/>
-    </row>
-    <row r="5677" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5677" s="2"/>
-      <c r="I5677" s="1"/>
-    </row>
-    <row r="5678" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5678" s="2"/>
-      <c r="I5678" s="1"/>
-    </row>
-    <row r="5679" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5679" s="1"/>
-    </row>
-    <row r="5680" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5680" s="2"/>
-      <c r="I5680" s="1"/>
-    </row>
-    <row r="5681" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5681" s="2"/>
-      <c r="I5681" s="1"/>
-    </row>
-    <row r="5682" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5682" s="2"/>
-      <c r="I5682" s="1"/>
-    </row>
-    <row r="5683" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5683" s="2"/>
-      <c r="I5683" s="1"/>
-    </row>
-    <row r="5684" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5684" s="2"/>
-      <c r="I5684" s="1"/>
-    </row>
-    <row r="5685" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5685" s="2"/>
-      <c r="I5685" s="1"/>
-    </row>
-    <row r="5686" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5686" s="2"/>
-      <c r="I5686" s="1"/>
-    </row>
-    <row r="5687" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5687" s="2"/>
-      <c r="I5687" s="1"/>
-    </row>
-    <row r="5688" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5688" s="2"/>
-      <c r="I5688" s="1"/>
-    </row>
-    <row r="5689" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5689" s="1"/>
-    </row>
-    <row r="5690" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5690" s="1"/>
-    </row>
-    <row r="5691" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5691" s="2"/>
-      <c r="I5691" s="1"/>
-    </row>
-    <row r="5692" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5692" s="2"/>
-      <c r="I5692" s="1"/>
-    </row>
-    <row r="5693" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5693" s="2"/>
-      <c r="I5693" s="1"/>
-    </row>
-    <row r="5694" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5694" s="2"/>
-      <c r="I5694" s="1"/>
-    </row>
-    <row r="5695" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5695" s="2"/>
-      <c r="I5695" s="1"/>
-    </row>
-    <row r="5696" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5696" s="2"/>
-      <c r="I5696" s="1"/>
-    </row>
-    <row r="5697" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5697" s="2"/>
-      <c r="I5697" s="1"/>
-    </row>
-    <row r="5698" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5698" s="2"/>
-      <c r="I5698" s="1"/>
-    </row>
-    <row r="5699" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5699" s="2"/>
-      <c r="I5699" s="1"/>
-    </row>
-    <row r="5700" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5700" s="2"/>
-      <c r="I5700" s="1"/>
-    </row>
-    <row r="5701" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5701" s="2"/>
-      <c r="I5701" s="1"/>
-    </row>
-    <row r="5702" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5702" s="2"/>
-      <c r="I5702" s="1"/>
-    </row>
-    <row r="5703" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5703" s="2"/>
-      <c r="I5703" s="1"/>
-    </row>
-    <row r="5704" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5704" s="2"/>
-      <c r="I5704" s="1"/>
-    </row>
-    <row r="5705" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5705" s="2"/>
-      <c r="I5705" s="1"/>
-    </row>
-    <row r="5706" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5706" s="2"/>
-      <c r="I5706" s="1"/>
-    </row>
-    <row r="5707" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5707" s="2"/>
-      <c r="I5707" s="1"/>
-    </row>
-    <row r="5708" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5708" s="2"/>
-      <c r="I5708" s="1"/>
-    </row>
-    <row r="5709" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5709" s="2"/>
-      <c r="I5709" s="1"/>
-    </row>
-    <row r="5710" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5710" s="2"/>
-      <c r="I5710" s="1"/>
-    </row>
-    <row r="5711" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5711" s="2"/>
-      <c r="I5711" s="1"/>
-    </row>
-    <row r="5712" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5712" s="2"/>
-      <c r="I5712" s="1"/>
-    </row>
-    <row r="5713" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5713" s="2"/>
-      <c r="I5713" s="1"/>
-    </row>
-    <row r="5714" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5714" s="2"/>
-      <c r="I5714" s="1"/>
-    </row>
-    <row r="5715" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5715" s="2"/>
-      <c r="I5715" s="1"/>
-    </row>
-    <row r="5716" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5716" s="2"/>
-      <c r="I5716" s="1"/>
-    </row>
-    <row r="5717" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5717" s="2"/>
-      <c r="I5717" s="1"/>
-    </row>
-    <row r="5718" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5718" s="1"/>
-    </row>
-    <row r="5719" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5719" s="2"/>
-      <c r="I5719" s="1"/>
-    </row>
-    <row r="5720" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5720" s="2"/>
-      <c r="I5720" s="1"/>
-    </row>
-    <row r="5721" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5721" s="2"/>
-      <c r="I5721" s="1"/>
-    </row>
-    <row r="5722" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5722" s="2"/>
-      <c r="I5722" s="1"/>
-    </row>
-    <row r="5723" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5723" s="2"/>
-      <c r="I5723" s="1"/>
-    </row>
-    <row r="5724" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5724" s="2"/>
-      <c r="I5724" s="1"/>
-    </row>
-    <row r="5725" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5725" s="2"/>
-      <c r="I5725" s="1"/>
-    </row>
-    <row r="5726" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5726" s="2"/>
-      <c r="I5726" s="1"/>
-    </row>
-    <row r="5727" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5727" s="2"/>
-      <c r="I5727" s="1"/>
-    </row>
-    <row r="5728" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5728" s="2"/>
-      <c r="I5728" s="1"/>
-    </row>
-    <row r="5729" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5729" s="2"/>
-      <c r="I5729" s="1"/>
-    </row>
-    <row r="5730" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5730" s="2"/>
-      <c r="I5730" s="1"/>
-    </row>
-    <row r="5731" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5731" s="2"/>
-      <c r="I5731" s="1"/>
-    </row>
-    <row r="5732" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5732" s="2"/>
-      <c r="I5732" s="1"/>
-    </row>
-    <row r="5733" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5733" s="2"/>
-      <c r="I5733" s="1"/>
-    </row>
-    <row r="5734" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5734" s="2"/>
-      <c r="I5734" s="1"/>
-    </row>
-    <row r="5735" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5735" s="2"/>
-      <c r="I5735" s="1"/>
-    </row>
-    <row r="5736" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5736" s="2"/>
-      <c r="I5736" s="1"/>
-    </row>
-    <row r="5737" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5737" s="1"/>
-    </row>
-    <row r="5738" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5738" s="2"/>
-      <c r="I5738" s="1"/>
-    </row>
-    <row r="5739" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5739" s="2"/>
-      <c r="I5739" s="1"/>
-    </row>
-    <row r="5740" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5740" s="2"/>
-      <c r="I5740" s="1"/>
-    </row>
-    <row r="5741" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5741" s="2"/>
-      <c r="I5741" s="1"/>
-    </row>
-    <row r="5742" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5742" s="2"/>
-      <c r="I5742" s="1"/>
-    </row>
-    <row r="5743" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5743" s="2"/>
-      <c r="I5743" s="1"/>
-    </row>
-    <row r="5744" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5744" s="2"/>
-      <c r="I5744" s="1"/>
-    </row>
-    <row r="5745" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5745" s="2"/>
-      <c r="I5745" s="1"/>
-    </row>
-    <row r="5746" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5746" s="2"/>
-      <c r="I5746" s="1"/>
-    </row>
-    <row r="5747" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5747" s="2"/>
-      <c r="I5747" s="1"/>
-    </row>
-    <row r="5748" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5748" s="2"/>
-      <c r="I5748" s="1"/>
-    </row>
-    <row r="5749" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5749" s="2"/>
-      <c r="I5749" s="1"/>
-    </row>
-    <row r="5750" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5750" s="1"/>
-    </row>
-    <row r="5751" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5751" s="2"/>
-      <c r="I5751" s="1"/>
-    </row>
-    <row r="5752" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5752" s="2"/>
-      <c r="I5752" s="1"/>
-    </row>
-    <row r="5753" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5753" s="2"/>
-      <c r="I5753" s="1"/>
-    </row>
-    <row r="5754" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5754" s="2"/>
-      <c r="I5754" s="1"/>
-    </row>
-    <row r="5755" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5755" s="2"/>
-      <c r="I5755" s="1"/>
-    </row>
-    <row r="5756" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5756" s="2"/>
-      <c r="I5756" s="1"/>
-    </row>
-    <row r="5757" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5757" s="2"/>
-      <c r="I5757" s="1"/>
-    </row>
-    <row r="5758" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5758" s="2"/>
-      <c r="I5758" s="1"/>
-    </row>
-    <row r="5759" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5759" s="2"/>
-      <c r="I5759" s="1"/>
-    </row>
-    <row r="5760" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5760" s="2"/>
-      <c r="I5760" s="1"/>
-    </row>
-    <row r="5761" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5761" s="1"/>
-    </row>
-    <row r="5762" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5762" s="1"/>
-    </row>
-    <row r="5763" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5763" s="2"/>
-      <c r="I5763" s="1"/>
-    </row>
-    <row r="5764" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5764" s="2"/>
-      <c r="I5764" s="1"/>
-    </row>
-    <row r="5765" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5765" s="2"/>
-      <c r="I5765" s="1"/>
-    </row>
-    <row r="5766" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5766" s="2"/>
-      <c r="I5766" s="1"/>
-    </row>
-    <row r="5767" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5767" s="1"/>
-    </row>
-    <row r="5768" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5768" s="2"/>
-      <c r="I5768" s="1"/>
-    </row>
-    <row r="5769" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5769" s="2"/>
-      <c r="I5769" s="1"/>
-    </row>
-    <row r="5770" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5770" s="2"/>
-      <c r="I5770" s="1"/>
-    </row>
-    <row r="5771" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5771" s="2"/>
-      <c r="I5771" s="1"/>
-    </row>
-    <row r="5772" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5772" s="2"/>
-      <c r="I5772" s="1"/>
-    </row>
-    <row r="5773" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5773" s="2"/>
-      <c r="I5773" s="1"/>
-    </row>
-    <row r="5774" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5774" s="2"/>
-      <c r="I5774" s="1"/>
-    </row>
-    <row r="5775" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5775" s="2"/>
-      <c r="I5775" s="1"/>
-    </row>
-    <row r="5776" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5776" s="2"/>
-      <c r="I5776" s="1"/>
-    </row>
-    <row r="5777" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5777" s="2"/>
-      <c r="I5777" s="1"/>
-    </row>
-    <row r="5778" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5778" s="2"/>
-      <c r="I5778" s="1"/>
-    </row>
-    <row r="5779" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5779" s="2"/>
-      <c r="I5779" s="1"/>
-    </row>
-    <row r="5780" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5780" s="2"/>
-      <c r="I5780" s="1"/>
-    </row>
-    <row r="5781" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5781" s="2"/>
-      <c r="I5781" s="1"/>
-    </row>
-    <row r="5782" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5782" s="2"/>
-      <c r="I5782" s="1"/>
-    </row>
-    <row r="5783" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5783" s="2"/>
-      <c r="I5783" s="1"/>
-    </row>
-    <row r="5784" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5784" s="2"/>
-      <c r="I5784" s="1"/>
-    </row>
-    <row r="5785" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5785" s="2"/>
-      <c r="I5785" s="1"/>
-    </row>
-    <row r="5786" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5786" s="1"/>
-    </row>
-    <row r="5787" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5787" s="1"/>
-    </row>
-    <row r="5788" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5788" s="2"/>
-      <c r="I5788" s="1"/>
-    </row>
-    <row r="5789" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5789" s="2"/>
-      <c r="I5789" s="1"/>
-    </row>
-    <row r="5790" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5790" s="2"/>
-      <c r="I5790" s="1"/>
-    </row>
-    <row r="5791" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5791" s="2"/>
-      <c r="I5791" s="1"/>
-    </row>
-    <row r="5792" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5792" s="2"/>
-      <c r="I5792" s="1"/>
-    </row>
-    <row r="5793" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5793" s="2"/>
-      <c r="I5793" s="1"/>
-    </row>
-    <row r="5794" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5794" s="2"/>
-      <c r="I5794" s="1"/>
-    </row>
-    <row r="5795" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5795" s="2"/>
-      <c r="I5795" s="1"/>
-    </row>
-    <row r="5796" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5796" s="2"/>
-      <c r="I5796" s="1"/>
-    </row>
-    <row r="5797" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5797" s="2"/>
-      <c r="I5797" s="1"/>
-    </row>
-    <row r="5798" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5798" s="2"/>
-      <c r="I5798" s="1"/>
-    </row>
-    <row r="5799" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5799" s="2"/>
-      <c r="I5799" s="1"/>
-    </row>
-    <row r="5800" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5800" s="2"/>
-      <c r="I5800" s="1"/>
-    </row>
-    <row r="5801" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5801" s="2"/>
-      <c r="I5801" s="1"/>
-    </row>
-    <row r="5802" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5802" s="2"/>
-      <c r="I5802" s="1"/>
-    </row>
-    <row r="5803" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5803" s="1"/>
-    </row>
-    <row r="5804" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5804" s="2"/>
-      <c r="I5804" s="1"/>
-    </row>
-    <row r="5805" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5805" s="2"/>
-      <c r="I5805" s="1"/>
-    </row>
-    <row r="5806" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5806" s="2"/>
-      <c r="I5806" s="1"/>
-    </row>
-    <row r="5807" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5807" s="2"/>
-      <c r="I5807" s="1"/>
-    </row>
-    <row r="5808" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5808" s="1"/>
-    </row>
-    <row r="5809" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5809" s="2"/>
-      <c r="I5809" s="1"/>
-    </row>
-    <row r="5810" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5810" s="2"/>
-      <c r="I5810" s="1"/>
-    </row>
-    <row r="5811" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5811" s="2"/>
-      <c r="I5811" s="1"/>
-    </row>
-    <row r="5812" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5812" s="2"/>
-      <c r="I5812" s="1"/>
-    </row>
-    <row r="5813" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5813" s="2"/>
-      <c r="I5813" s="1"/>
-    </row>
-    <row r="5814" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5814" s="2"/>
-      <c r="I5814" s="1"/>
-    </row>
-    <row r="5815" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5815" s="2"/>
-      <c r="I5815" s="1"/>
-    </row>
-    <row r="5816" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5816" s="1"/>
-    </row>
-    <row r="5817" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5817" s="2"/>
-      <c r="I5817" s="1"/>
-    </row>
-    <row r="5818" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5818" s="2"/>
-      <c r="I5818" s="1"/>
-    </row>
-    <row r="5819" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5819" s="2"/>
-      <c r="I5819" s="1"/>
-    </row>
-    <row r="5820" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5820" s="2"/>
-      <c r="I5820" s="1"/>
-    </row>
-    <row r="5821" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5821" s="2"/>
-      <c r="I5821" s="1"/>
-    </row>
-    <row r="5822" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5822" s="2"/>
-      <c r="I5822" s="1"/>
-    </row>
-    <row r="5823" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5823" s="2"/>
-      <c r="I5823" s="1"/>
-    </row>
-    <row r="5824" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5824" s="2"/>
-      <c r="I5824" s="1"/>
-    </row>
-    <row r="5825" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5825" s="2"/>
-      <c r="I5825" s="1"/>
-    </row>
-    <row r="5826" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5826" s="2"/>
-      <c r="I5826" s="1"/>
-    </row>
-    <row r="5827" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5827" s="2"/>
-      <c r="I5827" s="1"/>
-    </row>
-    <row r="5828" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5828" s="2"/>
-      <c r="I5828" s="1"/>
-    </row>
-    <row r="5829" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5829" s="2"/>
-      <c r="I5829" s="1"/>
-    </row>
-    <row r="5830" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5830" s="2"/>
-      <c r="I5830" s="1"/>
-    </row>
-    <row r="5831" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5831" s="2"/>
-      <c r="I5831" s="1"/>
-    </row>
-    <row r="5832" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5832" s="2"/>
-      <c r="I5832" s="1"/>
-    </row>
-    <row r="5833" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5833" s="2"/>
-      <c r="I5833" s="1"/>
-    </row>
-    <row r="5834" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5834" s="2"/>
-      <c r="I5834" s="1"/>
-    </row>
-    <row r="5835" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5835" s="2"/>
-      <c r="I5835" s="1"/>
-    </row>
-    <row r="5836" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5836" s="2"/>
-      <c r="I5836" s="1"/>
-    </row>
-    <row r="5837" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5837" s="2"/>
-      <c r="I5837" s="1"/>
-    </row>
-    <row r="5838" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5838" s="2"/>
-      <c r="I5838" s="1"/>
-    </row>
-    <row r="5839" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5839" s="2"/>
-      <c r="I5839" s="1"/>
-    </row>
-    <row r="5840" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5840" s="2"/>
-      <c r="I5840" s="1"/>
-    </row>
-    <row r="5841" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5841" s="2"/>
-      <c r="I5841" s="1"/>
-    </row>
-    <row r="5842" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5842" s="1"/>
-    </row>
-    <row r="5843" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5843" s="2"/>
-      <c r="I5843" s="1"/>
-    </row>
-    <row r="5844" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5844" s="2"/>
-      <c r="I5844" s="1"/>
-    </row>
-    <row r="5845" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5845" s="2"/>
-      <c r="I5845" s="1"/>
-    </row>
-    <row r="5846" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5846" s="2"/>
-      <c r="I5846" s="1"/>
-    </row>
-    <row r="5847" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5847" s="2"/>
-      <c r="I5847" s="1"/>
-    </row>
-    <row r="5848" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5848" s="2"/>
-      <c r="I5848" s="1"/>
-    </row>
-    <row r="5849" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5849" s="2"/>
-      <c r="I5849" s="1"/>
-    </row>
-    <row r="5850" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5850" s="2"/>
-      <c r="I5850" s="1"/>
-    </row>
-    <row r="5851" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5851" s="2"/>
-      <c r="I5851" s="1"/>
-    </row>
-    <row r="5852" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5852" s="1"/>
-    </row>
-    <row r="5853" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5853" s="2"/>
-      <c r="I5853" s="1"/>
-    </row>
-    <row r="5854" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5854" s="2"/>
-      <c r="I5854" s="1"/>
-    </row>
-    <row r="5855" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5855" s="2"/>
-      <c r="I5855" s="1"/>
-    </row>
-    <row r="5856" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5856" s="1"/>
-    </row>
-    <row r="5857" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5857" s="2"/>
-      <c r="I5857" s="1"/>
-    </row>
-    <row r="5858" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5858" s="2"/>
-      <c r="I5858" s="1"/>
-    </row>
-    <row r="5859" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5859" s="2"/>
-      <c r="I5859" s="1"/>
-    </row>
-    <row r="5860" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5860" s="1"/>
-    </row>
-    <row r="5861" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5861" s="2"/>
-      <c r="I5861" s="1"/>
-    </row>
-    <row r="5862" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5862" s="2"/>
-      <c r="I5862" s="1"/>
-    </row>
-    <row r="5863" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5863" s="2"/>
-      <c r="I5863" s="1"/>
-    </row>
-    <row r="5864" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5864" s="2"/>
-      <c r="I5864" s="1"/>
-    </row>
-    <row r="5865" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5865" s="2"/>
-      <c r="I5865" s="1"/>
-    </row>
-    <row r="5866" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5866" s="1"/>
-    </row>
-    <row r="5867" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5867" s="2"/>
-      <c r="I5867" s="1"/>
-    </row>
-    <row r="5868" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5868" s="2"/>
-      <c r="I5868" s="1"/>
-    </row>
-    <row r="5869" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5869" s="2"/>
-      <c r="I5869" s="1"/>
-    </row>
-    <row r="5870" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5870" s="2"/>
-      <c r="I5870" s="1"/>
-    </row>
-    <row r="5871" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5871" s="2"/>
-      <c r="I5871" s="1"/>
-    </row>
-    <row r="5872" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5872" s="2"/>
-      <c r="I5872" s="1"/>
-    </row>
-    <row r="5873" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5873" s="2"/>
-      <c r="I5873" s="1"/>
-    </row>
-    <row r="5874" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5874" s="1"/>
-    </row>
-    <row r="5875" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5875" s="2"/>
-      <c r="I5875" s="1"/>
-    </row>
-    <row r="5876" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5876" s="2"/>
-      <c r="I5876" s="1"/>
-    </row>
-    <row r="5877" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5877" s="2"/>
-      <c r="I5877" s="1"/>
-    </row>
-    <row r="5878" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5878" s="2"/>
-      <c r="I5878" s="1"/>
-    </row>
-    <row r="5879" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5879" s="2"/>
-      <c r="I5879" s="1"/>
-    </row>
-    <row r="5880" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5880" s="1"/>
-    </row>
-    <row r="5881" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5881" s="2"/>
-      <c r="I5881" s="1"/>
-    </row>
-    <row r="5882" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5882" s="2"/>
-      <c r="I5882" s="1"/>
-    </row>
-    <row r="5883" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5883" s="2"/>
-      <c r="I5883" s="1"/>
-    </row>
-    <row r="5884" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5884" s="2"/>
-      <c r="I5884" s="1"/>
-    </row>
-    <row r="5885" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5885" s="2"/>
-      <c r="I5885" s="1"/>
-    </row>
-    <row r="5886" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5886" s="2"/>
-      <c r="I5886" s="1"/>
-    </row>
-    <row r="5887" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5887" s="2"/>
-      <c r="I5887" s="1"/>
-    </row>
-    <row r="5888" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5888" s="2"/>
-      <c r="I5888" s="1"/>
-    </row>
-    <row r="5889" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5889" s="2"/>
-      <c r="I5889" s="1"/>
-    </row>
-    <row r="5890" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5890" s="2"/>
-      <c r="I5890" s="1"/>
-    </row>
-    <row r="5891" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5891" s="2"/>
-      <c r="I5891" s="1"/>
-    </row>
-    <row r="5892" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5892" s="2"/>
-      <c r="I5892" s="1"/>
-    </row>
-    <row r="5893" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5893" s="2"/>
-      <c r="I5893" s="1"/>
-    </row>
-    <row r="5894" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5894" s="2"/>
-      <c r="I5894" s="1"/>
-    </row>
-    <row r="5895" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5895" s="2"/>
-      <c r="I5895" s="1"/>
-    </row>
-    <row r="5896" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5896" s="2"/>
-      <c r="I5896" s="1"/>
-    </row>
-    <row r="5897" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5897" s="2"/>
-      <c r="I5897" s="1"/>
-    </row>
-    <row r="5898" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5898" s="1"/>
-    </row>
-    <row r="5899" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5899" s="2"/>
-      <c r="I5899" s="1"/>
-    </row>
-    <row r="5900" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5900" s="2"/>
-      <c r="I5900" s="1"/>
-    </row>
-    <row r="5901" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5901" s="2"/>
-      <c r="I5901" s="1"/>
-    </row>
-    <row r="5902" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5902" s="2"/>
-      <c r="I5902" s="1"/>
-    </row>
-    <row r="5903" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5903" s="2"/>
-      <c r="I5903" s="1"/>
-    </row>
-    <row r="5904" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5904" s="2"/>
-      <c r="I5904" s="1"/>
-    </row>
-    <row r="5905" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5905" s="2"/>
-      <c r="I5905" s="1"/>
-    </row>
-    <row r="5906" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5906" s="2"/>
-      <c r="I5906" s="1"/>
-    </row>
-    <row r="5907" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5907" s="2"/>
-      <c r="I5907" s="1"/>
-    </row>
-    <row r="5908" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5908" s="2"/>
-      <c r="I5908" s="1"/>
-    </row>
-    <row r="5909" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5909" s="2"/>
-      <c r="I5909" s="1"/>
-    </row>
-    <row r="5910" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5910" s="2"/>
-      <c r="I5910" s="1"/>
-    </row>
-    <row r="5911" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5911" s="2"/>
-      <c r="I5911" s="1"/>
-    </row>
-    <row r="5912" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5912" s="1"/>
-    </row>
-    <row r="5913" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5913" s="2"/>
-      <c r="I5913" s="1"/>
-    </row>
-    <row r="5914" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5914" s="2"/>
-      <c r="I5914" s="1"/>
-    </row>
-    <row r="5915" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5915" s="2"/>
-      <c r="I5915" s="1"/>
-    </row>
-    <row r="5916" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5916" s="2"/>
-      <c r="I5916" s="1"/>
-    </row>
-    <row r="5917" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5917" s="2"/>
-      <c r="I5917" s="1"/>
-    </row>
-    <row r="5918" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5918" s="2"/>
-      <c r="I5918" s="1"/>
-    </row>
-    <row r="5919" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5919" s="2"/>
-      <c r="I5919" s="1"/>
-    </row>
-    <row r="5920" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5920" s="2"/>
-      <c r="I5920" s="1"/>
-    </row>
-    <row r="5921" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5921" s="2"/>
-      <c r="I5921" s="1"/>
-    </row>
-    <row r="5922" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5922" s="2"/>
-      <c r="I5922" s="1"/>
-    </row>
-    <row r="5923" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5923" s="1"/>
-    </row>
-    <row r="5924" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5924" s="1"/>
-    </row>
-    <row r="5925" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5925" s="2"/>
-      <c r="I5925" s="1"/>
-    </row>
-    <row r="5926" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5926" s="2"/>
-      <c r="I5926" s="1"/>
-    </row>
-    <row r="5927" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5927" s="1"/>
-    </row>
-    <row r="5928" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I5928" s="1"/>
-    </row>
-    <row r="5929" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H5929" s="2"/>
-      <c r="I5929" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8012C9E-FC66-4DF7-AF1B-BAD1DF7206C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091CE884-BF69-4028-B095-E113426D8DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="60">
   <si>
     <t>Company Name</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>Julio Mendoza</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -629,10 +632,10 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -9192,74 +9195,352 @@
       </c>
     </row>
     <row r="319" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H319" s="2"/>
-      <c r="I319" s="1"/>
+      <c r="B319" t="s">
+        <v>34</v>
+      </c>
+      <c r="C319">
+        <v>1818</v>
+      </c>
+      <c r="D319" t="s">
+        <v>35</v>
+      </c>
+      <c r="F319" t="s">
+        <v>59</v>
+      </c>
+      <c r="G319" t="s">
+        <v>14</v>
+      </c>
+      <c r="H319" s="2">
+        <v>0</v>
+      </c>
+      <c r="I319" s="1">
+        <v>46118.760300925926</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H320" s="2"/>
       <c r="I320" s="1"/>
-    </row>
-    <row r="321" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H321" s="2"/>
-      <c r="I321" s="1"/>
-    </row>
-    <row r="322" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H322" s="2"/>
-      <c r="I322" s="1"/>
-    </row>
-    <row r="323" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H323" s="2"/>
-      <c r="I323" s="1"/>
-    </row>
-    <row r="324" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H324" s="2"/>
-      <c r="I324" s="1"/>
-    </row>
-    <row r="325" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H325" s="2"/>
-      <c r="I325" s="1"/>
-    </row>
-    <row r="326" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H326" s="2"/>
-      <c r="I326" s="1"/>
-    </row>
-    <row r="327" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H327" s="2"/>
-      <c r="I327" s="1"/>
-    </row>
-    <row r="328" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H328" s="2"/>
-      <c r="I328" s="1"/>
-    </row>
-    <row r="329" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H329" s="2"/>
-      <c r="I329" s="1"/>
-    </row>
-    <row r="330" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H330" s="2"/>
-      <c r="I330" s="1"/>
-    </row>
-    <row r="331" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K320" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="321" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B321" t="s">
+        <v>34</v>
+      </c>
+      <c r="C321">
+        <v>1819</v>
+      </c>
+      <c r="D321" t="s">
+        <v>38</v>
+      </c>
+      <c r="F321" t="s">
+        <v>59</v>
+      </c>
+      <c r="G321" t="s">
+        <v>13</v>
+      </c>
+      <c r="H321" s="2">
+        <v>0</v>
+      </c>
+      <c r="I321" s="1">
+        <v>46118.760300925926</v>
+      </c>
+      <c r="J321">
+        <v>1</v>
+      </c>
+      <c r="K321" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B322" t="s">
+        <v>34</v>
+      </c>
+      <c r="C322">
+        <v>1815</v>
+      </c>
+      <c r="D322" t="s">
+        <v>39</v>
+      </c>
+      <c r="F322" t="s">
+        <v>59</v>
+      </c>
+      <c r="G322" t="s">
+        <v>13</v>
+      </c>
+      <c r="H322" s="2">
+        <v>0</v>
+      </c>
+      <c r="I322" s="1">
+        <v>46118.760995370372</v>
+      </c>
+      <c r="J322">
+        <v>1</v>
+      </c>
+      <c r="K322" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="323" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B323" t="s">
+        <v>34</v>
+      </c>
+      <c r="C323">
+        <v>4827</v>
+      </c>
+      <c r="D323" t="s">
+        <v>57</v>
+      </c>
+      <c r="F323" t="s">
+        <v>59</v>
+      </c>
+      <c r="G323" t="s">
+        <v>10</v>
+      </c>
+      <c r="H323" s="2">
+        <v>6.6087962962962966E-3</v>
+      </c>
+      <c r="I323" s="1">
+        <v>46118.760995370372</v>
+      </c>
+      <c r="J323">
+        <v>1</v>
+      </c>
+      <c r="K323" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="324" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B324" t="s">
+        <v>34</v>
+      </c>
+      <c r="C324">
+        <v>1813</v>
+      </c>
+      <c r="D324" t="s">
+        <v>40</v>
+      </c>
+      <c r="F324" t="s">
+        <v>59</v>
+      </c>
+      <c r="G324" t="s">
+        <v>13</v>
+      </c>
+      <c r="H324" s="2">
+        <v>0</v>
+      </c>
+      <c r="I324" s="1">
+        <v>46118.761689814812</v>
+      </c>
+      <c r="J324">
+        <v>1</v>
+      </c>
+      <c r="K324" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B325" t="s">
+        <v>34</v>
+      </c>
+      <c r="C325">
+        <v>1812</v>
+      </c>
+      <c r="D325" t="s">
+        <v>41</v>
+      </c>
+      <c r="F325" t="s">
+        <v>59</v>
+      </c>
+      <c r="G325" t="s">
+        <v>10</v>
+      </c>
+      <c r="H325" s="2">
+        <v>1.8738425925925926E-2</v>
+      </c>
+      <c r="I325" s="1">
+        <v>46118.762384259258</v>
+      </c>
+      <c r="J325">
+        <v>0</v>
+      </c>
+      <c r="K325" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="326" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B326" t="s">
+        <v>34</v>
+      </c>
+      <c r="C326">
+        <v>4828</v>
+      </c>
+      <c r="D326" t="s">
+        <v>58</v>
+      </c>
+      <c r="F326" t="s">
+        <v>59</v>
+      </c>
+      <c r="G326" t="s">
+        <v>10</v>
+      </c>
+      <c r="H326" s="2">
+        <v>1.3125E-2</v>
+      </c>
+      <c r="I326" s="1">
+        <v>46118.762384259258</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="327" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B327" t="s">
+        <v>34</v>
+      </c>
+      <c r="C327">
+        <v>3125</v>
+      </c>
+      <c r="D327" t="s">
+        <v>53</v>
+      </c>
+      <c r="F327" t="s">
+        <v>59</v>
+      </c>
+      <c r="G327" t="s">
+        <v>13</v>
+      </c>
+      <c r="H327" s="2">
+        <v>0</v>
+      </c>
+      <c r="I327" s="1">
+        <v>46118.763078703705</v>
+      </c>
+      <c r="J327">
+        <v>1</v>
+      </c>
+      <c r="K327" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B328" t="s">
+        <v>34</v>
+      </c>
+      <c r="C328">
+        <v>1816</v>
+      </c>
+      <c r="D328" t="s">
+        <v>43</v>
+      </c>
+      <c r="F328" t="s">
+        <v>59</v>
+      </c>
+      <c r="G328" t="s">
+        <v>13</v>
+      </c>
+      <c r="H328" s="2">
+        <v>0</v>
+      </c>
+      <c r="I328" s="1">
+        <v>46118.763078703705</v>
+      </c>
+      <c r="J328">
+        <v>1</v>
+      </c>
+      <c r="K328" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="329" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B329" t="s">
+        <v>34</v>
+      </c>
+      <c r="C329">
+        <v>1809</v>
+      </c>
+      <c r="D329" t="s">
+        <v>47</v>
+      </c>
+      <c r="F329" t="s">
+        <v>59</v>
+      </c>
+      <c r="G329" t="s">
+        <v>13</v>
+      </c>
+      <c r="H329" s="2">
+        <v>0</v>
+      </c>
+      <c r="I329" s="1">
+        <v>46118.763773148145</v>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="330" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B330" t="s">
+        <v>34</v>
+      </c>
+      <c r="C330">
+        <v>1817</v>
+      </c>
+      <c r="D330" t="s">
+        <v>48</v>
+      </c>
+      <c r="F330" t="s">
+        <v>59</v>
+      </c>
+      <c r="G330" t="s">
+        <v>13</v>
+      </c>
+      <c r="H330" s="2">
+        <v>0</v>
+      </c>
+      <c r="I330" s="1">
+        <v>46118.764467592591</v>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="331" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H331" s="2"/>
       <c r="I331" s="1"/>
     </row>
-    <row r="332" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H332" s="2"/>
       <c r="I332" s="1"/>
     </row>
-    <row r="333" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H333" s="2"/>
       <c r="I333" s="1"/>
     </row>
-    <row r="334" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H334" s="2"/>
       <c r="I334" s="1"/>
     </row>
-    <row r="335" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H335" s="2"/>
       <c r="I335" s="1"/>
     </row>
-    <row r="336" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091CE884-BF69-4028-B095-E113426D8DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF7EA55-954A-41A6-9080-1683C0DA55F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="60">
   <si>
     <t>Company Name</t>
   </si>
@@ -635,7 +635,7 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -9244,48 +9244,26 @@
         <v>59</v>
       </c>
       <c r="G321" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H321" s="2">
-        <v>0</v>
+        <v>1.1574074074074075E-4</v>
       </c>
       <c r="I321" s="1">
         <v>46118.760300925926</v>
       </c>
       <c r="J321">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K321" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="322" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B322" t="s">
-        <v>34</v>
-      </c>
-      <c r="C322">
-        <v>1815</v>
-      </c>
-      <c r="D322" t="s">
-        <v>39</v>
-      </c>
-      <c r="F322" t="s">
-        <v>59</v>
-      </c>
-      <c r="G322" t="s">
-        <v>13</v>
-      </c>
-      <c r="H322" s="2">
-        <v>0</v>
-      </c>
-      <c r="I322" s="1">
-        <v>46118.760995370372</v>
-      </c>
-      <c r="J322">
-        <v>1</v>
-      </c>
+      <c r="H322" s="2"/>
+      <c r="I322" s="1"/>
       <c r="K322" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="323" spans="2:11" x14ac:dyDescent="0.25">
@@ -9293,10 +9271,10 @@
         <v>34</v>
       </c>
       <c r="C323">
-        <v>4827</v>
+        <v>1815</v>
       </c>
       <c r="D323" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F323" t="s">
         <v>59</v>
@@ -9305,13 +9283,13 @@
         <v>10</v>
       </c>
       <c r="H323" s="2">
-        <v>6.6087962962962966E-3</v>
+        <v>7.1990740740740739E-3</v>
       </c>
       <c r="I323" s="1">
         <v>46118.760995370372</v>
       </c>
       <c r="J323">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K323" t="s">
         <v>11</v>
@@ -9322,22 +9300,22 @@
         <v>34</v>
       </c>
       <c r="C324">
-        <v>1813</v>
+        <v>4827</v>
       </c>
       <c r="D324" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F324" t="s">
         <v>59</v>
       </c>
       <c r="G324" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H324" s="2">
-        <v>0</v>
+        <v>6.6087962962962966E-3</v>
       </c>
       <c r="I324" s="1">
-        <v>46118.761689814812</v>
+        <v>46118.760995370372</v>
       </c>
       <c r="J324">
         <v>1</v>
@@ -9351,25 +9329,25 @@
         <v>34</v>
       </c>
       <c r="C325">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="D325" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F325" t="s">
         <v>59</v>
       </c>
       <c r="G325" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H325" s="2">
-        <v>1.8738425925925926E-2</v>
+        <v>0</v>
       </c>
       <c r="I325" s="1">
-        <v>46118.762384259258</v>
+        <v>46118.761689814812</v>
       </c>
       <c r="J325">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K325" t="s">
         <v>11</v>
@@ -9380,10 +9358,10 @@
         <v>34</v>
       </c>
       <c r="C326">
-        <v>4828</v>
+        <v>1812</v>
       </c>
       <c r="D326" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F326" t="s">
         <v>59</v>
@@ -9392,7 +9370,7 @@
         <v>10</v>
       </c>
       <c r="H326" s="2">
-        <v>1.3125E-2</v>
+        <v>1.8738425925925926E-2</v>
       </c>
       <c r="I326" s="1">
         <v>46118.762384259258</v>
@@ -9409,25 +9387,25 @@
         <v>34</v>
       </c>
       <c r="C327">
-        <v>3125</v>
+        <v>4828</v>
       </c>
       <c r="D327" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F327" t="s">
         <v>59</v>
       </c>
       <c r="G327" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H327" s="2">
+        <v>1.3125E-2</v>
+      </c>
+      <c r="I327" s="1">
+        <v>46118.762384259258</v>
+      </c>
+      <c r="J327">
         <v>0</v>
-      </c>
-      <c r="I327" s="1">
-        <v>46118.763078703705</v>
-      </c>
-      <c r="J327">
-        <v>1</v>
       </c>
       <c r="K327" t="s">
         <v>11</v>
@@ -9438,10 +9416,10 @@
         <v>34</v>
       </c>
       <c r="C328">
-        <v>1816</v>
+        <v>3125</v>
       </c>
       <c r="D328" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F328" t="s">
         <v>59</v>
@@ -9456,7 +9434,7 @@
         <v>46118.763078703705</v>
       </c>
       <c r="J328">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -9467,25 +9445,25 @@
         <v>34</v>
       </c>
       <c r="C329">
-        <v>1809</v>
+        <v>1816</v>
       </c>
       <c r="D329" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F329" t="s">
         <v>59</v>
       </c>
       <c r="G329" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H329" s="2">
-        <v>0</v>
+        <v>7.9398148148148145E-3</v>
       </c>
       <c r="I329" s="1">
-        <v>46118.763773148145</v>
+        <v>46118.763078703705</v>
       </c>
       <c r="J329">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K329" t="s">
         <v>11</v>
@@ -9496,33 +9474,58 @@
         <v>34</v>
       </c>
       <c r="C330">
-        <v>1817</v>
+        <v>1809</v>
       </c>
       <c r="D330" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F330" t="s">
         <v>59</v>
       </c>
       <c r="G330" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H330" s="2">
-        <v>0</v>
+        <v>1.1979166666666667E-2</v>
       </c>
       <c r="I330" s="1">
+        <v>46118.763773148145</v>
+      </c>
+      <c r="J330">
+        <v>2</v>
+      </c>
+      <c r="K330" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="331" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B331" t="s">
+        <v>34</v>
+      </c>
+      <c r="C331">
+        <v>1817</v>
+      </c>
+      <c r="D331" t="s">
+        <v>48</v>
+      </c>
+      <c r="F331" t="s">
+        <v>59</v>
+      </c>
+      <c r="G331" t="s">
+        <v>10</v>
+      </c>
+      <c r="H331" s="2">
+        <v>1.0104166666666666E-2</v>
+      </c>
+      <c r="I331" s="1">
         <v>46118.764467592591</v>
       </c>
-      <c r="J330">
-        <v>1</v>
-      </c>
-      <c r="K330" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="331" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H331" s="2"/>
-      <c r="I331" s="1"/>
+      <c r="J331">
+        <v>3</v>
+      </c>
+      <c r="K331" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="332" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H332" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF7EA55-954A-41A6-9080-1683C0DA55F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63899389-CD31-474D-A884-DF503C221102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="60">
   <si>
     <t>Company Name</t>
   </si>
@@ -9347,7 +9347,7 @@
         <v>46118.761689814812</v>
       </c>
       <c r="J325">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K325" t="s">
         <v>11</v>
@@ -9434,7 +9434,7 @@
         <v>46118.763078703705</v>
       </c>
       <c r="J328">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -9528,86 +9528,364 @@
       </c>
     </row>
     <row r="332" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H332" s="2"/>
-      <c r="I332" s="1"/>
+      <c r="B332" t="s">
+        <v>34</v>
+      </c>
+      <c r="C332">
+        <v>1818</v>
+      </c>
+      <c r="D332" t="s">
+        <v>35</v>
+      </c>
+      <c r="F332" t="s">
+        <v>17</v>
+      </c>
+      <c r="G332" t="s">
+        <v>14</v>
+      </c>
+      <c r="H332" s="2">
+        <v>0</v>
+      </c>
+      <c r="I332" s="1">
+        <v>46146.690393518518</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="333" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H333" s="2"/>
       <c r="I333" s="1"/>
+      <c r="K333" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="334" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H334" s="2"/>
-      <c r="I334" s="1"/>
+      <c r="B334" t="s">
+        <v>34</v>
+      </c>
+      <c r="C334">
+        <v>1819</v>
+      </c>
+      <c r="D334" t="s">
+        <v>38</v>
+      </c>
+      <c r="F334" t="s">
+        <v>17</v>
+      </c>
+      <c r="G334" t="s">
+        <v>13</v>
+      </c>
+      <c r="H334" s="2">
+        <v>0</v>
+      </c>
+      <c r="I334" s="1">
+        <v>46146.691087962965</v>
+      </c>
+      <c r="J334">
+        <v>0</v>
+      </c>
+      <c r="K334" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="335" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H335" s="2"/>
-      <c r="I335" s="1"/>
+      <c r="B335" t="s">
+        <v>34</v>
+      </c>
+      <c r="C335">
+        <v>1815</v>
+      </c>
+      <c r="D335" t="s">
+        <v>39</v>
+      </c>
+      <c r="F335" t="s">
+        <v>17</v>
+      </c>
+      <c r="G335" t="s">
+        <v>13</v>
+      </c>
+      <c r="H335" s="2">
+        <v>0</v>
+      </c>
+      <c r="I335" s="1">
+        <v>46146.691782407404</v>
+      </c>
+      <c r="J335">
+        <v>0</v>
+      </c>
+      <c r="K335" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="336" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H336" s="2"/>
-      <c r="I336" s="1"/>
-    </row>
-    <row r="337" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H337" s="2"/>
-      <c r="I337" s="1"/>
-    </row>
-    <row r="338" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H338" s="2"/>
-      <c r="I338" s="1"/>
-    </row>
-    <row r="339" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H339" s="2"/>
-      <c r="I339" s="1"/>
-    </row>
-    <row r="340" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H340" s="2"/>
-      <c r="I340" s="1"/>
-    </row>
-    <row r="341" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H341" s="2"/>
-      <c r="I341" s="1"/>
-    </row>
-    <row r="342" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H342" s="2"/>
-      <c r="I342" s="1"/>
-    </row>
-    <row r="343" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H343" s="2"/>
-      <c r="I343" s="1"/>
-    </row>
-    <row r="344" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B336" t="s">
+        <v>34</v>
+      </c>
+      <c r="C336">
+        <v>4827</v>
+      </c>
+      <c r="D336" t="s">
+        <v>57</v>
+      </c>
+      <c r="F336" t="s">
+        <v>17</v>
+      </c>
+      <c r="G336" t="s">
+        <v>13</v>
+      </c>
+      <c r="H336" s="2">
+        <v>0</v>
+      </c>
+      <c r="I336" s="1">
+        <v>46146.691782407404</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
+      </c>
+      <c r="K336" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="337" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B337" t="s">
+        <v>34</v>
+      </c>
+      <c r="C337">
+        <v>1813</v>
+      </c>
+      <c r="D337" t="s">
+        <v>40</v>
+      </c>
+      <c r="F337" t="s">
+        <v>17</v>
+      </c>
+      <c r="G337" t="s">
+        <v>13</v>
+      </c>
+      <c r="H337" s="2">
+        <v>0</v>
+      </c>
+      <c r="I337" s="1">
+        <v>46146.668981481482</v>
+      </c>
+      <c r="J337">
+        <v>0</v>
+      </c>
+      <c r="K337" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B338" t="s">
+        <v>34</v>
+      </c>
+      <c r="C338">
+        <v>1812</v>
+      </c>
+      <c r="D338" t="s">
+        <v>41</v>
+      </c>
+      <c r="F338" t="s">
+        <v>17</v>
+      </c>
+      <c r="G338" t="s">
+        <v>13</v>
+      </c>
+      <c r="H338" s="2">
+        <v>0</v>
+      </c>
+      <c r="I338" s="1">
+        <v>46146.669675925928</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="339" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B339" t="s">
+        <v>34</v>
+      </c>
+      <c r="C339">
+        <v>4828</v>
+      </c>
+      <c r="D339" t="s">
+        <v>58</v>
+      </c>
+      <c r="F339" t="s">
+        <v>17</v>
+      </c>
+      <c r="G339" t="s">
+        <v>13</v>
+      </c>
+      <c r="H339" s="2">
+        <v>0</v>
+      </c>
+      <c r="I339" s="1">
+        <v>46146.670370370368</v>
+      </c>
+      <c r="J339">
+        <v>0</v>
+      </c>
+      <c r="K339" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="340" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B340" t="s">
+        <v>34</v>
+      </c>
+      <c r="C340">
+        <v>3125</v>
+      </c>
+      <c r="D340" t="s">
+        <v>53</v>
+      </c>
+      <c r="F340" t="s">
+        <v>17</v>
+      </c>
+      <c r="G340" t="s">
+        <v>10</v>
+      </c>
+      <c r="H340" s="2">
+        <v>4.31712962962963E-3</v>
+      </c>
+      <c r="I340" s="1">
+        <v>46146.671064814815</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="341" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B341" t="s">
+        <v>34</v>
+      </c>
+      <c r="C341">
+        <v>1816</v>
+      </c>
+      <c r="D341" t="s">
+        <v>43</v>
+      </c>
+      <c r="F341" t="s">
+        <v>17</v>
+      </c>
+      <c r="G341" t="s">
+        <v>10</v>
+      </c>
+      <c r="H341" s="2">
+        <v>5.0231481481481481E-3</v>
+      </c>
+      <c r="I341" s="1">
+        <v>46146.671064814815</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="342" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B342" t="s">
+        <v>34</v>
+      </c>
+      <c r="C342">
+        <v>1809</v>
+      </c>
+      <c r="D342" t="s">
+        <v>47</v>
+      </c>
+      <c r="F342" t="s">
+        <v>17</v>
+      </c>
+      <c r="G342" t="s">
+        <v>13</v>
+      </c>
+      <c r="H342" s="2">
+        <v>0</v>
+      </c>
+      <c r="I342" s="1">
+        <v>46146.671759259261</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="343" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B343" t="s">
+        <v>34</v>
+      </c>
+      <c r="C343">
+        <v>1817</v>
+      </c>
+      <c r="D343" t="s">
+        <v>48</v>
+      </c>
+      <c r="F343" t="s">
+        <v>17</v>
+      </c>
+      <c r="G343" t="s">
+        <v>13</v>
+      </c>
+      <c r="H343" s="2">
+        <v>0</v>
+      </c>
+      <c r="I343" s="1">
+        <v>46146.672453703701</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="344" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H344" s="2"/>
       <c r="I344" s="1"/>
     </row>
-    <row r="345" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H345" s="2"/>
       <c r="I345" s="1"/>
     </row>
-    <row r="346" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H346" s="2"/>
       <c r="I346" s="1"/>
     </row>
-    <row r="347" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H347" s="2"/>
       <c r="I347" s="1"/>
     </row>
-    <row r="348" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H348" s="2"/>
       <c r="I348" s="1"/>
     </row>
-    <row r="349" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H349" s="2"/>
       <c r="I349" s="1"/>
     </row>
-    <row r="350" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H350" s="2"/>
       <c r="I350" s="1"/>
     </row>
-    <row r="351" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H351" s="2"/>
       <c r="I351" s="1"/>
     </row>
-    <row r="352" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H352" s="2"/>
       <c r="I352" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63899389-CD31-474D-A884-DF503C221102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C3383A-2C47-47EB-AED5-4A74C1DE7442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -9347,7 +9347,7 @@
         <v>46118.761689814812</v>
       </c>
       <c r="J325">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K325" t="s">
         <v>11</v>
@@ -9434,7 +9434,7 @@
         <v>46118.763078703705</v>
       </c>
       <c r="J328">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -9606,10 +9606,10 @@
         <v>17</v>
       </c>
       <c r="G335" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H335" s="2">
-        <v>0</v>
+        <v>5.9722222222222225E-3</v>
       </c>
       <c r="I335" s="1">
         <v>46146.691782407404</v>
@@ -9635,10 +9635,10 @@
         <v>17</v>
       </c>
       <c r="G336" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H336" s="2">
-        <v>0</v>
+        <v>4.8726851851851848E-3</v>
       </c>
       <c r="I336" s="1">
         <v>46146.691782407404</v>
@@ -9693,10 +9693,10 @@
         <v>17</v>
       </c>
       <c r="G338" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H338" s="2">
-        <v>0</v>
+        <v>5.9953703703703705E-3</v>
       </c>
       <c r="I338" s="1">
         <v>46146.669675925928</v>
@@ -9722,10 +9722,10 @@
         <v>17</v>
       </c>
       <c r="G339" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H339" s="2">
-        <v>0</v>
+        <v>6.0069444444444441E-3</v>
       </c>
       <c r="I339" s="1">
         <v>46146.670370370368</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A668E7-A258-4138-B591-3D426A882675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882CE687-4806-4B80-BDBD-B7C523B48A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -9680,7 +9680,7 @@
         <v>46146.668981481482</v>
       </c>
       <c r="J338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K338" t="s">
         <v>11</v>
@@ -9816,16 +9816,16 @@
         <v>17</v>
       </c>
       <c r="G343" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H343" s="2">
-        <v>0</v>
+        <v>8.518518518518519E-3</v>
       </c>
       <c r="I343" s="1">
         <v>46146.671759259261</v>
       </c>
       <c r="J343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K343" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home Motors- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B72D21F0-F56D-4182-86E6-C4B8CC1A1D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A157C57D-1988-4F8B-BF38-7C72A3B5F3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10093,16 +10093,16 @@
         <v>24</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H350" s="2">
-        <v>0</v>
+        <v>7.5231481481481477E-3</v>
       </c>
       <c r="I350" s="1">
         <v>46175.795486111114</v>
       </c>
       <c r="J350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K350" t="s">
         <v>11</v>
@@ -10160,7 +10160,7 @@
         <v>46175.797569444447</v>
       </c>
       <c r="J352">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K352" t="s">
         <v>11</v>
@@ -10218,7 +10218,7 @@
         <v>46175.798958333333</v>
       </c>
       <c r="J354">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K354" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E6CC5F7-CC77-4352-A019-073A27FCE4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2D216A6-07CF-461A-80D7-0D2DF8009B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -89,6 +89,9 @@
     <t>Speed Management</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -101,10 +104,19 @@
     <t>Space Management-Big 5</t>
   </si>
   <si>
+    <t>Distracted Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
+  </si>
+  <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -116,49 +128,37 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Vehicle Inspections</t>
+    <t>Work Zone Safety</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
+    <t>Fatigue</t>
+  </si>
+  <si>
+    <t>Scene of an Accident</t>
+  </si>
+  <si>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>3 points of contact</t>
   </si>
   <si>
-    <t>Driver Health</t>
+    <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Fire Extinguisher Training for CDL</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
+    <t>DNU-Speed Management</t>
   </si>
   <si>
     <t>DNU-Def.Drive Distracted Driving</t>
   </si>
   <si>
-    <t>DNU-Speed Management</t>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>DNUNEW-Space Management Big 5</t>
-  </si>
-  <si>
-    <t>Scene of an Accident</t>
-  </si>
-  <si>
-    <t>Fatigue</t>
-  </si>
-  <si>
-    <t>Micro-Learn Safe Following Distance</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Home Motors</t>
@@ -601,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -659,7 +659,7 @@
         <v>41</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -688,7 +688,7 @@
         <v>42</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>13</v>
@@ -717,7 +717,7 @@
         <v>43</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -746,7 +746,7 @@
         <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -775,7 +775,7 @@
         <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>12</v>
@@ -799,7 +799,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="1"/>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>46</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -842,7 +842,7 @@
         <v>47</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -871,7 +871,7 @@
         <v>48</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -900,7 +900,7 @@
         <v>49</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -929,7 +929,7 @@
         <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -958,7 +958,7 @@
         <v>51</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>14</v>
@@ -982,7 +982,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="1"/>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
@@ -996,7 +996,7 @@
         <v>52</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>14</v>
@@ -1020,7 +1020,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="1"/>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
@@ -1034,7 +1034,7 @@
         <v>52</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1063,7 +1063,7 @@
         <v>53</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>41</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -1121,7 +1121,7 @@
         <v>42</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>13</v>
@@ -1150,7 +1150,7 @@
         <v>54</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>12</v>
@@ -1174,7 +1174,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
@@ -1188,7 +1188,7 @@
         <v>43</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1217,7 +1217,7 @@
         <v>44</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1246,7 +1246,7 @@
         <v>45</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>12</v>
@@ -1270,7 +1270,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1284,7 +1284,7 @@
         <v>46</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1313,7 +1313,7 @@
         <v>47</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1342,7 +1342,7 @@
         <v>48</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1371,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>14</v>
@@ -1395,7 +1395,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="1"/>
       <c r="M31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
@@ -1409,7 +1409,7 @@
         <v>51</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1438,7 +1438,7 @@
         <v>52</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>12</v>
@@ -1462,7 +1462,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
       <c r="M34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
@@ -1476,7 +1476,7 @@
         <v>52</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>12</v>
@@ -1500,7 +1500,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="1"/>
       <c r="M36" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
@@ -1514,7 +1514,7 @@
         <v>53</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>14</v>
@@ -1538,7 +1538,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="1"/>
       <c r="M38" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
@@ -1552,7 +1552,7 @@
         <v>41</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>13</v>
@@ -1581,7 +1581,7 @@
         <v>42</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>13</v>
@@ -1610,7 +1610,7 @@
         <v>54</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>13</v>
@@ -1639,7 +1639,7 @@
         <v>43</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>12</v>
@@ -1663,7 +1663,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="1"/>
       <c r="M43" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
@@ -1677,7 +1677,7 @@
         <v>44</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1706,7 +1706,7 @@
         <v>45</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>13</v>
@@ -1735,7 +1735,7 @@
         <v>46</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1764,7 +1764,7 @@
         <v>47</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1793,7 +1793,7 @@
         <v>48</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1822,7 +1822,7 @@
         <v>50</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -1851,7 +1851,7 @@
         <v>51</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>13</v>
@@ -1880,7 +1880,7 @@
         <v>52</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -1909,7 +1909,7 @@
         <v>53</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>12</v>
@@ -1933,7 +1933,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
       <c r="M53" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
@@ -1947,7 +1947,7 @@
         <v>41</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>13</v>
@@ -1976,7 +1976,7 @@
         <v>42</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>13</v>
@@ -2005,7 +2005,7 @@
         <v>54</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2034,7 +2034,7 @@
         <v>43</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2063,7 +2063,7 @@
         <v>44</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2092,7 +2092,7 @@
         <v>45</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2121,7 +2121,7 @@
         <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2150,7 +2150,7 @@
         <v>51</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2179,7 +2179,7 @@
         <v>53</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2208,7 +2208,7 @@
         <v>41</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>13</v>
@@ -2237,7 +2237,7 @@
         <v>42</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>13</v>
@@ -2266,7 +2266,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>13</v>
@@ -2295,7 +2295,7 @@
         <v>43</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2324,7 +2324,7 @@
         <v>44</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2353,7 +2353,7 @@
         <v>45</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2382,7 +2382,7 @@
         <v>46</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2411,7 +2411,7 @@
         <v>47</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2440,7 +2440,7 @@
         <v>48</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2469,7 +2469,7 @@
         <v>50</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2498,7 +2498,7 @@
         <v>51</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2527,7 +2527,7 @@
         <v>52</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2556,7 +2556,7 @@
         <v>53</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2585,7 +2585,7 @@
         <v>41</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>13</v>
@@ -2614,7 +2614,7 @@
         <v>42</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>13</v>
@@ -2643,7 +2643,7 @@
         <v>43</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>10</v>
@@ -2672,7 +2672,7 @@
         <v>44</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2701,7 +2701,7 @@
         <v>45</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2730,7 +2730,7 @@
         <v>46</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2759,7 +2759,7 @@
         <v>47</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2788,7 +2788,7 @@
         <v>48</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>50</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2846,7 +2846,7 @@
         <v>51</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2875,7 +2875,7 @@
         <v>52</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>10</v>
@@ -2904,7 +2904,7 @@
         <v>53</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -2933,7 +2933,7 @@
         <v>41</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -2962,7 +2962,7 @@
         <v>42</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -2991,7 +2991,7 @@
         <v>55</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -3020,7 +3020,7 @@
         <v>43</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3049,7 +3049,7 @@
         <v>44</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3078,7 +3078,7 @@
         <v>45</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3107,7 +3107,7 @@
         <v>46</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3136,7 +3136,7 @@
         <v>47</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3165,7 +3165,7 @@
         <v>48</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3194,7 +3194,7 @@
         <v>50</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>10</v>
@@ -3223,7 +3223,7 @@
         <v>51</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>13</v>
@@ -3252,7 +3252,7 @@
         <v>52</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3281,7 +3281,7 @@
         <v>53</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3310,7 +3310,7 @@
         <v>41</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3339,7 +3339,7 @@
         <v>42</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3368,7 +3368,7 @@
         <v>55</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3397,7 +3397,7 @@
         <v>43</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3426,7 +3426,7 @@
         <v>44</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3455,7 +3455,7 @@
         <v>45</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>13</v>
@@ -3484,7 +3484,7 @@
         <v>46</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3513,7 +3513,7 @@
         <v>47</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3542,7 +3542,7 @@
         <v>48</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3571,7 +3571,7 @@
         <v>50</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>13</v>
@@ -3600,7 +3600,7 @@
         <v>51</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>13</v>
@@ -3629,7 +3629,7 @@
         <v>52</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3658,7 +3658,7 @@
         <v>53</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3687,7 +3687,7 @@
         <v>41</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3716,7 +3716,7 @@
         <v>42</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3745,7 +3745,7 @@
         <v>55</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3774,7 +3774,7 @@
         <v>43</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -3803,7 +3803,7 @@
         <v>44</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3832,7 +3832,7 @@
         <v>45</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3861,7 +3861,7 @@
         <v>46</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -3890,7 +3890,7 @@
         <v>48</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -3919,7 +3919,7 @@
         <v>50</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3948,7 +3948,7 @@
         <v>51</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -3977,7 +3977,7 @@
         <v>52</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4006,7 +4006,7 @@
         <v>53</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4035,7 +4035,7 @@
         <v>41</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>12</v>
@@ -4059,7 +4059,7 @@
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
       <c r="M127" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
@@ -4073,7 +4073,7 @@
         <v>42</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4102,7 +4102,7 @@
         <v>55</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4131,7 +4131,7 @@
         <v>43</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>10</v>
@@ -4160,7 +4160,7 @@
         <v>44</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4189,7 +4189,7 @@
         <v>45</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>14</v>
@@ -4213,7 +4213,7 @@
       <c r="J133" s="2"/>
       <c r="K133" s="1"/>
       <c r="M133" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
@@ -4227,7 +4227,7 @@
         <v>46</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4256,7 +4256,7 @@
         <v>56</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>12</v>
@@ -4280,7 +4280,7 @@
       <c r="J136" s="2"/>
       <c r="K136" s="1"/>
       <c r="M136" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
@@ -4294,7 +4294,7 @@
         <v>48</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4323,7 +4323,7 @@
         <v>57</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4352,7 +4352,7 @@
         <v>51</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4381,7 +4381,7 @@
         <v>52</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>12</v>
@@ -4405,7 +4405,7 @@
       <c r="J141" s="2"/>
       <c r="K141" s="1"/>
       <c r="M141" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
@@ -4419,7 +4419,7 @@
         <v>53</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>10</v>
@@ -4675,7 +4675,7 @@
       <c r="J151" s="2"/>
       <c r="K151" s="1"/>
       <c r="M151" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
@@ -4800,7 +4800,7 @@
       <c r="J156" s="2"/>
       <c r="K156" s="1"/>
       <c r="M156" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
@@ -4843,7 +4843,7 @@
         <v>41</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>10</v>
@@ -4872,7 +4872,7 @@
         <v>42</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -4901,7 +4901,7 @@
         <v>43</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -4930,7 +4930,7 @@
         <v>44</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>10</v>
@@ -4959,7 +4959,7 @@
         <v>45</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>12</v>
@@ -4983,7 +4983,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
       <c r="M163" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -4997,7 +4997,7 @@
         <v>46</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>10</v>
@@ -5026,7 +5026,7 @@
         <v>56</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>10</v>
@@ -5055,7 +5055,7 @@
         <v>48</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>10</v>
@@ -5084,7 +5084,7 @@
         <v>57</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>10</v>
@@ -5113,7 +5113,7 @@
         <v>51</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>13</v>
@@ -5142,7 +5142,7 @@
         <v>52</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>12</v>
@@ -5166,7 +5166,7 @@
       <c r="J170" s="2"/>
       <c r="K170" s="1"/>
       <c r="M170" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.3">
@@ -5180,7 +5180,7 @@
         <v>53</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>13</v>
@@ -5209,7 +5209,7 @@
         <v>41</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5238,7 +5238,7 @@
         <v>42</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>13</v>
@@ -5267,7 +5267,7 @@
         <v>43</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>10</v>
@@ -5296,7 +5296,7 @@
         <v>44</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5325,7 +5325,7 @@
         <v>45</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>10</v>
@@ -5354,7 +5354,7 @@
         <v>46</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -5383,7 +5383,7 @@
         <v>56</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5412,7 +5412,7 @@
         <v>48</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5441,7 +5441,7 @@
         <v>57</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>10</v>
@@ -5470,7 +5470,7 @@
         <v>51</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5499,7 +5499,7 @@
         <v>52</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -5528,7 +5528,7 @@
         <v>53</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -5557,7 +5557,7 @@
         <v>41</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>10</v>
@@ -5586,7 +5586,7 @@
         <v>42</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5615,7 +5615,7 @@
         <v>43</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>10</v>
@@ -5644,7 +5644,7 @@
         <v>44</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -5673,7 +5673,7 @@
         <v>45</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>10</v>
@@ -5702,7 +5702,7 @@
         <v>46</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5731,7 +5731,7 @@
         <v>56</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -5760,7 +5760,7 @@
         <v>48</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -5789,7 +5789,7 @@
         <v>57</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>10</v>
@@ -5818,7 +5818,7 @@
         <v>51</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>13</v>
@@ -5847,7 +5847,7 @@
         <v>52</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -5876,7 +5876,7 @@
         <v>53</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -5905,7 +5905,7 @@
         <v>41</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -5934,7 +5934,7 @@
         <v>42</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>13</v>
@@ -5963,7 +5963,7 @@
         <v>43</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>10</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6021,7 +6021,7 @@
         <v>45</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6050,7 +6050,7 @@
         <v>46</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>10</v>
@@ -6079,7 +6079,7 @@
         <v>56</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6108,7 +6108,7 @@
         <v>48</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6137,7 +6137,7 @@
         <v>57</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6166,7 +6166,7 @@
         <v>51</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>13</v>
@@ -6195,7 +6195,7 @@
         <v>52</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>13</v>
@@ -6224,7 +6224,7 @@
         <v>53</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>10</v>
@@ -6253,7 +6253,7 @@
         <v>41</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -6282,7 +6282,7 @@
         <v>42</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6311,7 +6311,7 @@
         <v>43</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>10</v>
@@ -6340,7 +6340,7 @@
         <v>44</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6369,7 +6369,7 @@
         <v>58</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6398,7 +6398,7 @@
         <v>45</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>13</v>
@@ -6427,7 +6427,7 @@
         <v>46</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>12</v>
@@ -6451,7 +6451,7 @@
       <c r="J215" s="2"/>
       <c r="K215" s="1"/>
       <c r="M215" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
@@ -6465,7 +6465,7 @@
         <v>56</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6494,7 +6494,7 @@
         <v>48</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6523,7 +6523,7 @@
         <v>57</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6552,7 +6552,7 @@
         <v>51</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6581,7 +6581,7 @@
         <v>52</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -6610,7 +6610,7 @@
         <v>53</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>10</v>
@@ -6639,7 +6639,7 @@
         <v>41</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6668,7 +6668,7 @@
         <v>42</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>13</v>
@@ -6697,7 +6697,7 @@
         <v>43</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6726,7 +6726,7 @@
         <v>44</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>10</v>
@@ -6755,7 +6755,7 @@
         <v>59</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>10</v>
@@ -6784,7 +6784,7 @@
         <v>45</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -6813,7 +6813,7 @@
         <v>46</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -6842,7 +6842,7 @@
         <v>56</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -6871,7 +6871,7 @@
         <v>48</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -6900,7 +6900,7 @@
         <v>57</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -6929,7 +6929,7 @@
         <v>51</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -6958,7 +6958,7 @@
         <v>52</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -6987,7 +6987,7 @@
         <v>53</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -7016,7 +7016,7 @@
         <v>41</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>10</v>
@@ -7045,7 +7045,7 @@
         <v>42</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>13</v>
@@ -7074,7 +7074,7 @@
         <v>43</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7103,7 +7103,7 @@
         <v>44</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -7132,7 +7132,7 @@
         <v>60</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>10</v>
@@ -7161,7 +7161,7 @@
         <v>59</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7190,7 +7190,7 @@
         <v>45</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>10</v>
@@ -7219,7 +7219,7 @@
         <v>46</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -7248,7 +7248,7 @@
         <v>61</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -7277,7 +7277,7 @@
         <v>56</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>10</v>
@@ -7306,7 +7306,7 @@
         <v>48</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -7335,7 +7335,7 @@
         <v>51</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7364,7 +7364,7 @@
         <v>52</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>12</v>
@@ -7388,7 +7388,7 @@
       <c r="J248" s="2"/>
       <c r="K248" s="1"/>
       <c r="M248" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
@@ -7402,7 +7402,7 @@
         <v>53</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>10</v>
@@ -7431,7 +7431,7 @@
         <v>41</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>14</v>
@@ -7455,7 +7455,7 @@
       <c r="J251" s="2"/>
       <c r="K251" s="1"/>
       <c r="M251" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
@@ -7469,7 +7469,7 @@
         <v>42</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7498,7 +7498,7 @@
         <v>43</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -7527,7 +7527,7 @@
         <v>44</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7556,7 +7556,7 @@
         <v>60</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7585,7 +7585,7 @@
         <v>59</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>13</v>
@@ -7614,7 +7614,7 @@
         <v>45</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7643,7 +7643,7 @@
         <v>46</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -7672,7 +7672,7 @@
         <v>61</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>10</v>
@@ -7701,7 +7701,7 @@
         <v>56</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>10</v>
@@ -7730,7 +7730,7 @@
         <v>48</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7759,7 +7759,7 @@
         <v>51</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -7788,7 +7788,7 @@
         <v>52</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>12</v>
@@ -7812,7 +7812,7 @@
       <c r="J264" s="2"/>
       <c r="K264" s="1"/>
       <c r="M264" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
@@ -7826,7 +7826,7 @@
         <v>53</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>10</v>
@@ -7855,7 +7855,7 @@
         <v>41</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>12</v>
@@ -7879,7 +7879,7 @@
       <c r="J267" s="2"/>
       <c r="K267" s="1"/>
       <c r="M267" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
@@ -7893,7 +7893,7 @@
         <v>42</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -7922,7 +7922,7 @@
         <v>43</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -7951,7 +7951,7 @@
         <v>44</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>10</v>
@@ -7980,7 +7980,7 @@
         <v>60</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -8009,7 +8009,7 @@
         <v>59</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>13</v>
@@ -8038,7 +8038,7 @@
         <v>45</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -8067,7 +8067,7 @@
         <v>46</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>12</v>
@@ -8091,7 +8091,7 @@
       <c r="J275" s="2"/>
       <c r="K275" s="1"/>
       <c r="M275" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
@@ -8105,7 +8105,7 @@
         <v>61</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>10</v>
@@ -8134,7 +8134,7 @@
         <v>56</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>10</v>
@@ -8163,7 +8163,7 @@
         <v>48</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -8192,7 +8192,7 @@
         <v>51</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8221,7 +8221,7 @@
         <v>52</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>13</v>
@@ -8250,7 +8250,7 @@
         <v>53</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8279,7 +8279,7 @@
         <v>41</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>14</v>
@@ -8303,7 +8303,7 @@
       <c r="J283" s="2"/>
       <c r="K283" s="1"/>
       <c r="M283" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
@@ -8317,7 +8317,7 @@
         <v>43</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>10</v>
@@ -8346,7 +8346,7 @@
         <v>44</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>10</v>
@@ -8375,7 +8375,7 @@
         <v>60</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>10</v>
@@ -8404,7 +8404,7 @@
         <v>45</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>10</v>
@@ -8433,7 +8433,7 @@
         <v>46</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>10</v>
@@ -8462,7 +8462,7 @@
         <v>61</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -8491,7 +8491,7 @@
         <v>56</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>10</v>
@@ -8520,7 +8520,7 @@
         <v>48</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>10</v>
@@ -8549,7 +8549,7 @@
         <v>52</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>13</v>
@@ -8578,7 +8578,7 @@
         <v>53</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>10</v>
@@ -8607,7 +8607,7 @@
         <v>41</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8636,7 +8636,7 @@
         <v>43</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>10</v>
@@ -8665,7 +8665,7 @@
         <v>44</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8694,7 +8694,7 @@
         <v>60</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>10</v>
@@ -8723,7 +8723,7 @@
         <v>45</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -8752,7 +8752,7 @@
         <v>46</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -8781,7 +8781,7 @@
         <v>61</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>10</v>
@@ -8810,7 +8810,7 @@
         <v>56</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>12</v>
@@ -8834,7 +8834,7 @@
       <c r="J302" s="2"/>
       <c r="K302" s="1"/>
       <c r="M302" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.3">
@@ -8848,7 +8848,7 @@
         <v>48</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>10</v>
@@ -8877,7 +8877,7 @@
         <v>52</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>13</v>
@@ -8906,7 +8906,7 @@
         <v>53</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -8935,7 +8935,7 @@
         <v>41</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -8964,7 +8964,7 @@
         <v>43</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>10</v>
@@ -8993,7 +8993,7 @@
         <v>44</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>10</v>
@@ -9022,7 +9022,7 @@
         <v>60</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>10</v>
@@ -9051,7 +9051,7 @@
         <v>45</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>10</v>
@@ -9080,7 +9080,7 @@
         <v>46</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>12</v>
@@ -9104,7 +9104,7 @@
       <c r="J312" s="2"/>
       <c r="K312" s="1"/>
       <c r="M312" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="313" spans="4:13" x14ac:dyDescent="0.3">
@@ -9118,7 +9118,7 @@
         <v>61</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>10</v>
@@ -9147,7 +9147,7 @@
         <v>56</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>14</v>
@@ -9171,7 +9171,7 @@
       <c r="J315" s="2"/>
       <c r="K315" s="1"/>
       <c r="M315" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
@@ -9185,7 +9185,7 @@
         <v>48</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>10</v>
@@ -9214,7 +9214,7 @@
         <v>52</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>13</v>
@@ -9243,7 +9243,7 @@
         <v>53</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -9272,7 +9272,7 @@
         <v>41</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>14</v>
@@ -9296,7 +9296,7 @@
       <c r="J320" s="2"/>
       <c r="K320" s="1"/>
       <c r="M320" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="321" spans="4:13" x14ac:dyDescent="0.3">
@@ -9310,7 +9310,7 @@
         <v>43</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>12</v>
@@ -9334,7 +9334,7 @@
       <c r="J322" s="2"/>
       <c r="K322" s="1"/>
       <c r="M322" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="323" spans="4:13" x14ac:dyDescent="0.3">
@@ -9348,7 +9348,7 @@
         <v>44</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>10</v>
@@ -9377,7 +9377,7 @@
         <v>60</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>10</v>
@@ -9406,7 +9406,7 @@
         <v>45</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>13</v>
@@ -9435,7 +9435,7 @@
         <v>46</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>10</v>
@@ -9464,7 +9464,7 @@
         <v>61</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>10</v>
@@ -9493,7 +9493,7 @@
         <v>56</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>13</v>
@@ -9522,7 +9522,7 @@
         <v>48</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9551,7 +9551,7 @@
         <v>52</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9580,7 +9580,7 @@
         <v>53</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9609,7 +9609,7 @@
         <v>41</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>14</v>
@@ -9633,7 +9633,7 @@
       <c r="J333" s="2"/>
       <c r="K333" s="1"/>
       <c r="M333" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="334" spans="4:13" x14ac:dyDescent="0.3">
@@ -9647,7 +9647,7 @@
         <v>43</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>12</v>
@@ -9671,7 +9671,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
       <c r="M335" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
@@ -9685,7 +9685,7 @@
         <v>44</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -9714,7 +9714,7 @@
         <v>60</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>10</v>
@@ -9743,7 +9743,7 @@
         <v>45</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>10</v>
@@ -9772,7 +9772,7 @@
         <v>46</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -9801,7 +9801,7 @@
         <v>61</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -9830,7 +9830,7 @@
         <v>56</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>10</v>
@@ -9859,7 +9859,7 @@
         <v>48</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>10</v>
@@ -9888,7 +9888,7 @@
         <v>52</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -9917,7 +9917,7 @@
         <v>53</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>10</v>
@@ -10062,7 +10062,7 @@
         <v>43</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>10</v>
@@ -10091,7 +10091,7 @@
         <v>44</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>10</v>
@@ -10120,7 +10120,7 @@
         <v>60</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>10</v>
@@ -10149,7 +10149,7 @@
         <v>56</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>13</v>
@@ -10178,7 +10178,7 @@
         <v>48</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>10</v>
@@ -10207,7 +10207,7 @@
         <v>52</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>13</v>
@@ -10236,7 +10236,7 @@
         <v>53</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10265,7 +10265,7 @@
         <v>45</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -12902,6 +12902,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -12976,6 +12977,7 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
@@ -46484,7 +46486,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2D216A6-07CF-461A-80D7-0D2DF8009B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71C15146-42D7-42EF-9C25-75FEF039C774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="64">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,10 +86,16 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -101,7 +107,7 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Fatigue</t>
   </si>
   <si>
     <t>Distracted Driving</t>
@@ -110,16 +116,19 @@
     <t>Driver Health</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
@@ -128,19 +137,10 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Fatigue</t>
-  </si>
-  <si>
     <t>Scene of an Accident</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>3 points of contact</t>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>Colynn Brandt Taylor</t>
+  </si>
+  <si>
+    <t>Mike Moreno</t>
   </si>
 </sst>
 </file>
@@ -601,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -799,7 +802,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="1"/>
       <c r="M7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
@@ -982,7 +985,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="1"/>
       <c r="M14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
@@ -1020,7 +1023,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="1"/>
       <c r="M16" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
@@ -1174,7 +1177,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
@@ -1270,7 +1273,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1395,7 +1398,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="1"/>
       <c r="M31" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
@@ -1462,7 +1465,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
       <c r="M34" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
@@ -1500,7 +1503,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="1"/>
       <c r="M36" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
@@ -1538,7 +1541,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="1"/>
       <c r="M38" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
@@ -1663,7 +1666,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="1"/>
       <c r="M43" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
@@ -1933,7 +1936,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
       <c r="M53" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
@@ -1947,7 +1950,7 @@
         <v>41</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>13</v>
@@ -1976,7 +1979,7 @@
         <v>42</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>13</v>
@@ -2005,7 +2008,7 @@
         <v>54</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2034,7 +2037,7 @@
         <v>43</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2063,7 +2066,7 @@
         <v>44</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2092,7 +2095,7 @@
         <v>45</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2121,7 +2124,7 @@
         <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2150,7 +2153,7 @@
         <v>51</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2179,7 +2182,7 @@
         <v>53</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2208,7 +2211,7 @@
         <v>41</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>13</v>
@@ -2237,7 +2240,7 @@
         <v>42</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>13</v>
@@ -2266,7 +2269,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>13</v>
@@ -2295,7 +2298,7 @@
         <v>43</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2324,7 +2327,7 @@
         <v>44</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2353,7 +2356,7 @@
         <v>45</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2382,7 +2385,7 @@
         <v>46</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2411,7 +2414,7 @@
         <v>47</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2440,7 +2443,7 @@
         <v>48</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2469,7 +2472,7 @@
         <v>50</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2498,7 +2501,7 @@
         <v>51</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2527,7 +2530,7 @@
         <v>52</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2556,7 +2559,7 @@
         <v>53</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2585,7 +2588,7 @@
         <v>41</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>13</v>
@@ -2614,7 +2617,7 @@
         <v>42</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>13</v>
@@ -2643,7 +2646,7 @@
         <v>43</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>10</v>
@@ -2672,7 +2675,7 @@
         <v>44</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2701,7 +2704,7 @@
         <v>45</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2730,7 +2733,7 @@
         <v>46</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2759,7 +2762,7 @@
         <v>47</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2788,7 +2791,7 @@
         <v>48</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2817,7 +2820,7 @@
         <v>50</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2846,7 +2849,7 @@
         <v>51</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2875,7 +2878,7 @@
         <v>52</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>10</v>
@@ -2904,7 +2907,7 @@
         <v>53</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -2933,7 +2936,7 @@
         <v>41</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -2962,7 +2965,7 @@
         <v>42</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -2991,7 +2994,7 @@
         <v>55</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -3020,7 +3023,7 @@
         <v>43</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3049,7 +3052,7 @@
         <v>44</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3078,7 +3081,7 @@
         <v>45</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3107,7 +3110,7 @@
         <v>46</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3136,7 +3139,7 @@
         <v>47</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3165,7 +3168,7 @@
         <v>48</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3194,7 +3197,7 @@
         <v>50</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>10</v>
@@ -3223,7 +3226,7 @@
         <v>51</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>13</v>
@@ -3252,7 +3255,7 @@
         <v>52</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3281,7 +3284,7 @@
         <v>53</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3310,7 +3313,7 @@
         <v>41</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3339,7 +3342,7 @@
         <v>42</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3368,7 +3371,7 @@
         <v>55</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3397,7 +3400,7 @@
         <v>43</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3426,7 +3429,7 @@
         <v>44</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3455,7 +3458,7 @@
         <v>45</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>13</v>
@@ -3484,7 +3487,7 @@
         <v>46</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3513,7 +3516,7 @@
         <v>47</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3542,7 +3545,7 @@
         <v>48</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3571,7 +3574,7 @@
         <v>50</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>13</v>
@@ -3600,7 +3603,7 @@
         <v>51</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>13</v>
@@ -3629,7 +3632,7 @@
         <v>52</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3658,7 +3661,7 @@
         <v>53</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3687,7 +3690,7 @@
         <v>41</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3716,7 +3719,7 @@
         <v>42</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3745,7 +3748,7 @@
         <v>55</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3774,7 +3777,7 @@
         <v>43</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -3803,7 +3806,7 @@
         <v>44</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3832,7 +3835,7 @@
         <v>45</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3861,7 +3864,7 @@
         <v>46</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -3890,7 +3893,7 @@
         <v>48</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -3919,7 +3922,7 @@
         <v>50</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3948,7 +3951,7 @@
         <v>51</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -3977,7 +3980,7 @@
         <v>52</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4006,7 +4009,7 @@
         <v>53</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4035,7 +4038,7 @@
         <v>41</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>12</v>
@@ -4059,7 +4062,7 @@
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
       <c r="M127" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
@@ -4073,7 +4076,7 @@
         <v>42</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4102,7 +4105,7 @@
         <v>55</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4131,7 +4134,7 @@
         <v>43</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>10</v>
@@ -4160,7 +4163,7 @@
         <v>44</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4189,7 +4192,7 @@
         <v>45</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>14</v>
@@ -4213,7 +4216,7 @@
       <c r="J133" s="2"/>
       <c r="K133" s="1"/>
       <c r="M133" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
@@ -4227,7 +4230,7 @@
         <v>46</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4256,7 +4259,7 @@
         <v>56</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>12</v>
@@ -4280,7 +4283,7 @@
       <c r="J136" s="2"/>
       <c r="K136" s="1"/>
       <c r="M136" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
@@ -4294,7 +4297,7 @@
         <v>48</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4323,7 +4326,7 @@
         <v>57</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4352,7 +4355,7 @@
         <v>51</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4381,7 +4384,7 @@
         <v>52</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>12</v>
@@ -4405,7 +4408,7 @@
       <c r="J141" s="2"/>
       <c r="K141" s="1"/>
       <c r="M141" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
@@ -4419,7 +4422,7 @@
         <v>53</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>10</v>
@@ -4448,7 +4451,7 @@
         <v>41</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4477,7 +4480,7 @@
         <v>42</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4506,7 +4509,7 @@
         <v>55</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4535,7 +4538,7 @@
         <v>43</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4564,7 +4567,7 @@
         <v>44</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -4593,7 +4596,7 @@
         <v>45</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>10</v>
@@ -4622,7 +4625,7 @@
         <v>46</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -4651,7 +4654,7 @@
         <v>56</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>12</v>
@@ -4675,7 +4678,7 @@
       <c r="J151" s="2"/>
       <c r="K151" s="1"/>
       <c r="M151" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
@@ -4689,7 +4692,7 @@
         <v>48</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>10</v>
@@ -4718,7 +4721,7 @@
         <v>57</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>10</v>
@@ -4747,7 +4750,7 @@
         <v>51</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>13</v>
@@ -4776,7 +4779,7 @@
         <v>52</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>12</v>
@@ -4800,7 +4803,7 @@
       <c r="J156" s="2"/>
       <c r="K156" s="1"/>
       <c r="M156" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
@@ -4814,7 +4817,7 @@
         <v>53</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -4843,7 +4846,7 @@
         <v>41</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>10</v>
@@ -4872,7 +4875,7 @@
         <v>42</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -4901,7 +4904,7 @@
         <v>43</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -4930,7 +4933,7 @@
         <v>44</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>10</v>
@@ -4959,7 +4962,7 @@
         <v>45</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>12</v>
@@ -4983,7 +4986,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
       <c r="M163" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -4997,7 +5000,7 @@
         <v>46</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>10</v>
@@ -5026,7 +5029,7 @@
         <v>56</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>10</v>
@@ -5055,7 +5058,7 @@
         <v>48</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>10</v>
@@ -5084,7 +5087,7 @@
         <v>57</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>10</v>
@@ -5113,7 +5116,7 @@
         <v>51</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>13</v>
@@ -5142,7 +5145,7 @@
         <v>52</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>12</v>
@@ -5166,7 +5169,7 @@
       <c r="J170" s="2"/>
       <c r="K170" s="1"/>
       <c r="M170" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.3">
@@ -5180,7 +5183,7 @@
         <v>53</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>13</v>
@@ -5209,7 +5212,7 @@
         <v>41</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5238,7 +5241,7 @@
         <v>42</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>13</v>
@@ -5267,7 +5270,7 @@
         <v>43</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>10</v>
@@ -5296,7 +5299,7 @@
         <v>44</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5325,7 +5328,7 @@
         <v>45</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>10</v>
@@ -5354,7 +5357,7 @@
         <v>46</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -5383,7 +5386,7 @@
         <v>56</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5412,7 +5415,7 @@
         <v>48</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5441,7 +5444,7 @@
         <v>57</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>10</v>
@@ -5470,7 +5473,7 @@
         <v>51</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5499,7 +5502,7 @@
         <v>52</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -5528,7 +5531,7 @@
         <v>53</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -6253,7 +6256,7 @@
         <v>41</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -6282,7 +6285,7 @@
         <v>42</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6311,7 +6314,7 @@
         <v>43</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>10</v>
@@ -6340,7 +6343,7 @@
         <v>44</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6369,7 +6372,7 @@
         <v>58</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6398,7 +6401,7 @@
         <v>45</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>13</v>
@@ -6427,7 +6430,7 @@
         <v>46</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>12</v>
@@ -6451,7 +6454,7 @@
       <c r="J215" s="2"/>
       <c r="K215" s="1"/>
       <c r="M215" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
@@ -6465,7 +6468,7 @@
         <v>56</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6494,7 +6497,7 @@
         <v>48</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6523,7 +6526,7 @@
         <v>57</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6552,7 +6555,7 @@
         <v>51</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6581,7 +6584,7 @@
         <v>52</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -6610,7 +6613,7 @@
         <v>53</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>10</v>
@@ -6639,7 +6642,7 @@
         <v>41</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6668,7 +6671,7 @@
         <v>42</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>13</v>
@@ -6697,7 +6700,7 @@
         <v>43</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6726,7 +6729,7 @@
         <v>44</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>10</v>
@@ -6755,7 +6758,7 @@
         <v>59</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>10</v>
@@ -6784,7 +6787,7 @@
         <v>45</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -6813,7 +6816,7 @@
         <v>46</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -6842,7 +6845,7 @@
         <v>56</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -6871,7 +6874,7 @@
         <v>48</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -6900,7 +6903,7 @@
         <v>57</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -6929,7 +6932,7 @@
         <v>51</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -6958,7 +6961,7 @@
         <v>52</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -6987,7 +6990,7 @@
         <v>53</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -7388,7 +7391,7 @@
       <c r="J248" s="2"/>
       <c r="K248" s="1"/>
       <c r="M248" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
@@ -7431,7 +7434,7 @@
         <v>41</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>14</v>
@@ -7455,7 +7458,7 @@
       <c r="J251" s="2"/>
       <c r="K251" s="1"/>
       <c r="M251" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
@@ -7469,7 +7472,7 @@
         <v>42</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7498,7 +7501,7 @@
         <v>43</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -7527,7 +7530,7 @@
         <v>44</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7556,7 +7559,7 @@
         <v>60</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7585,7 +7588,7 @@
         <v>59</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>13</v>
@@ -7614,7 +7617,7 @@
         <v>45</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7643,7 +7646,7 @@
         <v>46</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -7672,7 +7675,7 @@
         <v>61</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>10</v>
@@ -7701,7 +7704,7 @@
         <v>56</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>10</v>
@@ -7730,7 +7733,7 @@
         <v>48</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7759,7 +7762,7 @@
         <v>51</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -7788,7 +7791,7 @@
         <v>52</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>12</v>
@@ -7812,7 +7815,7 @@
       <c r="J264" s="2"/>
       <c r="K264" s="1"/>
       <c r="M264" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
@@ -7826,7 +7829,7 @@
         <v>53</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>10</v>
@@ -7855,7 +7858,7 @@
         <v>41</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>12</v>
@@ -7879,7 +7882,7 @@
       <c r="J267" s="2"/>
       <c r="K267" s="1"/>
       <c r="M267" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
@@ -7893,7 +7896,7 @@
         <v>42</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -7922,7 +7925,7 @@
         <v>43</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -7951,7 +7954,7 @@
         <v>44</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>10</v>
@@ -7980,7 +7983,7 @@
         <v>60</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -8009,7 +8012,7 @@
         <v>59</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>13</v>
@@ -8038,7 +8041,7 @@
         <v>45</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -8067,7 +8070,7 @@
         <v>46</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>12</v>
@@ -8091,7 +8094,7 @@
       <c r="J275" s="2"/>
       <c r="K275" s="1"/>
       <c r="M275" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
@@ -8105,7 +8108,7 @@
         <v>61</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>10</v>
@@ -8134,7 +8137,7 @@
         <v>56</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>10</v>
@@ -8163,7 +8166,7 @@
         <v>48</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -8192,7 +8195,7 @@
         <v>51</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8221,7 +8224,7 @@
         <v>52</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>13</v>
@@ -8250,7 +8253,7 @@
         <v>53</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8279,7 +8282,7 @@
         <v>41</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>14</v>
@@ -8303,7 +8306,7 @@
       <c r="J283" s="2"/>
       <c r="K283" s="1"/>
       <c r="M283" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
@@ -8317,7 +8320,7 @@
         <v>43</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>10</v>
@@ -8346,7 +8349,7 @@
         <v>44</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>10</v>
@@ -8375,7 +8378,7 @@
         <v>60</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>10</v>
@@ -8404,7 +8407,7 @@
         <v>45</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>10</v>
@@ -8433,7 +8436,7 @@
         <v>46</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>10</v>
@@ -8462,7 +8465,7 @@
         <v>61</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -8491,7 +8494,7 @@
         <v>56</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>10</v>
@@ -8520,7 +8523,7 @@
         <v>48</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>10</v>
@@ -8549,7 +8552,7 @@
         <v>52</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>13</v>
@@ -8578,7 +8581,7 @@
         <v>53</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>10</v>
@@ -8607,7 +8610,7 @@
         <v>41</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8636,7 +8639,7 @@
         <v>43</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>10</v>
@@ -8665,7 +8668,7 @@
         <v>44</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8694,7 +8697,7 @@
         <v>60</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>10</v>
@@ -8723,7 +8726,7 @@
         <v>45</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -8752,7 +8755,7 @@
         <v>46</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -8781,7 +8784,7 @@
         <v>61</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>10</v>
@@ -8810,7 +8813,7 @@
         <v>56</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>12</v>
@@ -8834,7 +8837,7 @@
       <c r="J302" s="2"/>
       <c r="K302" s="1"/>
       <c r="M302" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.3">
@@ -8848,7 +8851,7 @@
         <v>48</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>10</v>
@@ -8877,7 +8880,7 @@
         <v>52</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>13</v>
@@ -8906,7 +8909,7 @@
         <v>53</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -8935,7 +8938,7 @@
         <v>41</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -8964,7 +8967,7 @@
         <v>43</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>10</v>
@@ -8993,7 +8996,7 @@
         <v>44</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>10</v>
@@ -9022,7 +9025,7 @@
         <v>60</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>10</v>
@@ -9051,7 +9054,7 @@
         <v>45</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>10</v>
@@ -9080,7 +9083,7 @@
         <v>46</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>12</v>
@@ -9104,7 +9107,7 @@
       <c r="J312" s="2"/>
       <c r="K312" s="1"/>
       <c r="M312" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313" spans="4:13" x14ac:dyDescent="0.3">
@@ -9118,7 +9121,7 @@
         <v>61</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>10</v>
@@ -9147,7 +9150,7 @@
         <v>56</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>14</v>
@@ -9171,7 +9174,7 @@
       <c r="J315" s="2"/>
       <c r="K315" s="1"/>
       <c r="M315" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
@@ -9185,7 +9188,7 @@
         <v>48</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>10</v>
@@ -9214,7 +9217,7 @@
         <v>52</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>13</v>
@@ -9243,7 +9246,7 @@
         <v>53</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -9272,7 +9275,7 @@
         <v>41</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>14</v>
@@ -9296,7 +9299,7 @@
       <c r="J320" s="2"/>
       <c r="K320" s="1"/>
       <c r="M320" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="321" spans="4:13" x14ac:dyDescent="0.3">
@@ -9310,7 +9313,7 @@
         <v>43</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>12</v>
@@ -9334,7 +9337,7 @@
       <c r="J322" s="2"/>
       <c r="K322" s="1"/>
       <c r="M322" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="323" spans="4:13" x14ac:dyDescent="0.3">
@@ -9348,7 +9351,7 @@
         <v>44</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>10</v>
@@ -9377,7 +9380,7 @@
         <v>60</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>10</v>
@@ -9406,7 +9409,7 @@
         <v>45</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>13</v>
@@ -9435,7 +9438,7 @@
         <v>46</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>10</v>
@@ -9464,7 +9467,7 @@
         <v>61</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>10</v>
@@ -9493,7 +9496,7 @@
         <v>56</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>13</v>
@@ -9522,7 +9525,7 @@
         <v>48</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9551,7 +9554,7 @@
         <v>52</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9580,7 +9583,7 @@
         <v>53</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9609,7 +9612,7 @@
         <v>41</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>14</v>
@@ -9633,7 +9636,7 @@
       <c r="J333" s="2"/>
       <c r="K333" s="1"/>
       <c r="M333" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334" spans="4:13" x14ac:dyDescent="0.3">
@@ -9647,7 +9650,7 @@
         <v>43</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>12</v>
@@ -9671,7 +9674,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
       <c r="M335" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
@@ -9685,7 +9688,7 @@
         <v>44</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -9714,7 +9717,7 @@
         <v>60</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>10</v>
@@ -9743,7 +9746,7 @@
         <v>45</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>10</v>
@@ -9772,7 +9775,7 @@
         <v>46</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -9801,7 +9804,7 @@
         <v>61</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -9830,7 +9833,7 @@
         <v>56</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>10</v>
@@ -9859,7 +9862,7 @@
         <v>48</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>10</v>
@@ -9888,7 +9891,7 @@
         <v>52</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -9917,7 +9920,7 @@
         <v>53</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>10</v>
@@ -9946,7 +9949,7 @@
         <v>41</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>10</v>
@@ -9975,7 +9978,7 @@
         <v>62</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -10004,7 +10007,7 @@
         <v>46</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -10033,7 +10036,7 @@
         <v>61</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>10</v>
@@ -10062,7 +10065,7 @@
         <v>43</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>10</v>
@@ -10091,7 +10094,7 @@
         <v>44</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>10</v>
@@ -10120,7 +10123,7 @@
         <v>60</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>10</v>
@@ -10149,7 +10152,7 @@
         <v>56</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>13</v>
@@ -10178,7 +10181,7 @@
         <v>48</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>10</v>
@@ -10207,7 +10210,7 @@
         <v>52</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>13</v>
@@ -10236,7 +10239,7 @@
         <v>53</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10265,7 +10268,7 @@
         <v>45</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -10284,168 +10287,447 @@
       </c>
     </row>
     <row r="357" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H357" s="2"/>
-      <c r="I357" s="1"/>
-      <c r="J357" s="2"/>
-      <c r="K357" s="1"/>
+      <c r="D357" t="s">
+        <v>40</v>
+      </c>
+      <c r="E357">
+        <v>1818</v>
+      </c>
+      <c r="F357" t="s">
+        <v>41</v>
+      </c>
+      <c r="H357" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I357" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J357" s="2">
+        <v>6.5393518518518517E-3</v>
+      </c>
+      <c r="K357" s="1">
+        <v>46219.688194444447</v>
+      </c>
+      <c r="L357">
+        <v>0</v>
+      </c>
+      <c r="M357" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="358" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H358" s="2"/>
-      <c r="I358" s="1"/>
-      <c r="J358" s="2"/>
-      <c r="K358" s="1"/>
+      <c r="D358" t="s">
+        <v>40</v>
+      </c>
+      <c r="E358">
+        <v>5587</v>
+      </c>
+      <c r="F358" t="s">
+        <v>62</v>
+      </c>
+      <c r="H358" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I358" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J358" s="2">
+        <v>0</v>
+      </c>
+      <c r="K358" s="1">
+        <v>46219.688888888886</v>
+      </c>
+      <c r="L358">
+        <v>0</v>
+      </c>
+      <c r="M358" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="359" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H359" s="2"/>
-      <c r="I359" s="1"/>
-      <c r="J359" s="2"/>
-      <c r="K359" s="1"/>
+      <c r="D359" t="s">
+        <v>40</v>
+      </c>
+      <c r="E359">
+        <v>1819</v>
+      </c>
+      <c r="F359" t="s">
+        <v>43</v>
+      </c>
+      <c r="H359" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I359" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J359" s="2">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="K359" s="1">
+        <v>46219.689583333333</v>
+      </c>
+      <c r="L359">
+        <v>0</v>
+      </c>
+      <c r="M359" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="360" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H360" s="2"/>
       <c r="I360" s="1"/>
       <c r="J360" s="2"/>
       <c r="K360" s="1"/>
+      <c r="M360" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="361" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H361" s="2"/>
-      <c r="I361" s="1"/>
-      <c r="J361" s="2"/>
-      <c r="K361" s="1"/>
+      <c r="D361" t="s">
+        <v>40</v>
+      </c>
+      <c r="E361">
+        <v>1815</v>
+      </c>
+      <c r="F361" t="s">
+        <v>44</v>
+      </c>
+      <c r="H361" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I361" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J361" s="2">
+        <v>0</v>
+      </c>
+      <c r="K361" s="1">
+        <v>46219.689583333333</v>
+      </c>
+      <c r="L361">
+        <v>0</v>
+      </c>
+      <c r="M361" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="362" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H362" s="2"/>
-      <c r="I362" s="1"/>
-      <c r="J362" s="2"/>
-      <c r="K362" s="1"/>
+      <c r="D362" t="s">
+        <v>40</v>
+      </c>
+      <c r="E362">
+        <v>4827</v>
+      </c>
+      <c r="F362" t="s">
+        <v>60</v>
+      </c>
+      <c r="H362" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I362" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J362" s="2">
+        <v>6.828703703703704E-3</v>
+      </c>
+      <c r="K362" s="1">
+        <v>46219.69027777778</v>
+      </c>
+      <c r="L362">
+        <v>0</v>
+      </c>
+      <c r="M362" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="363" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H363" s="2"/>
-      <c r="I363" s="1"/>
-      <c r="J363" s="2"/>
-      <c r="K363" s="1"/>
+      <c r="D363" t="s">
+        <v>40</v>
+      </c>
+      <c r="E363">
+        <v>1813</v>
+      </c>
+      <c r="F363" t="s">
+        <v>45</v>
+      </c>
+      <c r="H363" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I363" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J363" s="2">
+        <v>0</v>
+      </c>
+      <c r="K363" s="1">
+        <v>46219.690972222219</v>
+      </c>
+      <c r="L363">
+        <v>0</v>
+      </c>
+      <c r="M363" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="364" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H364" s="2"/>
-      <c r="I364" s="1"/>
-      <c r="J364" s="2"/>
-      <c r="K364" s="1"/>
+      <c r="D364" t="s">
+        <v>40</v>
+      </c>
+      <c r="E364">
+        <v>1812</v>
+      </c>
+      <c r="F364" t="s">
+        <v>46</v>
+      </c>
+      <c r="H364" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I364" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J364" s="2">
+        <v>0</v>
+      </c>
+      <c r="K364" s="1">
+        <v>46219.690972222219</v>
+      </c>
+      <c r="L364">
+        <v>0</v>
+      </c>
+      <c r="M364" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="365" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H365" s="2"/>
-      <c r="I365" s="1"/>
-      <c r="J365" s="2"/>
-      <c r="K365" s="1"/>
+      <c r="D365" t="s">
+        <v>40</v>
+      </c>
+      <c r="E365">
+        <v>4828</v>
+      </c>
+      <c r="F365" t="s">
+        <v>61</v>
+      </c>
+      <c r="H365" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I365" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J365" s="2">
+        <v>7.951388888888888E-3</v>
+      </c>
+      <c r="K365" s="1">
+        <v>46219.691666666666</v>
+      </c>
+      <c r="L365">
+        <v>0</v>
+      </c>
+      <c r="M365" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="366" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H366" s="2"/>
-      <c r="I366" s="1"/>
-      <c r="J366" s="2"/>
-      <c r="K366" s="1"/>
+      <c r="D366" t="s">
+        <v>40</v>
+      </c>
+      <c r="E366">
+        <v>1816</v>
+      </c>
+      <c r="F366" t="s">
+        <v>48</v>
+      </c>
+      <c r="H366" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I366" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J366" s="2">
+        <v>5.6597222222222222E-3</v>
+      </c>
+      <c r="K366" s="1">
+        <v>46219.692361111112</v>
+      </c>
+      <c r="L366">
+        <v>0</v>
+      </c>
+      <c r="M366" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="367" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H367" s="2"/>
-      <c r="I367" s="1"/>
-      <c r="J367" s="2"/>
-      <c r="K367" s="1"/>
+      <c r="D367" t="s">
+        <v>40</v>
+      </c>
+      <c r="E367">
+        <v>5882</v>
+      </c>
+      <c r="F367" t="s">
+        <v>63</v>
+      </c>
+      <c r="H367" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I367" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J367" s="2">
+        <v>0</v>
+      </c>
+      <c r="K367" s="1">
+        <v>46219.692361111112</v>
+      </c>
+      <c r="L367">
+        <v>0</v>
+      </c>
+      <c r="M367" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="368" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H368" s="2"/>
-      <c r="I368" s="1"/>
-      <c r="J368" s="2"/>
-      <c r="K368" s="1"/>
-    </row>
-    <row r="369" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H369" s="2"/>
-      <c r="I369" s="1"/>
-      <c r="J369" s="2"/>
-      <c r="K369" s="1"/>
-    </row>
-    <row r="370" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D368" t="s">
+        <v>40</v>
+      </c>
+      <c r="E368">
+        <v>1809</v>
+      </c>
+      <c r="F368" t="s">
+        <v>52</v>
+      </c>
+      <c r="H368" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I368" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J368" s="2">
+        <v>0</v>
+      </c>
+      <c r="K368" s="1">
+        <v>46219.693055555559</v>
+      </c>
+      <c r="L368">
+        <v>0</v>
+      </c>
+      <c r="M368" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="369" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D369" t="s">
+        <v>40</v>
+      </c>
+      <c r="E369">
+        <v>1817</v>
+      </c>
+      <c r="F369" t="s">
+        <v>53</v>
+      </c>
+      <c r="H369" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I369" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J369" s="2">
+        <v>0</v>
+      </c>
+      <c r="K369" s="1">
+        <v>46219.693749999999</v>
+      </c>
+      <c r="L369">
+        <v>0</v>
+      </c>
+      <c r="M369" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="370" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H370" s="2"/>
       <c r="I370" s="1"/>
       <c r="J370" s="2"/>
       <c r="K370" s="1"/>
     </row>
-    <row r="371" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H371" s="2"/>
       <c r="I371" s="1"/>
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
       <c r="K372" s="1"/>
     </row>
-    <row r="373" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H373" s="2"/>
       <c r="I373" s="1"/>
       <c r="J373" s="2"/>
       <c r="K373" s="1"/>
     </row>
-    <row r="374" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H374" s="2"/>
       <c r="I374" s="1"/>
       <c r="J374" s="2"/>
       <c r="K374" s="1"/>
     </row>
-    <row r="375" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H375" s="2"/>
       <c r="I375" s="1"/>
       <c r="J375" s="2"/>
       <c r="K375" s="1"/>
     </row>
-    <row r="376" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H376" s="2"/>
       <c r="I376" s="1"/>
       <c r="J376" s="2"/>
       <c r="K376" s="1"/>
     </row>
-    <row r="377" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H377" s="2"/>
       <c r="I377" s="1"/>
       <c r="J377" s="2"/>
       <c r="K377" s="1"/>
     </row>
-    <row r="378" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H378" s="2"/>
       <c r="I378" s="1"/>
       <c r="J378" s="2"/>
       <c r="K378" s="1"/>
     </row>
-    <row r="379" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H379" s="2"/>
       <c r="I379" s="1"/>
       <c r="J379" s="2"/>
       <c r="K379" s="1"/>
     </row>
-    <row r="380" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H380" s="2"/>
       <c r="I380" s="1"/>
       <c r="J380" s="2"/>
       <c r="K380" s="1"/>
     </row>
-    <row r="381" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H381" s="2"/>
       <c r="I381" s="1"/>
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
       <c r="K382" s="1"/>
     </row>
-    <row r="383" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H383" s="2"/>
       <c r="I383" s="1"/>
       <c r="J383" s="2"/>
       <c r="K383" s="1"/>
     </row>
-    <row r="384" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H384" s="2"/>
       <c r="I384" s="1"/>
       <c r="J384" s="2"/>
@@ -12832,6 +13114,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -12861,6 +13144,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -12926,6 +13210,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -12949,6 +13234,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -12966,6 +13252,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -12983,6 +13270,7 @@
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -13102,6 +13390,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -13185,6 +13474,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -13208,6 +13498,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -13219,6 +13510,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -13230,6 +13522,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -13277,6 +13570,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -13330,6 +13624,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -13502,6 +13797,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -13513,6 +13809,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -13590,6 +13887,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -13607,6 +13905,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -13654,6 +13953,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -13766,6 +14066,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -13825,6 +14126,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -13836,6 +14138,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -13907,6 +14210,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -13959,6 +14263,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -14035,11 +14340,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -14099,6 +14406,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -14110,6 +14418,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -14121,11 +14430,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -14179,6 +14490,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -14195,6 +14507,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -14218,6 +14531,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -14235,6 +14549,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -14281,11 +14596,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -14327,11 +14644,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -14349,6 +14668,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -14360,6 +14680,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -14371,6 +14692,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -14388,6 +14710,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -14465,6 +14788,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -14494,6 +14818,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -14505,16 +14830,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -14526,16 +14854,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -14547,11 +14878,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -14575,6 +14908,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -14616,6 +14950,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -14645,21 +14980,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -14671,6 +15010,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -14688,6 +15028,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -14727,11 +15068,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -14779,6 +15122,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -14808,6 +15152,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -14884,6 +15229,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -14930,6 +15276,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -14965,11 +15312,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -14986,6 +15335,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -14996,6 +15346,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -15031,6 +15382,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -15042,6 +15394,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -15053,6 +15406,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -15064,6 +15418,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -15075,6 +15430,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -15116,6 +15472,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -15133,6 +15490,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -15150,6 +15508,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -15191,6 +15550,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -15214,6 +15574,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -15260,6 +15621,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -15295,6 +15657,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -15318,6 +15681,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -15358,6 +15722,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -15375,11 +15740,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -15438,6 +15805,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -15454,6 +15822,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -15465,6 +15834,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -15476,11 +15846,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -15516,6 +15888,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -15568,6 +15941,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -15578,6 +15952,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -15593,6 +15968,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -15616,16 +15992,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -15696,6 +16075,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -15707,6 +16087,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -15807,6 +16188,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -15863,6 +16246,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -15886,6 +16270,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -16010,6 +16395,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -16168,6 +16554,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -16185,6 +16572,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -16225,6 +16613,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -16557,6 +16946,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -16645,6 +17035,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -16738,6 +17129,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -16797,11 +17189,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -16853,6 +17247,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -16894,6 +17289,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -16938,6 +17334,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -16984,11 +17381,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -17186,6 +17585,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -17215,6 +17615,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -17230,6 +17632,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -17289,6 +17692,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -17360,6 +17764,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -17401,6 +17806,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -17519,6 +17925,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -17583,6 +17990,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -17707,6 +18115,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -17933,6 +18342,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -18050,6 +18460,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -18133,6 +18544,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -18192,6 +18604,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -18215,6 +18628,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -18262,6 +18676,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -18321,6 +18736,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -18344,6 +18760,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -18361,6 +18778,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -18444,6 +18862,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -18635,6 +19054,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -46491,6 +46911,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -46498,6 +46919,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -46505,6 +46927,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -46520,6 +46943,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -46529,6 +46953,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -46536,9 +46961,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -46546,12 +46977,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -46559,12 +46993,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -46576,9 +47013,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -46593,6 +47032,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -46619,6 +47059,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -46629,7 +47070,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -46637,6 +47083,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -46648,6 +47095,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -46655,6 +47103,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -46669,13 +47118,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -46686,15 +47141,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -46710,6 +47168,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -46728,6 +47187,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -46739,6 +47199,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -46756,18 +47217,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -46796,6 +47262,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -46803,9 +47270,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -46828,12 +47297,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -46848,9 +47320,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -46866,12 +47340,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -46892,6 +47368,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -46903,9 +47380,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -46917,6 +47396,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -46956,9 +47436,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -46966,9 +47448,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -46979,6 +47463,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -46986,18 +47471,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -47005,6 +47498,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -47015,6 +47509,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -47041,15 +47536,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -47071,6 +47570,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -47078,9 +47578,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -47088,6 +47590,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -47099,6 +47602,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -47113,6 +47617,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -47122,6 +47630,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -47133,6 +47642,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -47143,10 +47653,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -47154,6 +47669,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -47168,6 +47684,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -47190,6 +47707,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -47209,25 +47727,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -47235,6 +47765,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -47242,15 +47773,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -47264,6 +47802,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -47282,9 +47821,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -47292,9 +47833,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -47302,6 +47845,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -47318,10 +47862,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38B67885-2AE4-4987-BC23-2EB65EA69130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F57971E-9E07-494B-9867-5D0BE7182731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="72">
   <si>
     <t>Company Name</t>
   </si>
@@ -134,6 +134,9 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
+    <t>Dangers of Distracted Driving</t>
+  </si>
+  <si>
     <t>Scene of an Accident</t>
   </si>
   <si>
@@ -141,9 +144,6 @@
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
-  </si>
-  <si>
-    <t>3 points of contact</t>
   </si>
   <si>
     <t>Micro-Learn Safe Following Distance</t>
@@ -158,7 +158,7 @@
     <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
-    <t>Dustin Smith</t>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>DNUNEW-Space Management Big 5</t>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>Alonzo Soto</t>
+  </si>
+  <si>
+    <t>Dustin Smith</t>
   </si>
   <si>
     <t>Ed Smith</t>
@@ -231,6 +234,27 @@
   </si>
   <si>
     <t>Mike Moreno</t>
+  </si>
+  <si>
+    <t>Bradley Johnson</t>
+  </si>
+  <si>
+    <t>Brian Longbine</t>
+  </si>
+  <si>
+    <t>Joseph Pruiett</t>
+  </si>
+  <si>
+    <t>Josue Faz Pina</t>
+  </si>
+  <si>
+    <t>Lorenzo Sanchez</t>
+  </si>
+  <si>
+    <t>Luis Martinez</t>
+  </si>
+  <si>
+    <t>Richard Killam Rivera</t>
   </si>
 </sst>
 </file>
@@ -604,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -619,39 +643,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>41</v>
       </c>
@@ -680,7 +704,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -709,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>41</v>
       </c>
@@ -717,7 +741,7 @@
         <v>1819</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
         <v>37</v>
@@ -738,7 +762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>41</v>
       </c>
@@ -746,7 +770,7 @@
         <v>1815</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
         <v>37</v>
@@ -767,7 +791,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>41</v>
       </c>
@@ -775,7 +799,7 @@
         <v>1813</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
         <v>37</v>
@@ -796,7 +820,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="J7" s="2"/>
@@ -804,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>41</v>
       </c>
@@ -812,7 +836,7 @@
         <v>1812</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
         <v>37</v>
@@ -833,7 +857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>41</v>
       </c>
@@ -841,7 +865,7 @@
         <v>1814</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
         <v>37</v>
@@ -862,7 +886,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>41</v>
       </c>
@@ -870,7 +894,7 @@
         <v>1816</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
         <v>37</v>
@@ -891,7 +915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>41</v>
       </c>
@@ -899,7 +923,7 @@
         <v>1820</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
         <v>37</v>
@@ -920,7 +944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>41</v>
       </c>
@@ -928,7 +952,7 @@
         <v>1821</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
         <v>37</v>
@@ -949,7 +973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>41</v>
       </c>
@@ -957,7 +981,7 @@
         <v>1811</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
         <v>37</v>
@@ -978,7 +1002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H14" s="2"/>
       <c r="I14" s="1"/>
       <c r="J14" s="2"/>
@@ -986,7 +1010,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>41</v>
       </c>
@@ -994,7 +1018,7 @@
         <v>1809</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
         <v>37</v>
@@ -1015,7 +1039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H16" s="2"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2"/>
@@ -1031,7 +1055,7 @@
         <v>1786</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
         <v>37</v>
@@ -1060,7 +1084,7 @@
         <v>1817</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
         <v>37</v>
@@ -1147,7 +1171,7 @@
         <v>1888</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
         <v>36</v>
@@ -1184,7 +1208,7 @@
         <v>1819</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
         <v>36</v>
@@ -1213,7 +1237,7 @@
         <v>1815</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>36</v>
@@ -1242,7 +1266,7 @@
         <v>1813</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F25" t="s">
         <v>36</v>
@@ -1279,7 +1303,7 @@
         <v>1812</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s">
         <v>36</v>
@@ -1308,7 +1332,7 @@
         <v>1814</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F28" t="s">
         <v>36</v>
@@ -1337,7 +1361,7 @@
         <v>1816</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s">
         <v>36</v>
@@ -1366,7 +1390,7 @@
         <v>1821</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
         <v>36</v>
@@ -1403,7 +1427,7 @@
         <v>1811</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s">
         <v>36</v>
@@ -1432,7 +1456,7 @@
         <v>1809</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
         <v>36</v>
@@ -1469,7 +1493,7 @@
         <v>1786</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
         <v>36</v>
@@ -1506,7 +1530,7 @@
         <v>1817</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F37" t="s">
         <v>36</v>
@@ -1601,7 +1625,7 @@
         <v>1888</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
         <v>40</v>
@@ -1630,7 +1654,7 @@
         <v>1819</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F42" t="s">
         <v>40</v>
@@ -1667,7 +1691,7 @@
         <v>1815</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F44" t="s">
         <v>40</v>
@@ -1696,7 +1720,7 @@
         <v>1813</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F45" t="s">
         <v>40</v>
@@ -1725,7 +1749,7 @@
         <v>1812</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F46" t="s">
         <v>40</v>
@@ -1754,7 +1778,7 @@
         <v>1814</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F47" t="s">
         <v>40</v>
@@ -1783,7 +1807,7 @@
         <v>1816</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F48" t="s">
         <v>40</v>
@@ -1812,7 +1836,7 @@
         <v>1821</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F49" t="s">
         <v>40</v>
@@ -1841,7 +1865,7 @@
         <v>1811</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F50" t="s">
         <v>40</v>
@@ -1870,7 +1894,7 @@
         <v>1809</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F51" t="s">
         <v>40</v>
@@ -1899,7 +1923,7 @@
         <v>1817</v>
       </c>
       <c r="D52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F52" t="s">
         <v>40</v>
@@ -1994,7 +2018,7 @@
         <v>1888</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
@@ -2023,7 +2047,7 @@
         <v>1819</v>
       </c>
       <c r="D57" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
@@ -2052,7 +2076,7 @@
         <v>1815</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
@@ -2081,7 +2105,7 @@
         <v>1813</v>
       </c>
       <c r="D59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
@@ -2110,7 +2134,7 @@
         <v>1821</v>
       </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
@@ -2139,7 +2163,7 @@
         <v>1811</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
@@ -2168,7 +2192,7 @@
         <v>1817</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
@@ -2200,7 +2224,7 @@
         <v>42</v>
       </c>
       <c r="F63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G63" t="s">
         <v>13</v>
@@ -2229,7 +2253,7 @@
         <v>43</v>
       </c>
       <c r="F64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G64" t="s">
         <v>13</v>
@@ -2255,10 +2279,10 @@
         <v>1888</v>
       </c>
       <c r="D65" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G65" t="s">
         <v>13</v>
@@ -2284,10 +2308,10 @@
         <v>1819</v>
       </c>
       <c r="D66" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2313,10 +2337,10 @@
         <v>1815</v>
       </c>
       <c r="D67" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F67" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2342,10 +2366,10 @@
         <v>1813</v>
       </c>
       <c r="D68" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G68" t="s">
         <v>13</v>
@@ -2371,10 +2395,10 @@
         <v>1812</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G69" t="s">
         <v>10</v>
@@ -2400,10 +2424,10 @@
         <v>1814</v>
       </c>
       <c r="D70" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G70" t="s">
         <v>10</v>
@@ -2429,10 +2453,10 @@
         <v>1816</v>
       </c>
       <c r="D71" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2458,10 +2482,10 @@
         <v>1821</v>
       </c>
       <c r="D72" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F72" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
@@ -2487,10 +2511,10 @@
         <v>1811</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G73" t="s">
         <v>13</v>
@@ -2516,10 +2540,10 @@
         <v>1809</v>
       </c>
       <c r="D74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2545,10 +2569,10 @@
         <v>1817</v>
       </c>
       <c r="D75" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -2632,7 +2656,7 @@
         <v>1819</v>
       </c>
       <c r="D78" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
@@ -2661,7 +2685,7 @@
         <v>1815</v>
       </c>
       <c r="D79" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F79" t="s">
         <v>16</v>
@@ -2690,7 +2714,7 @@
         <v>1813</v>
       </c>
       <c r="D80" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F80" t="s">
         <v>16</v>
@@ -2719,7 +2743,7 @@
         <v>1812</v>
       </c>
       <c r="D81" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F81" t="s">
         <v>16</v>
@@ -2748,7 +2772,7 @@
         <v>1814</v>
       </c>
       <c r="D82" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F82" t="s">
         <v>16</v>
@@ -2777,7 +2801,7 @@
         <v>1816</v>
       </c>
       <c r="D83" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
@@ -2806,7 +2830,7 @@
         <v>1821</v>
       </c>
       <c r="D84" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F84" t="s">
         <v>16</v>
@@ -2835,7 +2859,7 @@
         <v>1811</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F85" t="s">
         <v>16</v>
@@ -2864,7 +2888,7 @@
         <v>1809</v>
       </c>
       <c r="D86" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F86" t="s">
         <v>16</v>
@@ -2893,7 +2917,7 @@
         <v>1817</v>
       </c>
       <c r="D87" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F87" t="s">
         <v>16</v>
@@ -2980,7 +3004,7 @@
         <v>2770</v>
       </c>
       <c r="D90" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F90" t="s">
         <v>18</v>
@@ -3009,7 +3033,7 @@
         <v>1819</v>
       </c>
       <c r="D91" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F91" t="s">
         <v>18</v>
@@ -3038,7 +3062,7 @@
         <v>1815</v>
       </c>
       <c r="D92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F92" t="s">
         <v>18</v>
@@ -3067,7 +3091,7 @@
         <v>1813</v>
       </c>
       <c r="D93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F93" t="s">
         <v>18</v>
@@ -3096,7 +3120,7 @@
         <v>1812</v>
       </c>
       <c r="D94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F94" t="s">
         <v>18</v>
@@ -3125,7 +3149,7 @@
         <v>1814</v>
       </c>
       <c r="D95" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F95" t="s">
         <v>18</v>
@@ -3154,7 +3178,7 @@
         <v>1816</v>
       </c>
       <c r="D96" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F96" t="s">
         <v>18</v>
@@ -3183,7 +3207,7 @@
         <v>1821</v>
       </c>
       <c r="D97" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F97" t="s">
         <v>18</v>
@@ -3212,7 +3236,7 @@
         <v>1811</v>
       </c>
       <c r="D98" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F98" t="s">
         <v>18</v>
@@ -3241,7 +3265,7 @@
         <v>1809</v>
       </c>
       <c r="D99" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F99" t="s">
         <v>18</v>
@@ -3270,7 +3294,7 @@
         <v>1817</v>
       </c>
       <c r="D100" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F100" t="s">
         <v>18</v>
@@ -3357,7 +3381,7 @@
         <v>2770</v>
       </c>
       <c r="D103" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F103" t="s">
         <v>19</v>
@@ -3386,7 +3410,7 @@
         <v>1819</v>
       </c>
       <c r="D104" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F104" t="s">
         <v>19</v>
@@ -3415,7 +3439,7 @@
         <v>1815</v>
       </c>
       <c r="D105" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F105" t="s">
         <v>19</v>
@@ -3444,7 +3468,7 @@
         <v>1813</v>
       </c>
       <c r="D106" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F106" t="s">
         <v>19</v>
@@ -3473,7 +3497,7 @@
         <v>1812</v>
       </c>
       <c r="D107" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F107" t="s">
         <v>19</v>
@@ -3502,7 +3526,7 @@
         <v>1814</v>
       </c>
       <c r="D108" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F108" t="s">
         <v>19</v>
@@ -3531,7 +3555,7 @@
         <v>1816</v>
       </c>
       <c r="D109" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F109" t="s">
         <v>19</v>
@@ -3560,7 +3584,7 @@
         <v>1821</v>
       </c>
       <c r="D110" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F110" t="s">
         <v>19</v>
@@ -3589,7 +3613,7 @@
         <v>1811</v>
       </c>
       <c r="D111" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F111" t="s">
         <v>19</v>
@@ -3618,7 +3642,7 @@
         <v>1809</v>
       </c>
       <c r="D112" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F112" t="s">
         <v>19</v>
@@ -3647,7 +3671,7 @@
         <v>1817</v>
       </c>
       <c r="D113" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F113" t="s">
         <v>19</v>
@@ -3734,7 +3758,7 @@
         <v>2770</v>
       </c>
       <c r="D116" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F116" t="s">
         <v>20</v>
@@ -3763,7 +3787,7 @@
         <v>1819</v>
       </c>
       <c r="D117" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F117" t="s">
         <v>20</v>
@@ -3792,7 +3816,7 @@
         <v>1815</v>
       </c>
       <c r="D118" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F118" t="s">
         <v>20</v>
@@ -3821,7 +3845,7 @@
         <v>1813</v>
       </c>
       <c r="D119" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F119" t="s">
         <v>20</v>
@@ -3850,7 +3874,7 @@
         <v>1812</v>
       </c>
       <c r="D120" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F120" t="s">
         <v>20</v>
@@ -3879,7 +3903,7 @@
         <v>1816</v>
       </c>
       <c r="D121" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F121" t="s">
         <v>20</v>
@@ -3908,7 +3932,7 @@
         <v>1821</v>
       </c>
       <c r="D122" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F122" t="s">
         <v>20</v>
@@ -3937,7 +3961,7 @@
         <v>1811</v>
       </c>
       <c r="D123" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F123" t="s">
         <v>20</v>
@@ -3966,7 +3990,7 @@
         <v>1809</v>
       </c>
       <c r="D124" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F124" t="s">
         <v>20</v>
@@ -3995,7 +4019,7 @@
         <v>1817</v>
       </c>
       <c r="D125" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F125" t="s">
         <v>20</v>
@@ -4090,7 +4114,7 @@
         <v>2770</v>
       </c>
       <c r="D129" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F129" t="s">
         <v>22</v>
@@ -4119,7 +4143,7 @@
         <v>1819</v>
       </c>
       <c r="D130" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F130" t="s">
         <v>22</v>
@@ -4148,7 +4172,7 @@
         <v>1815</v>
       </c>
       <c r="D131" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F131" t="s">
         <v>22</v>
@@ -4177,7 +4201,7 @@
         <v>1813</v>
       </c>
       <c r="D132" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F132" t="s">
         <v>22</v>
@@ -4214,7 +4238,7 @@
         <v>1812</v>
       </c>
       <c r="D134" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F134" t="s">
         <v>22</v>
@@ -4243,7 +4267,7 @@
         <v>3125</v>
       </c>
       <c r="D135" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F135" t="s">
         <v>22</v>
@@ -4280,7 +4304,7 @@
         <v>1816</v>
       </c>
       <c r="D137" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F137" t="s">
         <v>22</v>
@@ -4309,7 +4333,7 @@
         <v>3126</v>
       </c>
       <c r="D138" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F138" t="s">
         <v>22</v>
@@ -4338,7 +4362,7 @@
         <v>1811</v>
       </c>
       <c r="D139" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F139" t="s">
         <v>22</v>
@@ -4367,7 +4391,7 @@
         <v>1809</v>
       </c>
       <c r="D140" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F140" t="s">
         <v>22</v>
@@ -4404,7 +4428,7 @@
         <v>1817</v>
       </c>
       <c r="D142" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F142" t="s">
         <v>22</v>
@@ -4491,7 +4515,7 @@
         <v>2770</v>
       </c>
       <c r="D145" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F145" t="s">
         <v>17</v>
@@ -4520,7 +4544,7 @@
         <v>1819</v>
       </c>
       <c r="D146" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F146" t="s">
         <v>17</v>
@@ -4549,7 +4573,7 @@
         <v>1815</v>
       </c>
       <c r="D147" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F147" t="s">
         <v>17</v>
@@ -4578,7 +4602,7 @@
         <v>1813</v>
       </c>
       <c r="D148" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F148" t="s">
         <v>17</v>
@@ -4607,7 +4631,7 @@
         <v>1812</v>
       </c>
       <c r="D149" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F149" t="s">
         <v>17</v>
@@ -4636,7 +4660,7 @@
         <v>3125</v>
       </c>
       <c r="D150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F150" t="s">
         <v>17</v>
@@ -4673,7 +4697,7 @@
         <v>1816</v>
       </c>
       <c r="D152" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F152" t="s">
         <v>17</v>
@@ -4702,7 +4726,7 @@
         <v>3126</v>
       </c>
       <c r="D153" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F153" t="s">
         <v>17</v>
@@ -4731,7 +4755,7 @@
         <v>1811</v>
       </c>
       <c r="D154" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F154" t="s">
         <v>17</v>
@@ -4760,7 +4784,7 @@
         <v>1809</v>
       </c>
       <c r="D155" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F155" t="s">
         <v>17</v>
@@ -4797,7 +4821,7 @@
         <v>1817</v>
       </c>
       <c r="D157" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F157" t="s">
         <v>17</v>
@@ -4884,7 +4908,7 @@
         <v>1819</v>
       </c>
       <c r="D160" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F160" t="s">
         <v>21</v>
@@ -4913,7 +4937,7 @@
         <v>1815</v>
       </c>
       <c r="D161" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F161" t="s">
         <v>21</v>
@@ -4942,7 +4966,7 @@
         <v>1813</v>
       </c>
       <c r="D162" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F162" t="s">
         <v>21</v>
@@ -4979,7 +5003,7 @@
         <v>1812</v>
       </c>
       <c r="D164" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F164" t="s">
         <v>21</v>
@@ -5008,7 +5032,7 @@
         <v>3125</v>
       </c>
       <c r="D165" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F165" t="s">
         <v>21</v>
@@ -5037,7 +5061,7 @@
         <v>1816</v>
       </c>
       <c r="D166" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F166" t="s">
         <v>21</v>
@@ -5066,7 +5090,7 @@
         <v>3126</v>
       </c>
       <c r="D167" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F167" t="s">
         <v>21</v>
@@ -5095,7 +5119,7 @@
         <v>1811</v>
       </c>
       <c r="D168" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F168" t="s">
         <v>21</v>
@@ -5124,7 +5148,7 @@
         <v>1809</v>
       </c>
       <c r="D169" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F169" t="s">
         <v>21</v>
@@ -5161,7 +5185,7 @@
         <v>1817</v>
       </c>
       <c r="D171" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F171" t="s">
         <v>21</v>
@@ -5248,7 +5272,7 @@
         <v>1819</v>
       </c>
       <c r="D174" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F174" t="s">
         <v>23</v>
@@ -5277,7 +5301,7 @@
         <v>1815</v>
       </c>
       <c r="D175" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F175" t="s">
         <v>23</v>
@@ -5306,7 +5330,7 @@
         <v>1813</v>
       </c>
       <c r="D176" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F176" t="s">
         <v>23</v>
@@ -5335,7 +5359,7 @@
         <v>1812</v>
       </c>
       <c r="D177" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F177" t="s">
         <v>23</v>
@@ -5364,7 +5388,7 @@
         <v>3125</v>
       </c>
       <c r="D178" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F178" t="s">
         <v>23</v>
@@ -5393,7 +5417,7 @@
         <v>1816</v>
       </c>
       <c r="D179" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F179" t="s">
         <v>23</v>
@@ -5422,7 +5446,7 @@
         <v>3126</v>
       </c>
       <c r="D180" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F180" t="s">
         <v>23</v>
@@ -5451,7 +5475,7 @@
         <v>1811</v>
       </c>
       <c r="D181" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F181" t="s">
         <v>23</v>
@@ -5480,7 +5504,7 @@
         <v>1809</v>
       </c>
       <c r="D182" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F182" t="s">
         <v>23</v>
@@ -5509,7 +5533,7 @@
         <v>1817</v>
       </c>
       <c r="D183" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F183" t="s">
         <v>23</v>
@@ -5596,7 +5620,7 @@
         <v>1819</v>
       </c>
       <c r="D186" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F186" t="s">
         <v>38</v>
@@ -5625,7 +5649,7 @@
         <v>1815</v>
       </c>
       <c r="D187" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F187" t="s">
         <v>38</v>
@@ -5654,7 +5678,7 @@
         <v>1813</v>
       </c>
       <c r="D188" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F188" t="s">
         <v>38</v>
@@ -5683,7 +5707,7 @@
         <v>1812</v>
       </c>
       <c r="D189" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F189" t="s">
         <v>38</v>
@@ -5712,7 +5736,7 @@
         <v>3125</v>
       </c>
       <c r="D190" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F190" t="s">
         <v>38</v>
@@ -5741,7 +5765,7 @@
         <v>1816</v>
       </c>
       <c r="D191" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F191" t="s">
         <v>38</v>
@@ -5770,7 +5794,7 @@
         <v>3126</v>
       </c>
       <c r="D192" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F192" t="s">
         <v>38</v>
@@ -5799,7 +5823,7 @@
         <v>1811</v>
       </c>
       <c r="D193" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F193" t="s">
         <v>38</v>
@@ -5828,7 +5852,7 @@
         <v>1809</v>
       </c>
       <c r="D194" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F194" t="s">
         <v>38</v>
@@ -5857,7 +5881,7 @@
         <v>1817</v>
       </c>
       <c r="D195" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F195" t="s">
         <v>38</v>
@@ -5944,7 +5968,7 @@
         <v>1819</v>
       </c>
       <c r="D198" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F198" t="s">
         <v>35</v>
@@ -5973,7 +5997,7 @@
         <v>1815</v>
       </c>
       <c r="D199" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F199" t="s">
         <v>35</v>
@@ -6002,7 +6026,7 @@
         <v>1813</v>
       </c>
       <c r="D200" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F200" t="s">
         <v>35</v>
@@ -6031,7 +6055,7 @@
         <v>1812</v>
       </c>
       <c r="D201" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F201" t="s">
         <v>35</v>
@@ -6060,7 +6084,7 @@
         <v>3125</v>
       </c>
       <c r="D202" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F202" t="s">
         <v>35</v>
@@ -6089,7 +6113,7 @@
         <v>1816</v>
       </c>
       <c r="D203" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F203" t="s">
         <v>35</v>
@@ -6118,7 +6142,7 @@
         <v>3126</v>
       </c>
       <c r="D204" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F204" t="s">
         <v>35</v>
@@ -6147,7 +6171,7 @@
         <v>1811</v>
       </c>
       <c r="D205" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F205" t="s">
         <v>35</v>
@@ -6176,7 +6200,7 @@
         <v>1809</v>
       </c>
       <c r="D206" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F206" t="s">
         <v>35</v>
@@ -6205,7 +6229,7 @@
         <v>1817</v>
       </c>
       <c r="D207" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F207" t="s">
         <v>35</v>
@@ -6237,7 +6261,7 @@
         <v>42</v>
       </c>
       <c r="F208" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G208" t="s">
         <v>10</v>
@@ -6266,7 +6290,7 @@
         <v>43</v>
       </c>
       <c r="F209" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G209" t="s">
         <v>13</v>
@@ -6292,10 +6316,10 @@
         <v>1819</v>
       </c>
       <c r="D210" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F210" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G210" t="s">
         <v>10</v>
@@ -6321,10 +6345,10 @@
         <v>1815</v>
       </c>
       <c r="D211" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F211" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G211" t="s">
         <v>10</v>
@@ -6350,10 +6374,10 @@
         <v>3840</v>
       </c>
       <c r="D212" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F212" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G212" t="s">
         <v>10</v>
@@ -6379,10 +6403,10 @@
         <v>1813</v>
       </c>
       <c r="D213" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F213" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G213" t="s">
         <v>13</v>
@@ -6408,10 +6432,10 @@
         <v>1812</v>
       </c>
       <c r="D214" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F214" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G214" t="s">
         <v>12</v>
@@ -6445,10 +6469,10 @@
         <v>3125</v>
       </c>
       <c r="D216" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F216" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G216" t="s">
         <v>10</v>
@@ -6474,10 +6498,10 @@
         <v>1816</v>
       </c>
       <c r="D217" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F217" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G217" t="s">
         <v>10</v>
@@ -6503,10 +6527,10 @@
         <v>3126</v>
       </c>
       <c r="D218" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F218" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G218" t="s">
         <v>10</v>
@@ -6532,10 +6556,10 @@
         <v>1811</v>
       </c>
       <c r="D219" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F219" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G219" t="s">
         <v>13</v>
@@ -6561,10 +6585,10 @@
         <v>1809</v>
       </c>
       <c r="D220" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F220" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G220" t="s">
         <v>10</v>
@@ -6590,10 +6614,10 @@
         <v>1817</v>
       </c>
       <c r="D221" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F221" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G221" t="s">
         <v>10</v>
@@ -6677,7 +6701,7 @@
         <v>1819</v>
       </c>
       <c r="D224" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F224" t="s">
         <v>25</v>
@@ -6706,7 +6730,7 @@
         <v>1815</v>
       </c>
       <c r="D225" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F225" t="s">
         <v>25</v>
@@ -6735,7 +6759,7 @@
         <v>4729</v>
       </c>
       <c r="D226" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F226" t="s">
         <v>25</v>
@@ -6764,7 +6788,7 @@
         <v>1813</v>
       </c>
       <c r="D227" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F227" t="s">
         <v>25</v>
@@ -6793,7 +6817,7 @@
         <v>1812</v>
       </c>
       <c r="D228" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F228" t="s">
         <v>25</v>
@@ -6822,7 +6846,7 @@
         <v>3125</v>
       </c>
       <c r="D229" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F229" t="s">
         <v>25</v>
@@ -6851,7 +6875,7 @@
         <v>1816</v>
       </c>
       <c r="D230" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F230" t="s">
         <v>25</v>
@@ -6880,7 +6904,7 @@
         <v>3126</v>
       </c>
       <c r="D231" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F231" t="s">
         <v>25</v>
@@ -6909,7 +6933,7 @@
         <v>1811</v>
       </c>
       <c r="D232" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F232" t="s">
         <v>25</v>
@@ -6938,7 +6962,7 @@
         <v>1809</v>
       </c>
       <c r="D233" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F233" t="s">
         <v>25</v>
@@ -6967,7 +6991,7 @@
         <v>1817</v>
       </c>
       <c r="D234" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F234" t="s">
         <v>25</v>
@@ -6999,7 +7023,7 @@
         <v>42</v>
       </c>
       <c r="F235" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G235" t="s">
         <v>10</v>
@@ -7028,7 +7052,7 @@
         <v>43</v>
       </c>
       <c r="F236" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G236" t="s">
         <v>13</v>
@@ -7054,10 +7078,10 @@
         <v>1819</v>
       </c>
       <c r="D237" t="s">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
         <v>39</v>
-      </c>
-      <c r="F237" t="s">
-        <v>34</v>
       </c>
       <c r="G237" t="s">
         <v>10</v>
@@ -7083,10 +7107,10 @@
         <v>1815</v>
       </c>
       <c r="D238" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F238" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G238" t="s">
         <v>10</v>
@@ -7112,10 +7136,10 @@
         <v>4827</v>
       </c>
       <c r="D239" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F239" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G239" t="s">
         <v>10</v>
@@ -7141,10 +7165,10 @@
         <v>4729</v>
       </c>
       <c r="D240" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F240" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G240" t="s">
         <v>13</v>
@@ -7170,10 +7194,10 @@
         <v>1813</v>
       </c>
       <c r="D241" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F241" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G241" t="s">
         <v>10</v>
@@ -7199,10 +7223,10 @@
         <v>1812</v>
       </c>
       <c r="D242" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F242" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G242" t="s">
         <v>10</v>
@@ -7228,10 +7252,10 @@
         <v>4828</v>
       </c>
       <c r="D243" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F243" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G243" t="s">
         <v>10</v>
@@ -7257,10 +7281,10 @@
         <v>3125</v>
       </c>
       <c r="D244" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F244" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G244" t="s">
         <v>10</v>
@@ -7286,10 +7310,10 @@
         <v>1816</v>
       </c>
       <c r="D245" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F245" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G245" t="s">
         <v>10</v>
@@ -7315,10 +7339,10 @@
         <v>1811</v>
       </c>
       <c r="D246" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F246" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G246" t="s">
         <v>13</v>
@@ -7344,10 +7368,10 @@
         <v>1809</v>
       </c>
       <c r="D247" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F247" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G247" t="s">
         <v>12</v>
@@ -7381,10 +7405,10 @@
         <v>1817</v>
       </c>
       <c r="D249" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F249" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G249" t="s">
         <v>10</v>
@@ -7476,7 +7500,7 @@
         <v>1819</v>
       </c>
       <c r="D253" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F253" t="s">
         <v>18</v>
@@ -7505,7 +7529,7 @@
         <v>1815</v>
       </c>
       <c r="D254" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F254" t="s">
         <v>18</v>
@@ -7534,7 +7558,7 @@
         <v>4827</v>
       </c>
       <c r="D255" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F255" t="s">
         <v>18</v>
@@ -7563,7 +7587,7 @@
         <v>4729</v>
       </c>
       <c r="D256" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F256" t="s">
         <v>18</v>
@@ -7592,7 +7616,7 @@
         <v>1813</v>
       </c>
       <c r="D257" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F257" t="s">
         <v>18</v>
@@ -7621,7 +7645,7 @@
         <v>1812</v>
       </c>
       <c r="D258" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F258" t="s">
         <v>18</v>
@@ -7650,7 +7674,7 @@
         <v>4828</v>
       </c>
       <c r="D259" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F259" t="s">
         <v>18</v>
@@ -7679,7 +7703,7 @@
         <v>3125</v>
       </c>
       <c r="D260" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F260" t="s">
         <v>18</v>
@@ -7708,7 +7732,7 @@
         <v>1816</v>
       </c>
       <c r="D261" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F261" t="s">
         <v>18</v>
@@ -7737,7 +7761,7 @@
         <v>1811</v>
       </c>
       <c r="D262" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F262" t="s">
         <v>18</v>
@@ -7766,7 +7790,7 @@
         <v>1809</v>
       </c>
       <c r="D263" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F263" t="s">
         <v>18</v>
@@ -7803,7 +7827,7 @@
         <v>1817</v>
       </c>
       <c r="D265" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F265" t="s">
         <v>18</v>
@@ -7898,7 +7922,7 @@
         <v>1819</v>
       </c>
       <c r="D269" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F269" t="s">
         <v>19</v>
@@ -7927,7 +7951,7 @@
         <v>1815</v>
       </c>
       <c r="D270" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F270" t="s">
         <v>19</v>
@@ -7956,7 +7980,7 @@
         <v>4827</v>
       </c>
       <c r="D271" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F271" t="s">
         <v>19</v>
@@ -7985,7 +8009,7 @@
         <v>4729</v>
       </c>
       <c r="D272" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F272" t="s">
         <v>19</v>
@@ -8014,7 +8038,7 @@
         <v>1813</v>
       </c>
       <c r="D273" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F273" t="s">
         <v>19</v>
@@ -8043,7 +8067,7 @@
         <v>1812</v>
       </c>
       <c r="D274" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F274" t="s">
         <v>19</v>
@@ -8080,7 +8104,7 @@
         <v>4828</v>
       </c>
       <c r="D276" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F276" t="s">
         <v>19</v>
@@ -8109,7 +8133,7 @@
         <v>3125</v>
       </c>
       <c r="D277" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F277" t="s">
         <v>19</v>
@@ -8138,7 +8162,7 @@
         <v>1816</v>
       </c>
       <c r="D278" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F278" t="s">
         <v>19</v>
@@ -8167,7 +8191,7 @@
         <v>1811</v>
       </c>
       <c r="D279" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F279" t="s">
         <v>19</v>
@@ -8196,7 +8220,7 @@
         <v>1809</v>
       </c>
       <c r="D280" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F280" t="s">
         <v>19</v>
@@ -8225,7 +8249,7 @@
         <v>1817</v>
       </c>
       <c r="D281" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F281" t="s">
         <v>19</v>
@@ -8291,7 +8315,7 @@
         <v>1819</v>
       </c>
       <c r="D284" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F284" t="s">
         <v>27</v>
@@ -8320,7 +8344,7 @@
         <v>1815</v>
       </c>
       <c r="D285" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F285" t="s">
         <v>27</v>
@@ -8349,7 +8373,7 @@
         <v>4827</v>
       </c>
       <c r="D286" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F286" t="s">
         <v>27</v>
@@ -8378,7 +8402,7 @@
         <v>1813</v>
       </c>
       <c r="D287" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F287" t="s">
         <v>27</v>
@@ -8407,7 +8431,7 @@
         <v>1812</v>
       </c>
       <c r="D288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F288" t="s">
         <v>27</v>
@@ -8436,7 +8460,7 @@
         <v>4828</v>
       </c>
       <c r="D289" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F289" t="s">
         <v>27</v>
@@ -8465,7 +8489,7 @@
         <v>3125</v>
       </c>
       <c r="D290" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F290" t="s">
         <v>27</v>
@@ -8494,7 +8518,7 @@
         <v>1816</v>
       </c>
       <c r="D291" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F291" t="s">
         <v>27</v>
@@ -8523,7 +8547,7 @@
         <v>1809</v>
       </c>
       <c r="D292" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F292" t="s">
         <v>27</v>
@@ -8552,7 +8576,7 @@
         <v>1817</v>
       </c>
       <c r="D293" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F293" t="s">
         <v>27</v>
@@ -8584,7 +8608,7 @@
         <v>42</v>
       </c>
       <c r="F294" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G294" t="s">
         <v>10</v>
@@ -8610,10 +8634,10 @@
         <v>1819</v>
       </c>
       <c r="D295" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F295" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G295" t="s">
         <v>10</v>
@@ -8639,10 +8663,10 @@
         <v>1815</v>
       </c>
       <c r="D296" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F296" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G296" t="s">
         <v>10</v>
@@ -8668,10 +8692,10 @@
         <v>4827</v>
       </c>
       <c r="D297" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F297" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G297" t="s">
         <v>10</v>
@@ -8697,10 +8721,10 @@
         <v>1813</v>
       </c>
       <c r="D298" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F298" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G298" t="s">
         <v>10</v>
@@ -8726,10 +8750,10 @@
         <v>1812</v>
       </c>
       <c r="D299" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F299" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G299" t="s">
         <v>10</v>
@@ -8755,10 +8779,10 @@
         <v>4828</v>
       </c>
       <c r="D300" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F300" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G300" t="s">
         <v>10</v>
@@ -8784,10 +8808,10 @@
         <v>3125</v>
       </c>
       <c r="D301" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F301" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G301" t="s">
         <v>12</v>
@@ -8821,10 +8845,10 @@
         <v>1816</v>
       </c>
       <c r="D303" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F303" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G303" t="s">
         <v>10</v>
@@ -8850,10 +8874,10 @@
         <v>1809</v>
       </c>
       <c r="D304" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F304" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G304" t="s">
         <v>13</v>
@@ -8879,10 +8903,10 @@
         <v>1817</v>
       </c>
       <c r="D305" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F305" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G305" t="s">
         <v>10</v>
@@ -8937,7 +8961,7 @@
         <v>1819</v>
       </c>
       <c r="D307" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -8966,7 +8990,7 @@
         <v>1815</v>
       </c>
       <c r="D308" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -8995,7 +9019,7 @@
         <v>4827</v>
       </c>
       <c r="D309" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -9024,7 +9048,7 @@
         <v>1813</v>
       </c>
       <c r="D310" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -9053,7 +9077,7 @@
         <v>1812</v>
       </c>
       <c r="D311" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -9090,7 +9114,7 @@
         <v>4828</v>
       </c>
       <c r="D313" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -9119,7 +9143,7 @@
         <v>3125</v>
       </c>
       <c r="D314" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -9156,7 +9180,7 @@
         <v>1816</v>
       </c>
       <c r="D316" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -9185,7 +9209,7 @@
         <v>1809</v>
       </c>
       <c r="D317" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -9214,7 +9238,7 @@
         <v>1817</v>
       </c>
       <c r="D318" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -9280,7 +9304,7 @@
         <v>1819</v>
       </c>
       <c r="D321" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F321" t="s">
         <v>29</v>
@@ -9317,7 +9341,7 @@
         <v>1815</v>
       </c>
       <c r="D323" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F323" t="s">
         <v>29</v>
@@ -9346,7 +9370,7 @@
         <v>4827</v>
       </c>
       <c r="D324" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F324" t="s">
         <v>29</v>
@@ -9375,7 +9399,7 @@
         <v>1813</v>
       </c>
       <c r="D325" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F325" t="s">
         <v>29</v>
@@ -9404,7 +9428,7 @@
         <v>1812</v>
       </c>
       <c r="D326" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F326" t="s">
         <v>29</v>
@@ -9433,7 +9457,7 @@
         <v>4828</v>
       </c>
       <c r="D327" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F327" t="s">
         <v>29</v>
@@ -9462,7 +9486,7 @@
         <v>3125</v>
       </c>
       <c r="D328" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F328" t="s">
         <v>29</v>
@@ -9491,7 +9515,7 @@
         <v>1816</v>
       </c>
       <c r="D329" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F329" t="s">
         <v>29</v>
@@ -9520,7 +9544,7 @@
         <v>1809</v>
       </c>
       <c r="D330" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F330" t="s">
         <v>29</v>
@@ -9549,7 +9573,7 @@
         <v>1817</v>
       </c>
       <c r="D331" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F331" t="s">
         <v>29</v>
@@ -9615,7 +9639,7 @@
         <v>1819</v>
       </c>
       <c r="D334" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F334" t="s">
         <v>20</v>
@@ -9652,7 +9676,7 @@
         <v>1815</v>
       </c>
       <c r="D336" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F336" t="s">
         <v>20</v>
@@ -9681,7 +9705,7 @@
         <v>4827</v>
       </c>
       <c r="D337" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F337" t="s">
         <v>20</v>
@@ -9710,7 +9734,7 @@
         <v>1813</v>
       </c>
       <c r="D338" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F338" t="s">
         <v>20</v>
@@ -9739,7 +9763,7 @@
         <v>1812</v>
       </c>
       <c r="D339" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F339" t="s">
         <v>20</v>
@@ -9768,7 +9792,7 @@
         <v>4828</v>
       </c>
       <c r="D340" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F340" t="s">
         <v>20</v>
@@ -9797,7 +9821,7 @@
         <v>3125</v>
       </c>
       <c r="D341" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F341" t="s">
         <v>20</v>
@@ -9826,7 +9850,7 @@
         <v>1816</v>
       </c>
       <c r="D342" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F342" t="s">
         <v>20</v>
@@ -9855,7 +9879,7 @@
         <v>1809</v>
       </c>
       <c r="D343" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F343" t="s">
         <v>20</v>
@@ -9884,7 +9908,7 @@
         <v>1817</v>
       </c>
       <c r="D344" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F344" t="s">
         <v>20</v>
@@ -9942,7 +9966,7 @@
         <v>5587</v>
       </c>
       <c r="D346" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F346" t="s">
         <v>24</v>
@@ -9971,7 +9995,7 @@
         <v>1812</v>
       </c>
       <c r="D347" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F347" t="s">
         <v>24</v>
@@ -10000,7 +10024,7 @@
         <v>4828</v>
       </c>
       <c r="D348" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F348" t="s">
         <v>24</v>
@@ -10029,7 +10053,7 @@
         <v>1819</v>
       </c>
       <c r="D349" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F349" t="s">
         <v>30</v>
@@ -10058,7 +10082,7 @@
         <v>1815</v>
       </c>
       <c r="D350" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F350" t="s">
         <v>30</v>
@@ -10087,7 +10111,7 @@
         <v>4827</v>
       </c>
       <c r="D351" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F351" t="s">
         <v>30</v>
@@ -10116,7 +10140,7 @@
         <v>3125</v>
       </c>
       <c r="D352" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F352" t="s">
         <v>30</v>
@@ -10145,7 +10169,7 @@
         <v>1816</v>
       </c>
       <c r="D353" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F353" t="s">
         <v>30</v>
@@ -10174,7 +10198,7 @@
         <v>1809</v>
       </c>
       <c r="D354" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F354" t="s">
         <v>30</v>
@@ -10203,7 +10227,7 @@
         <v>1817</v>
       </c>
       <c r="D355" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F355" t="s">
         <v>30</v>
@@ -10232,7 +10256,7 @@
         <v>1813</v>
       </c>
       <c r="D356" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F356" t="s">
         <v>30</v>
@@ -10290,7 +10314,7 @@
         <v>5587</v>
       </c>
       <c r="D358" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F358" t="s">
         <v>23</v>
@@ -10319,16 +10343,16 @@
         <v>1819</v>
       </c>
       <c r="D359" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F359" t="s">
         <v>23</v>
       </c>
       <c r="G359" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H359" s="2">
-        <v>6.9444444444444444E-5</v>
+        <v>5.9837962962962961E-3</v>
       </c>
       <c r="I359" s="1">
         <v>46219.689583333333</v>
@@ -10341,11 +10365,32 @@
       </c>
     </row>
     <row r="360" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H360" s="2"/>
-      <c r="I360" s="1"/>
-      <c r="J360" s="2"/>
+      <c r="B360" t="s">
+        <v>41</v>
+      </c>
+      <c r="C360">
+        <v>1815</v>
+      </c>
+      <c r="D360" t="s">
+        <v>45</v>
+      </c>
+      <c r="F360" t="s">
+        <v>23</v>
+      </c>
+      <c r="G360" t="s">
+        <v>10</v>
+      </c>
+      <c r="H360" s="2">
+        <v>6.5046296296296293E-3</v>
+      </c>
+      <c r="I360" s="1">
+        <v>46219.689583333333</v>
+      </c>
+      <c r="J360" s="2">
+        <v>2</v>
+      </c>
       <c r="K360" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="361" spans="2:11" x14ac:dyDescent="0.25">
@@ -10353,10 +10398,10 @@
         <v>41</v>
       </c>
       <c r="C361">
-        <v>1815</v>
+        <v>4827</v>
       </c>
       <c r="D361" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F361" t="s">
         <v>23</v>
@@ -10365,13 +10410,13 @@
         <v>10</v>
       </c>
       <c r="H361" s="2">
-        <v>6.5046296296296293E-3</v>
+        <v>6.828703703703704E-3</v>
       </c>
       <c r="I361" s="1">
-        <v>46219.689583333333</v>
+        <v>46219.69027777778</v>
       </c>
       <c r="J361" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K361" s="1" t="s">
         <v>11</v>
@@ -10382,10 +10427,10 @@
         <v>41</v>
       </c>
       <c r="C362">
-        <v>4827</v>
+        <v>1813</v>
       </c>
       <c r="D362" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F362" t="s">
         <v>23</v>
@@ -10394,13 +10439,13 @@
         <v>10</v>
       </c>
       <c r="H362" s="2">
-        <v>6.828703703703704E-3</v>
+        <v>9.5486111111111119E-3</v>
       </c>
       <c r="I362" s="1">
-        <v>46219.69027777778</v>
+        <v>46219.690972222219</v>
       </c>
       <c r="J362" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K362" s="1" t="s">
         <v>11</v>
@@ -10411,10 +10456,10 @@
         <v>41</v>
       </c>
       <c r="C363">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="D363" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F363" t="s">
         <v>23</v>
@@ -10423,7 +10468,7 @@
         <v>10</v>
       </c>
       <c r="H363" s="2">
-        <v>9.5486111111111119E-3</v>
+        <v>6.5046296296296293E-3</v>
       </c>
       <c r="I363" s="1">
         <v>46219.690972222219</v>
@@ -10440,10 +10485,10 @@
         <v>41</v>
       </c>
       <c r="C364">
-        <v>1812</v>
+        <v>4828</v>
       </c>
       <c r="D364" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F364" t="s">
         <v>23</v>
@@ -10452,13 +10497,13 @@
         <v>10</v>
       </c>
       <c r="H364" s="2">
-        <v>6.5046296296296293E-3</v>
+        <v>7.951388888888888E-3</v>
       </c>
       <c r="I364" s="1">
-        <v>46219.690972222219</v>
+        <v>46219.691666666666</v>
       </c>
       <c r="J364" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K364" s="1" t="s">
         <v>11</v>
@@ -10469,10 +10514,10 @@
         <v>41</v>
       </c>
       <c r="C365">
-        <v>4828</v>
+        <v>1816</v>
       </c>
       <c r="D365" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F365" t="s">
         <v>23</v>
@@ -10481,10 +10526,10 @@
         <v>10</v>
       </c>
       <c r="H365" s="2">
-        <v>7.951388888888888E-3</v>
+        <v>5.6597222222222222E-3</v>
       </c>
       <c r="I365" s="1">
-        <v>46219.691666666666</v>
+        <v>46219.692361111112</v>
       </c>
       <c r="J365" s="2">
         <v>0</v>
@@ -10498,10 +10543,10 @@
         <v>41</v>
       </c>
       <c r="C366">
-        <v>1816</v>
+        <v>5882</v>
       </c>
       <c r="D366" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F366" t="s">
         <v>23</v>
@@ -10510,13 +10555,13 @@
         <v>10</v>
       </c>
       <c r="H366" s="2">
-        <v>5.6597222222222222E-3</v>
+        <v>1.0266203703703704E-2</v>
       </c>
       <c r="I366" s="1">
         <v>46219.692361111112</v>
       </c>
       <c r="J366" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K366" s="1" t="s">
         <v>11</v>
@@ -10527,25 +10572,25 @@
         <v>41</v>
       </c>
       <c r="C367">
-        <v>5882</v>
+        <v>1809</v>
       </c>
       <c r="D367" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F367" t="s">
         <v>23</v>
       </c>
       <c r="G367" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H367" s="2">
-        <v>1.0266203703703704E-2</v>
+        <v>0</v>
       </c>
       <c r="I367" s="1">
-        <v>46219.692361111112</v>
+        <v>46219.693055555559</v>
       </c>
       <c r="J367" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K367" s="1" t="s">
         <v>11</v>
@@ -10556,22 +10601,22 @@
         <v>41</v>
       </c>
       <c r="C368">
-        <v>1809</v>
+        <v>1817</v>
       </c>
       <c r="D368" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F368" t="s">
         <v>23</v>
       </c>
       <c r="G368" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H368" s="2">
-        <v>0</v>
+        <v>6.6319444444444446E-3</v>
       </c>
       <c r="I368" s="1">
-        <v>46219.693055555559</v>
+        <v>46219.693749999999</v>
       </c>
       <c r="J368" s="2">
         <v>2</v>
@@ -10585,25 +10630,25 @@
         <v>41</v>
       </c>
       <c r="C369">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="D369" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F369" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G369" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H369" s="2">
-        <v>6.6319444444444446E-3</v>
+        <v>0</v>
       </c>
       <c r="I369" s="1">
-        <v>46219.693749999999</v>
+        <v>46237.798611111109</v>
       </c>
       <c r="J369" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K369" s="1" t="s">
         <v>11</v>
@@ -10613,183 +10658,603 @@
       <c r="H370" s="2"/>
       <c r="I370" s="1"/>
       <c r="J370" s="2"/>
-      <c r="K370" s="1"/>
+      <c r="K370" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="371" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H371" s="2"/>
-      <c r="I371" s="1"/>
-      <c r="J371" s="2"/>
-      <c r="K371" s="1"/>
+      <c r="B371" t="s">
+        <v>41</v>
+      </c>
+      <c r="C371">
+        <v>6051</v>
+      </c>
+      <c r="D371" t="s">
+        <v>65</v>
+      </c>
+      <c r="F371" t="s">
+        <v>31</v>
+      </c>
+      <c r="G371" t="s">
+        <v>10</v>
+      </c>
+      <c r="H371" s="2">
+        <v>8.1597222222222227E-3</v>
+      </c>
+      <c r="I371" s="1">
+        <v>46237.799305555556</v>
+      </c>
+      <c r="J371" s="2">
+        <v>0</v>
+      </c>
+      <c r="K371" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="372" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H372" s="2"/>
-      <c r="I372" s="1"/>
-      <c r="J372" s="2"/>
-      <c r="K372" s="1"/>
+      <c r="B372" t="s">
+        <v>41</v>
+      </c>
+      <c r="C372">
+        <v>6053</v>
+      </c>
+      <c r="D372" t="s">
+        <v>66</v>
+      </c>
+      <c r="F372" t="s">
+        <v>31</v>
+      </c>
+      <c r="G372" t="s">
+        <v>10</v>
+      </c>
+      <c r="H372" s="2">
+        <v>5.9027777777777776E-3</v>
+      </c>
+      <c r="I372" s="1">
+        <v>46237.8</v>
+      </c>
+      <c r="J372" s="2">
+        <v>0</v>
+      </c>
+      <c r="K372" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="373" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H373" s="2"/>
-      <c r="I373" s="1"/>
-      <c r="J373" s="2"/>
-      <c r="K373" s="1"/>
+      <c r="B373" t="s">
+        <v>41</v>
+      </c>
+      <c r="C373">
+        <v>5587</v>
+      </c>
+      <c r="D373" t="s">
+        <v>63</v>
+      </c>
+      <c r="F373" t="s">
+        <v>31</v>
+      </c>
+      <c r="G373" t="s">
+        <v>13</v>
+      </c>
+      <c r="H373" s="2">
+        <v>0</v>
+      </c>
+      <c r="I373" s="1">
+        <v>46237.8</v>
+      </c>
+      <c r="J373" s="2">
+        <v>0</v>
+      </c>
+      <c r="K373" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="374" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H374" s="2"/>
-      <c r="I374" s="1"/>
-      <c r="J374" s="2"/>
-      <c r="K374" s="1"/>
+      <c r="B374" t="s">
+        <v>41</v>
+      </c>
+      <c r="C374">
+        <v>1819</v>
+      </c>
+      <c r="D374" t="s">
+        <v>44</v>
+      </c>
+      <c r="F374" t="s">
+        <v>31</v>
+      </c>
+      <c r="G374" t="s">
+        <v>13</v>
+      </c>
+      <c r="H374" s="2">
+        <v>0</v>
+      </c>
+      <c r="I374" s="1">
+        <v>46237.800694444442</v>
+      </c>
+      <c r="J374" s="2">
+        <v>0</v>
+      </c>
+      <c r="K374" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="375" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H375" s="2"/>
-      <c r="I375" s="1"/>
-      <c r="J375" s="2"/>
-      <c r="K375" s="1"/>
+      <c r="B375" t="s">
+        <v>41</v>
+      </c>
+      <c r="C375">
+        <v>1815</v>
+      </c>
+      <c r="D375" t="s">
+        <v>45</v>
+      </c>
+      <c r="F375" t="s">
+        <v>31</v>
+      </c>
+      <c r="G375" t="s">
+        <v>13</v>
+      </c>
+      <c r="H375" s="2">
+        <v>0</v>
+      </c>
+      <c r="I375" s="1">
+        <v>46237.801388888889</v>
+      </c>
+      <c r="J375" s="2">
+        <v>0</v>
+      </c>
+      <c r="K375" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="376" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H376" s="2"/>
-      <c r="I376" s="1"/>
-      <c r="J376" s="2"/>
-      <c r="K376" s="1"/>
+      <c r="B376" t="s">
+        <v>41</v>
+      </c>
+      <c r="C376">
+        <v>4827</v>
+      </c>
+      <c r="D376" t="s">
+        <v>61</v>
+      </c>
+      <c r="F376" t="s">
+        <v>31</v>
+      </c>
+      <c r="G376" t="s">
+        <v>12</v>
+      </c>
+      <c r="H376" s="2">
+        <v>0</v>
+      </c>
+      <c r="I376" s="1">
+        <v>46237.802083333336</v>
+      </c>
+      <c r="J376" s="2">
+        <v>0</v>
+      </c>
+      <c r="K376" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="377" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H377" s="2"/>
       <c r="I377" s="1"/>
       <c r="J377" s="2"/>
-      <c r="K377" s="1"/>
+      <c r="K377" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="378" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H378" s="2"/>
-      <c r="I378" s="1"/>
-      <c r="J378" s="2"/>
-      <c r="K378" s="1"/>
+      <c r="B378" t="s">
+        <v>41</v>
+      </c>
+      <c r="C378">
+        <v>1813</v>
+      </c>
+      <c r="D378" t="s">
+        <v>46</v>
+      </c>
+      <c r="F378" t="s">
+        <v>31</v>
+      </c>
+      <c r="G378" t="s">
+        <v>13</v>
+      </c>
+      <c r="H378" s="2">
+        <v>0</v>
+      </c>
+      <c r="I378" s="1">
+        <v>46237.802083333336</v>
+      </c>
+      <c r="J378" s="2">
+        <v>0</v>
+      </c>
+      <c r="K378" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="379" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H379" s="2"/>
-      <c r="I379" s="1"/>
-      <c r="J379" s="2"/>
-      <c r="K379" s="1"/>
+      <c r="B379" t="s">
+        <v>41</v>
+      </c>
+      <c r="C379">
+        <v>1812</v>
+      </c>
+      <c r="D379" t="s">
+        <v>47</v>
+      </c>
+      <c r="F379" t="s">
+        <v>31</v>
+      </c>
+      <c r="G379" t="s">
+        <v>13</v>
+      </c>
+      <c r="H379" s="2">
+        <v>0</v>
+      </c>
+      <c r="I379" s="1">
+        <v>46237.802777777775</v>
+      </c>
+      <c r="J379" s="2">
+        <v>0</v>
+      </c>
+      <c r="K379" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="380" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H380" s="2"/>
-      <c r="I380" s="1"/>
-      <c r="J380" s="2"/>
-      <c r="K380" s="1"/>
+      <c r="B380" t="s">
+        <v>41</v>
+      </c>
+      <c r="C380">
+        <v>6057</v>
+      </c>
+      <c r="D380" t="s">
+        <v>67</v>
+      </c>
+      <c r="F380" t="s">
+        <v>31</v>
+      </c>
+      <c r="G380" t="s">
+        <v>10</v>
+      </c>
+      <c r="H380" s="2">
+        <v>8.9930555555555562E-3</v>
+      </c>
+      <c r="I380" s="1">
+        <v>46237.803472222222</v>
+      </c>
+      <c r="J380" s="2">
+        <v>0</v>
+      </c>
+      <c r="K380" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="381" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H381" s="2"/>
-      <c r="I381" s="1"/>
-      <c r="J381" s="2"/>
-      <c r="K381" s="1"/>
+      <c r="B381" t="s">
+        <v>41</v>
+      </c>
+      <c r="C381">
+        <v>6058</v>
+      </c>
+      <c r="D381" t="s">
+        <v>68</v>
+      </c>
+      <c r="F381" t="s">
+        <v>31</v>
+      </c>
+      <c r="G381" t="s">
+        <v>13</v>
+      </c>
+      <c r="H381" s="2">
+        <v>0</v>
+      </c>
+      <c r="I381" s="1">
+        <v>46237.803472222222</v>
+      </c>
+      <c r="J381" s="2">
+        <v>0</v>
+      </c>
+      <c r="K381" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="382" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H382" s="2"/>
-      <c r="I382" s="1"/>
-      <c r="J382" s="2"/>
-      <c r="K382" s="1"/>
+      <c r="B382" t="s">
+        <v>41</v>
+      </c>
+      <c r="C382">
+        <v>4828</v>
+      </c>
+      <c r="D382" t="s">
+        <v>62</v>
+      </c>
+      <c r="F382" t="s">
+        <v>31</v>
+      </c>
+      <c r="G382" t="s">
+        <v>10</v>
+      </c>
+      <c r="H382" s="2">
+        <v>8.7962962962962968E-3</v>
+      </c>
+      <c r="I382" s="1">
+        <v>46237.804166666669</v>
+      </c>
+      <c r="J382" s="2">
+        <v>0</v>
+      </c>
+      <c r="K382" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="383" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H383" s="2"/>
-      <c r="I383" s="1"/>
-      <c r="J383" s="2"/>
-      <c r="K383" s="1"/>
+      <c r="B383" t="s">
+        <v>41</v>
+      </c>
+      <c r="C383">
+        <v>6054</v>
+      </c>
+      <c r="D383" t="s">
+        <v>69</v>
+      </c>
+      <c r="F383" t="s">
+        <v>31</v>
+      </c>
+      <c r="G383" t="s">
+        <v>14</v>
+      </c>
+      <c r="H383" s="2">
+        <v>0</v>
+      </c>
+      <c r="I383" s="1">
+        <v>46237.804861111108</v>
+      </c>
+      <c r="J383" s="2">
+        <v>0</v>
+      </c>
+      <c r="K383" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="384" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H384" s="2"/>
       <c r="I384" s="1"/>
       <c r="J384" s="2"/>
-      <c r="K384" s="1"/>
-    </row>
-    <row r="385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H385" s="2"/>
-      <c r="I385" s="1"/>
-      <c r="J385" s="2"/>
-      <c r="K385" s="1"/>
-    </row>
-    <row r="386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H386" s="2"/>
-      <c r="I386" s="1"/>
-      <c r="J386" s="2"/>
-      <c r="K386" s="1"/>
-    </row>
-    <row r="387" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H387" s="2"/>
-      <c r="I387" s="1"/>
-      <c r="J387" s="2"/>
-      <c r="K387" s="1"/>
-    </row>
-    <row r="388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H388" s="2"/>
-      <c r="I388" s="1"/>
-      <c r="J388" s="2"/>
-      <c r="K388" s="1"/>
-    </row>
-    <row r="389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H389" s="2"/>
-      <c r="I389" s="1"/>
-      <c r="J389" s="2"/>
-      <c r="K389" s="1"/>
-    </row>
-    <row r="390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H390" s="2"/>
-      <c r="I390" s="1"/>
-      <c r="J390" s="2"/>
-      <c r="K390" s="1"/>
-    </row>
-    <row r="391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K384" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="385" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B385" t="s">
+        <v>41</v>
+      </c>
+      <c r="C385">
+        <v>6048</v>
+      </c>
+      <c r="D385" t="s">
+        <v>70</v>
+      </c>
+      <c r="F385" t="s">
+        <v>31</v>
+      </c>
+      <c r="G385" t="s">
+        <v>10</v>
+      </c>
+      <c r="H385" s="2">
+        <v>6.2152777777777779E-3</v>
+      </c>
+      <c r="I385" s="1">
+        <v>46237.805555555555</v>
+      </c>
+      <c r="J385" s="2">
+        <v>0</v>
+      </c>
+      <c r="K385" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="386" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B386" t="s">
+        <v>41</v>
+      </c>
+      <c r="C386">
+        <v>1816</v>
+      </c>
+      <c r="D386" t="s">
+        <v>49</v>
+      </c>
+      <c r="F386" t="s">
+        <v>31</v>
+      </c>
+      <c r="G386" t="s">
+        <v>10</v>
+      </c>
+      <c r="H386" s="2">
+        <v>7.0254629629629634E-3</v>
+      </c>
+      <c r="I386" s="1">
+        <v>46237.806250000001</v>
+      </c>
+      <c r="J386" s="2">
+        <v>0</v>
+      </c>
+      <c r="K386" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="387" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B387" t="s">
+        <v>41</v>
+      </c>
+      <c r="C387">
+        <v>5882</v>
+      </c>
+      <c r="D387" t="s">
+        <v>64</v>
+      </c>
+      <c r="F387" t="s">
+        <v>31</v>
+      </c>
+      <c r="G387" t="s">
+        <v>13</v>
+      </c>
+      <c r="H387" s="2">
+        <v>0</v>
+      </c>
+      <c r="I387" s="1">
+        <v>46237.806944444441</v>
+      </c>
+      <c r="J387" s="2">
+        <v>0</v>
+      </c>
+      <c r="K387" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="388" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B388" t="s">
+        <v>41</v>
+      </c>
+      <c r="C388">
+        <v>6052</v>
+      </c>
+      <c r="D388" t="s">
+        <v>71</v>
+      </c>
+      <c r="F388" t="s">
+        <v>31</v>
+      </c>
+      <c r="G388" t="s">
+        <v>13</v>
+      </c>
+      <c r="H388" s="2">
+        <v>0</v>
+      </c>
+      <c r="I388" s="1">
+        <v>46237.806944444441</v>
+      </c>
+      <c r="J388" s="2">
+        <v>0</v>
+      </c>
+      <c r="K388" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="389" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B389" t="s">
+        <v>41</v>
+      </c>
+      <c r="C389">
+        <v>1809</v>
+      </c>
+      <c r="D389" t="s">
+        <v>53</v>
+      </c>
+      <c r="F389" t="s">
+        <v>31</v>
+      </c>
+      <c r="G389" t="s">
+        <v>13</v>
+      </c>
+      <c r="H389" s="2">
+        <v>0</v>
+      </c>
+      <c r="I389" s="1">
+        <v>46237.807638888888</v>
+      </c>
+      <c r="J389" s="2">
+        <v>0</v>
+      </c>
+      <c r="K389" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="390" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B390" t="s">
+        <v>41</v>
+      </c>
+      <c r="C390">
+        <v>1817</v>
+      </c>
+      <c r="D390" t="s">
+        <v>54</v>
+      </c>
+      <c r="F390" t="s">
+        <v>31</v>
+      </c>
+      <c r="G390" t="s">
+        <v>13</v>
+      </c>
+      <c r="H390" s="2">
+        <v>0</v>
+      </c>
+      <c r="I390" s="1">
+        <v>46237.808333333334</v>
+      </c>
+      <c r="J390" s="2">
+        <v>0</v>
+      </c>
+      <c r="K390" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="391" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H391" s="2"/>
       <c r="I391" s="1"/>
       <c r="J391" s="2"/>
       <c r="K391" s="1"/>
     </row>
-    <row r="392" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H392" s="2"/>
       <c r="I392" s="1"/>
       <c r="J392" s="2"/>
       <c r="K392" s="1"/>
     </row>
-    <row r="393" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H393" s="2"/>
       <c r="I393" s="1"/>
       <c r="J393" s="2"/>
       <c r="K393" s="1"/>
     </row>
-    <row r="394" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H394" s="2"/>
       <c r="I394" s="1"/>
       <c r="J394" s="2"/>
       <c r="K394" s="1"/>
     </row>
-    <row r="395" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H395" s="2"/>
       <c r="I395" s="1"/>
       <c r="J395" s="2"/>
       <c r="K395" s="1"/>
     </row>
-    <row r="396" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H396" s="2"/>
       <c r="I396" s="1"/>
       <c r="J396" s="2"/>
       <c r="K396" s="1"/>
     </row>
-    <row r="397" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H397" s="2"/>
       <c r="I397" s="1"/>
       <c r="J397" s="2"/>
       <c r="K397" s="1"/>
     </row>
-    <row r="398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H398" s="2"/>
       <c r="I398" s="1"/>
       <c r="J398" s="2"/>
       <c r="K398" s="1"/>
     </row>
-    <row r="399" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H399" s="2"/>
       <c r="I399" s="1"/>
       <c r="J399" s="2"/>
       <c r="K399" s="1"/>
     </row>
-    <row r="400" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H400" s="2"/>
       <c r="I400" s="1"/>
       <c r="J400" s="2"/>
@@ -50523,6 +50988,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -50537,11 +51003,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -50552,10 +51020,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -50573,14 +51044,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -50591,14 +51065,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -50625,6 +51102,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -50633,6 +51111,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -50645,22 +51124,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -50679,6 +51163,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -50689,10 +51174,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -50701,10 +51188,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -50718,82 +51207,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -50807,6 +51311,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -50817,6 +51322,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -50824,6 +51330,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -50832,86 +51339,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -50928,26 +51448,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -50978,6 +51504,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -50987,10 +51514,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -51003,14 +51532,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -51019,14 +51551,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -51045,26 +51580,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -51083,6 +51624,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -51091,10 +51633,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -51103,6 +51647,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -51115,10 +51660,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -51127,6 +51674,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -51135,14 +51683,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -51151,14 +51702,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -51175,76 +51729,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -51258,31 +51821,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -51295,10 +51865,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -51307,10 +51879,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -51319,6 +51893,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -51333,10 +51908,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -51345,10 +51922,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -51362,6 +51941,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -51377,14 +51957,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -51402,14 +51985,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -51422,10 +52008,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -51434,14 +52022,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -51450,10 +52041,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -51462,14 +52055,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -51491,6 +52087,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -51499,39 +52096,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F57971E-9E07-494B-9867-5D0BE7182731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08E04093-3E5D-4885-B3A9-F2A920B991FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="66">
   <si>
     <t>Company Name</t>
   </si>
@@ -237,24 +237,6 @@
   </si>
   <si>
     <t>Bradley Johnson</t>
-  </si>
-  <si>
-    <t>Brian Longbine</t>
-  </si>
-  <si>
-    <t>Joseph Pruiett</t>
-  </si>
-  <si>
-    <t>Josue Faz Pina</t>
-  </si>
-  <si>
-    <t>Lorenzo Sanchez</t>
-  </si>
-  <si>
-    <t>Luis Martinez</t>
-  </si>
-  <si>
-    <t>Richard Killam Rivera</t>
   </si>
 </sst>
 </file>
@@ -628,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -704,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -857,7 +839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>41</v>
       </c>
@@ -973,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>41</v>
       </c>
@@ -1287,7 +1269,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1419,7 +1401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>41</v>
       </c>
@@ -1646,7 +1628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>41</v>
       </c>
@@ -1952,7 +1934,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>41</v>
       </c>
@@ -2532,7 +2514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>41</v>
       </c>
@@ -2764,7 +2746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>41</v>
       </c>
@@ -3054,7 +3036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>41</v>
       </c>
@@ -3634,7 +3616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>41</v>
       </c>
@@ -3721,7 +3703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>41</v>
       </c>
@@ -4069,7 +4051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -5264,7 +5246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>41</v>
       </c>
@@ -5409,7 +5391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>41</v>
       </c>
@@ -5699,7 +5681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>41</v>
       </c>
@@ -6221,7 +6203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>41</v>
       </c>
@@ -7128,7 +7110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>41</v>
       </c>
@@ -9391,7 +9373,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>41</v>
       </c>
@@ -9668,7 +9650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>41</v>
       </c>
@@ -9726,7 +9708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>41</v>
       </c>
@@ -10190,7 +10172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>41</v>
       </c>
@@ -10248,7 +10230,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>41</v>
       </c>
@@ -10648,7 +10630,7 @@
         <v>46237.798611111109</v>
       </c>
       <c r="J369" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K369" s="1" t="s">
         <v>11</v>
@@ -10691,15 +10673,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>41</v>
       </c>
       <c r="C372">
-        <v>6053</v>
+        <v>5587</v>
       </c>
       <c r="D372" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F372" t="s">
         <v>31</v>
@@ -10708,13 +10690,13 @@
         <v>10</v>
       </c>
       <c r="H372" s="2">
-        <v>5.9027777777777776E-3</v>
+        <v>6.5162037037037037E-3</v>
       </c>
       <c r="I372" s="1">
         <v>46237.8</v>
       </c>
       <c r="J372" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K372" s="1" t="s">
         <v>11</v>
@@ -10725,10 +10707,10 @@
         <v>41</v>
       </c>
       <c r="C373">
-        <v>5587</v>
+        <v>1819</v>
       </c>
       <c r="D373" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F373" t="s">
         <v>31</v>
@@ -10740,10 +10722,10 @@
         <v>0</v>
       </c>
       <c r="I373" s="1">
-        <v>46237.8</v>
+        <v>46237.800694444442</v>
       </c>
       <c r="J373" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K373" s="1" t="s">
         <v>11</v>
@@ -10754,25 +10736,25 @@
         <v>41</v>
       </c>
       <c r="C374">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="D374" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F374" t="s">
         <v>31</v>
       </c>
       <c r="G374" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H374" s="2">
-        <v>0</v>
+        <v>3.5752314814814813E-2</v>
       </c>
       <c r="I374" s="1">
-        <v>46237.800694444442</v>
+        <v>46237.801388888889</v>
       </c>
       <c r="J374" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K374" s="1" t="s">
         <v>11</v>
@@ -10783,25 +10765,25 @@
         <v>41</v>
       </c>
       <c r="C375">
-        <v>1815</v>
+        <v>4827</v>
       </c>
       <c r="D375" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="F375" t="s">
         <v>31</v>
       </c>
       <c r="G375" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H375" s="2">
-        <v>0</v>
+        <v>6.5046296296296293E-3</v>
       </c>
       <c r="I375" s="1">
-        <v>46237.801388888889</v>
+        <v>46237.802083333336</v>
       </c>
       <c r="J375" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K375" s="1" t="s">
         <v>11</v>
@@ -10812,16 +10794,16 @@
         <v>41</v>
       </c>
       <c r="C376">
-        <v>4827</v>
+        <v>1813</v>
       </c>
       <c r="D376" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F376" t="s">
         <v>31</v>
       </c>
       <c r="G376" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H376" s="2">
         <v>0</v>
@@ -10830,18 +10812,39 @@
         <v>46237.802083333336</v>
       </c>
       <c r="J376" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K376" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="377" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H377" s="2"/>
-      <c r="I377" s="1"/>
-      <c r="J377" s="2"/>
+      <c r="B377" t="s">
+        <v>41</v>
+      </c>
+      <c r="C377">
+        <v>1812</v>
+      </c>
+      <c r="D377" t="s">
+        <v>47</v>
+      </c>
+      <c r="F377" t="s">
+        <v>31</v>
+      </c>
+      <c r="G377" t="s">
+        <v>10</v>
+      </c>
+      <c r="H377" s="2">
+        <v>1.0034722222222223E-2</v>
+      </c>
+      <c r="I377" s="1">
+        <v>46237.802777777775</v>
+      </c>
+      <c r="J377" s="2">
+        <v>1</v>
+      </c>
       <c r="K377" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="378" spans="2:11" x14ac:dyDescent="0.25">
@@ -10849,22 +10852,22 @@
         <v>41</v>
       </c>
       <c r="C378">
-        <v>1813</v>
+        <v>4828</v>
       </c>
       <c r="D378" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F378" t="s">
         <v>31</v>
       </c>
       <c r="G378" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H378" s="2">
-        <v>0</v>
+        <v>8.7962962962962968E-3</v>
       </c>
       <c r="I378" s="1">
-        <v>46237.802083333336</v>
+        <v>46237.804166666669</v>
       </c>
       <c r="J378" s="2">
         <v>0</v>
@@ -10878,22 +10881,22 @@
         <v>41</v>
       </c>
       <c r="C379">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="D379" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F379" t="s">
         <v>31</v>
       </c>
       <c r="G379" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H379" s="2">
-        <v>0</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I379" s="1">
-        <v>46237.802777777775</v>
+        <v>46237.806250000001</v>
       </c>
       <c r="J379" s="2">
         <v>0</v>
@@ -10907,10 +10910,10 @@
         <v>41</v>
       </c>
       <c r="C380">
-        <v>6057</v>
+        <v>5882</v>
       </c>
       <c r="D380" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
         <v>31</v>
@@ -10919,13 +10922,13 @@
         <v>10</v>
       </c>
       <c r="H380" s="2">
-        <v>8.9930555555555562E-3</v>
+        <v>6.3541666666666668E-3</v>
       </c>
       <c r="I380" s="1">
-        <v>46237.803472222222</v>
+        <v>46237.806944444441</v>
       </c>
       <c r="J380" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K380" s="1" t="s">
         <v>11</v>
@@ -10936,10 +10939,10 @@
         <v>41</v>
       </c>
       <c r="C381">
-        <v>6058</v>
+        <v>1809</v>
       </c>
       <c r="D381" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F381" t="s">
         <v>31</v>
@@ -10951,24 +10954,24 @@
         <v>0</v>
       </c>
       <c r="I381" s="1">
-        <v>46237.803472222222</v>
+        <v>46237.807638888888</v>
       </c>
       <c r="J381" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K381" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>41</v>
       </c>
       <c r="C382">
-        <v>4828</v>
+        <v>1817</v>
       </c>
       <c r="D382" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F382" t="s">
         <v>31</v>
@@ -10977,284 +10980,121 @@
         <v>10</v>
       </c>
       <c r="H382" s="2">
-        <v>8.7962962962962968E-3</v>
+        <v>6.3194444444444444E-3</v>
       </c>
       <c r="I382" s="1">
-        <v>46237.804166666669</v>
+        <v>46237.808333333334</v>
       </c>
       <c r="J382" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K382" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="383" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B383" t="s">
-        <v>41</v>
-      </c>
-      <c r="C383">
-        <v>6054</v>
-      </c>
-      <c r="D383" t="s">
-        <v>69</v>
-      </c>
-      <c r="F383" t="s">
-        <v>31</v>
-      </c>
-      <c r="G383" t="s">
-        <v>14</v>
-      </c>
-      <c r="H383" s="2">
-        <v>0</v>
-      </c>
-      <c r="I383" s="1">
-        <v>46237.804861111108</v>
-      </c>
-      <c r="J383" s="2">
-        <v>0</v>
-      </c>
-      <c r="K383" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H383" s="2"/>
+      <c r="I383" s="1"/>
+      <c r="J383" s="2"/>
+      <c r="K383" s="1"/>
     </row>
     <row r="384" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H384" s="2"/>
       <c r="I384" s="1"/>
       <c r="J384" s="2"/>
-      <c r="K384" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="385" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B385" t="s">
-        <v>41</v>
-      </c>
-      <c r="C385">
-        <v>6048</v>
-      </c>
-      <c r="D385" t="s">
-        <v>70</v>
-      </c>
-      <c r="F385" t="s">
-        <v>31</v>
-      </c>
-      <c r="G385" t="s">
-        <v>10</v>
-      </c>
-      <c r="H385" s="2">
-        <v>6.2152777777777779E-3</v>
-      </c>
-      <c r="I385" s="1">
-        <v>46237.805555555555</v>
-      </c>
-      <c r="J385" s="2">
-        <v>0</v>
-      </c>
-      <c r="K385" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="386" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B386" t="s">
-        <v>41</v>
-      </c>
-      <c r="C386">
-        <v>1816</v>
-      </c>
-      <c r="D386" t="s">
-        <v>49</v>
-      </c>
-      <c r="F386" t="s">
-        <v>31</v>
-      </c>
-      <c r="G386" t="s">
-        <v>10</v>
-      </c>
-      <c r="H386" s="2">
-        <v>7.0254629629629634E-3</v>
-      </c>
-      <c r="I386" s="1">
-        <v>46237.806250000001</v>
-      </c>
-      <c r="J386" s="2">
-        <v>0</v>
-      </c>
-      <c r="K386" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="387" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B387" t="s">
-        <v>41</v>
-      </c>
-      <c r="C387">
-        <v>5882</v>
-      </c>
-      <c r="D387" t="s">
-        <v>64</v>
-      </c>
-      <c r="F387" t="s">
-        <v>31</v>
-      </c>
-      <c r="G387" t="s">
-        <v>13</v>
-      </c>
-      <c r="H387" s="2">
-        <v>0</v>
-      </c>
-      <c r="I387" s="1">
-        <v>46237.806944444441</v>
-      </c>
-      <c r="J387" s="2">
-        <v>0</v>
-      </c>
-      <c r="K387" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="388" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B388" t="s">
-        <v>41</v>
-      </c>
-      <c r="C388">
-        <v>6052</v>
-      </c>
-      <c r="D388" t="s">
-        <v>71</v>
-      </c>
-      <c r="F388" t="s">
-        <v>31</v>
-      </c>
-      <c r="G388" t="s">
-        <v>13</v>
-      </c>
-      <c r="H388" s="2">
-        <v>0</v>
-      </c>
-      <c r="I388" s="1">
-        <v>46237.806944444441</v>
-      </c>
-      <c r="J388" s="2">
-        <v>0</v>
-      </c>
-      <c r="K388" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="389" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B389" t="s">
-        <v>41</v>
-      </c>
-      <c r="C389">
-        <v>1809</v>
-      </c>
-      <c r="D389" t="s">
-        <v>53</v>
-      </c>
-      <c r="F389" t="s">
-        <v>31</v>
-      </c>
-      <c r="G389" t="s">
-        <v>13</v>
-      </c>
-      <c r="H389" s="2">
-        <v>0</v>
-      </c>
-      <c r="I389" s="1">
-        <v>46237.807638888888</v>
-      </c>
-      <c r="J389" s="2">
-        <v>0</v>
-      </c>
-      <c r="K389" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="390" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B390" t="s">
-        <v>41</v>
-      </c>
-      <c r="C390">
-        <v>1817</v>
-      </c>
-      <c r="D390" t="s">
-        <v>54</v>
-      </c>
-      <c r="F390" t="s">
-        <v>31</v>
-      </c>
-      <c r="G390" t="s">
-        <v>13</v>
-      </c>
-      <c r="H390" s="2">
-        <v>0</v>
-      </c>
-      <c r="I390" s="1">
-        <v>46237.808333333334</v>
-      </c>
-      <c r="J390" s="2">
-        <v>0</v>
-      </c>
-      <c r="K390" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="391" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K384" s="1"/>
+    </row>
+    <row r="385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H385" s="2"/>
+      <c r="I385" s="1"/>
+      <c r="J385" s="2"/>
+      <c r="K385" s="1"/>
+    </row>
+    <row r="386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H386" s="2"/>
+      <c r="I386" s="1"/>
+      <c r="J386" s="2"/>
+      <c r="K386" s="1"/>
+    </row>
+    <row r="387" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H387" s="2"/>
+      <c r="I387" s="1"/>
+      <c r="J387" s="2"/>
+      <c r="K387" s="1"/>
+    </row>
+    <row r="388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H388" s="2"/>
+      <c r="I388" s="1"/>
+      <c r="J388" s="2"/>
+      <c r="K388" s="1"/>
+    </row>
+    <row r="389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H389" s="2"/>
+      <c r="I389" s="1"/>
+      <c r="J389" s="2"/>
+      <c r="K389" s="1"/>
+    </row>
+    <row r="390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H390" s="2"/>
+      <c r="I390" s="1"/>
+      <c r="J390" s="2"/>
+      <c r="K390" s="1"/>
+    </row>
+    <row r="391" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H391" s="2"/>
       <c r="I391" s="1"/>
       <c r="J391" s="2"/>
       <c r="K391" s="1"/>
     </row>
-    <row r="392" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H392" s="2"/>
       <c r="I392" s="1"/>
       <c r="J392" s="2"/>
       <c r="K392" s="1"/>
     </row>
-    <row r="393" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H393" s="2"/>
       <c r="I393" s="1"/>
       <c r="J393" s="2"/>
       <c r="K393" s="1"/>
     </row>
-    <row r="394" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H394" s="2"/>
       <c r="I394" s="1"/>
       <c r="J394" s="2"/>
       <c r="K394" s="1"/>
     </row>
-    <row r="395" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H395" s="2"/>
       <c r="I395" s="1"/>
       <c r="J395" s="2"/>
       <c r="K395" s="1"/>
     </row>
-    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H396" s="2"/>
       <c r="I396" s="1"/>
       <c r="J396" s="2"/>
       <c r="K396" s="1"/>
     </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H397" s="2"/>
       <c r="I397" s="1"/>
       <c r="J397" s="2"/>
       <c r="K397" s="1"/>
     </row>
-    <row r="398" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H398" s="2"/>
       <c r="I398" s="1"/>
       <c r="J398" s="2"/>
       <c r="K398" s="1"/>
     </row>
-    <row r="399" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H399" s="2"/>
       <c r="I399" s="1"/>
       <c r="J399" s="2"/>
       <c r="K399" s="1"/>
     </row>
-    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H400" s="2"/>
       <c r="I400" s="1"/>
       <c r="J400" s="2"/>
@@ -50099,6 +49939,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -50391,6 +50232,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -50701,6 +50544,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -50825,6 +50669,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -50836,6 +50681,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -50984,6 +50830,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -50994,10 +50841,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -51031,15 +50880,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -51080,18 +50932,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -51107,6 +50963,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -51116,10 +50973,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -51155,10 +51014,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -51184,6 +51045,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -51198,6 +51060,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -51232,6 +51095,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -51241,6 +51105,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -51250,6 +51115,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -51264,15 +51130,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -51302,6 +51169,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -51322,11 +51190,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -51335,6 +51205,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -51364,6 +51235,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -51373,10 +51245,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -51391,14 +51265,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -51418,10 +51295,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -51441,9 +51320,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -51478,18 +51360,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -51504,12 +51390,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -51524,10 +51410,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -51547,6 +51435,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -51566,6 +51455,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -51575,6 +51465,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -51620,6 +51511,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -51629,6 +51521,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -51643,6 +51536,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -51652,10 +51546,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -51670,6 +51566,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -51679,6 +51576,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -51698,6 +51596,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -51717,10 +51616,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -51730,6 +51631,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -51740,10 +51642,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -51758,18 +51662,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -51789,10 +51697,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -51812,6 +51722,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -51842,7 +51753,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -51857,10 +51767,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -51875,6 +51787,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -51889,11 +51802,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -51903,6 +51816,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -51918,6 +51832,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -51932,6 +51847,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -51952,6 +51868,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -51977,11 +51894,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -52000,15 +51919,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -52018,6 +51938,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -52037,6 +51958,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -52051,6 +51973,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -52070,10 +51993,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -52083,6 +52008,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -52093,6 +52019,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -52129,7 +52056,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -52138,6 +52064,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -52151,10 +52078,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08E04093-3E5D-4885-B3A9-F2A920B991FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF4DBEC5-8D3B-4714-8112-299C14F40A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -149,19 +149,19 @@
     <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
-    <t>DNU-Speed Management</t>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>DNU-Def.Drive Distracted Driving</t>
   </si>
   <si>
-    <t>Hazcom for CDL Drivers</t>
-  </si>
-  <si>
-    <t>3 points of contact</t>
+    <t>DNU-Speed Management</t>
   </si>
   <si>
     <t>DNUNEW-Space Management Big 5</t>
+  </si>
+  <si>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Home Motors</t>
@@ -610,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -839,7 +839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>41</v>
       </c>
@@ -955,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>41</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1127,7 +1127,7 @@
         <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1156,7 +1156,7 @@
         <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -1193,7 +1193,7 @@
         <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
@@ -1222,7 +1222,7 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
@@ -1251,7 +1251,7 @@
         <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -1269,7 +1269,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1288,7 +1288,7 @@
         <v>47</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>48</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G28" t="s">
         <v>10</v>
@@ -1346,7 +1346,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
         <v>10</v>
@@ -1375,7 +1375,7 @@
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -1401,7 +1401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>41</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1441,7 +1441,7 @@
         <v>53</v>
       </c>
       <c r="F33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -1478,7 +1478,7 @@
         <v>53</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
         <v>12</v>
@@ -1515,7 +1515,7 @@
         <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
@@ -1552,7 +1552,7 @@
         <v>42</v>
       </c>
       <c r="F39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
@@ -1581,7 +1581,7 @@
         <v>43</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
@@ -1610,7 +1610,7 @@
         <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
@@ -1628,7 +1628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>41</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>44</v>
       </c>
       <c r="F42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -1676,7 +1676,7 @@
         <v>45</v>
       </c>
       <c r="F44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -1705,7 +1705,7 @@
         <v>46</v>
       </c>
       <c r="F45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G45" t="s">
         <v>13</v>
@@ -1734,7 +1734,7 @@
         <v>47</v>
       </c>
       <c r="F46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
@@ -1763,7 +1763,7 @@
         <v>48</v>
       </c>
       <c r="F47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G47" t="s">
         <v>10</v>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G48" t="s">
         <v>10</v>
@@ -1821,7 +1821,7 @@
         <v>51</v>
       </c>
       <c r="F49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G49" t="s">
         <v>13</v>
@@ -1850,7 +1850,7 @@
         <v>52</v>
       </c>
       <c r="F50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G50" t="s">
         <v>13</v>
@@ -1879,7 +1879,7 @@
         <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -1908,7 +1908,7 @@
         <v>54</v>
       </c>
       <c r="F52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -1934,7 +1934,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>41</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>41</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>41</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>41</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>41</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>41</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -5246,7 +5246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>41</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>41</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>42</v>
       </c>
       <c r="F184" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G184" t="s">
         <v>10</v>
@@ -5576,7 +5576,7 @@
         <v>43</v>
       </c>
       <c r="F185" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G185" t="s">
         <v>13</v>
@@ -5605,7 +5605,7 @@
         <v>44</v>
       </c>
       <c r="F186" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G186" t="s">
         <v>10</v>
@@ -5634,7 +5634,7 @@
         <v>45</v>
       </c>
       <c r="F187" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G187" t="s">
         <v>10</v>
@@ -5663,7 +5663,7 @@
         <v>46</v>
       </c>
       <c r="F188" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G188" t="s">
         <v>10</v>
@@ -5681,7 +5681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>41</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>47</v>
       </c>
       <c r="F189" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G189" t="s">
         <v>10</v>
@@ -5721,7 +5721,7 @@
         <v>57</v>
       </c>
       <c r="F190" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G190" t="s">
         <v>10</v>
@@ -5750,7 +5750,7 @@
         <v>49</v>
       </c>
       <c r="F191" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G191" t="s">
         <v>10</v>
@@ -5779,7 +5779,7 @@
         <v>58</v>
       </c>
       <c r="F192" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G192" t="s">
         <v>10</v>
@@ -5808,7 +5808,7 @@
         <v>52</v>
       </c>
       <c r="F193" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G193" t="s">
         <v>13</v>
@@ -5837,7 +5837,7 @@
         <v>53</v>
       </c>
       <c r="F194" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G194" t="s">
         <v>10</v>
@@ -5866,7 +5866,7 @@
         <v>54</v>
       </c>
       <c r="F195" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G195" t="s">
         <v>10</v>
@@ -6203,7 +6203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>41</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>42</v>
       </c>
       <c r="F235" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G235" t="s">
         <v>10</v>
@@ -7034,7 +7034,7 @@
         <v>43</v>
       </c>
       <c r="F236" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G236" t="s">
         <v>13</v>
@@ -7063,7 +7063,7 @@
         <v>44</v>
       </c>
       <c r="F237" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G237" t="s">
         <v>10</v>
@@ -7092,7 +7092,7 @@
         <v>45</v>
       </c>
       <c r="F238" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G238" t="s">
         <v>10</v>
@@ -7110,7 +7110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>41</v>
       </c>
@@ -7121,7 +7121,7 @@
         <v>61</v>
       </c>
       <c r="F239" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G239" t="s">
         <v>10</v>
@@ -7150,7 +7150,7 @@
         <v>60</v>
       </c>
       <c r="F240" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G240" t="s">
         <v>13</v>
@@ -7179,7 +7179,7 @@
         <v>46</v>
       </c>
       <c r="F241" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G241" t="s">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>47</v>
       </c>
       <c r="F242" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G242" t="s">
         <v>10</v>
@@ -7237,7 +7237,7 @@
         <v>62</v>
       </c>
       <c r="F243" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G243" t="s">
         <v>10</v>
@@ -7266,7 +7266,7 @@
         <v>57</v>
       </c>
       <c r="F244" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G244" t="s">
         <v>10</v>
@@ -7295,7 +7295,7 @@
         <v>49</v>
       </c>
       <c r="F245" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G245" t="s">
         <v>10</v>
@@ -7324,7 +7324,7 @@
         <v>52</v>
       </c>
       <c r="F246" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G246" t="s">
         <v>13</v>
@@ -7353,7 +7353,7 @@
         <v>53</v>
       </c>
       <c r="F247" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G247" t="s">
         <v>12</v>
@@ -7390,7 +7390,7 @@
         <v>54</v>
       </c>
       <c r="F249" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G249" t="s">
         <v>10</v>
@@ -9373,7 +9373,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>41</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>41</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>41</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>41</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>41</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>41</v>
       </c>
@@ -10716,10 +10716,10 @@
         <v>31</v>
       </c>
       <c r="G373" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H373" s="2">
-        <v>0</v>
+        <v>5.7175925925925927E-3</v>
       </c>
       <c r="I373" s="1">
         <v>46237.800694444442</v>
@@ -10963,7 +10963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>41</v>
       </c>
@@ -49939,7 +49939,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -50232,8 +50231,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -50544,7 +50541,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -50669,7 +50665,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -50681,7 +50676,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -50830,35 +50824,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -50869,44 +50857,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -50917,37 +50896,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -50958,52 +50930,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -51014,17 +50976,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -51035,32 +50994,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -51070,106 +51023,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -51179,7 +51112,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -51190,127 +51122,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -51320,62 +51226,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -51395,67 +51288,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -51465,38 +51345,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -51511,117 +51384,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -51630,99 +51480,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -51732,23 +51563,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -51757,52 +51584,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -51816,38 +51633,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -51857,7 +51667,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -51868,23 +51677,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -51894,37 +51699,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -51933,72 +51731,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -52008,76 +51792,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF4DBEC5-8D3B-4714-8112-299C14F40A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DE854C2-BBDA-4284-92A9-643CFE0FA679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -149,19 +149,19 @@
     <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
-    <t>3 points of contact</t>
+    <t>DNU-Speed Management</t>
   </si>
   <si>
     <t>DNU-Def.Drive Distracted Driving</t>
   </si>
   <si>
-    <t>DNU-Speed Management</t>
+    <t>Hazcom for CDL Drivers</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>DNUNEW-Space Management Big 5</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Home Motors</t>
@@ -610,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1098,7 +1098,7 @@
         <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1127,7 +1127,7 @@
         <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1156,7 +1156,7 @@
         <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -1193,7 +1193,7 @@
         <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
@@ -1222,7 +1222,7 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
@@ -1251,7 +1251,7 @@
         <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -1288,7 +1288,7 @@
         <v>47</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>48</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G28" t="s">
         <v>10</v>
@@ -1346,7 +1346,7 @@
         <v>49</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G29" t="s">
         <v>10</v>
@@ -1375,7 +1375,7 @@
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -1412,7 +1412,7 @@
         <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1441,7 +1441,7 @@
         <v>53</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -1478,7 +1478,7 @@
         <v>53</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G35" t="s">
         <v>12</v>
@@ -1515,7 +1515,7 @@
         <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
@@ -1552,7 +1552,7 @@
         <v>42</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
@@ -1581,7 +1581,7 @@
         <v>43</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
@@ -1610,7 +1610,7 @@
         <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
@@ -1639,7 +1639,7 @@
         <v>44</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -1676,7 +1676,7 @@
         <v>45</v>
       </c>
       <c r="F44" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -1705,7 +1705,7 @@
         <v>46</v>
       </c>
       <c r="F45" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G45" t="s">
         <v>13</v>
@@ -1734,7 +1734,7 @@
         <v>47</v>
       </c>
       <c r="F46" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
@@ -1763,7 +1763,7 @@
         <v>48</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G47" t="s">
         <v>10</v>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="F48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G48" t="s">
         <v>10</v>
@@ -1821,7 +1821,7 @@
         <v>51</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G49" t="s">
         <v>13</v>
@@ -1850,7 +1850,7 @@
         <v>52</v>
       </c>
       <c r="F50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G50" t="s">
         <v>13</v>
@@ -1879,7 +1879,7 @@
         <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -1908,7 +1908,7 @@
         <v>54</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -5547,7 +5547,7 @@
         <v>42</v>
       </c>
       <c r="F184" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G184" t="s">
         <v>10</v>
@@ -5576,7 +5576,7 @@
         <v>43</v>
       </c>
       <c r="F185" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G185" t="s">
         <v>13</v>
@@ -5605,7 +5605,7 @@
         <v>44</v>
       </c>
       <c r="F186" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G186" t="s">
         <v>10</v>
@@ -5634,7 +5634,7 @@
         <v>45</v>
       </c>
       <c r="F187" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G187" t="s">
         <v>10</v>
@@ -5663,7 +5663,7 @@
         <v>46</v>
       </c>
       <c r="F188" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G188" t="s">
         <v>10</v>
@@ -5692,7 +5692,7 @@
         <v>47</v>
       </c>
       <c r="F189" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G189" t="s">
         <v>10</v>
@@ -5721,7 +5721,7 @@
         <v>57</v>
       </c>
       <c r="F190" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G190" t="s">
         <v>10</v>
@@ -5750,7 +5750,7 @@
         <v>49</v>
       </c>
       <c r="F191" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G191" t="s">
         <v>10</v>
@@ -5779,7 +5779,7 @@
         <v>58</v>
       </c>
       <c r="F192" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G192" t="s">
         <v>10</v>
@@ -5808,7 +5808,7 @@
         <v>52</v>
       </c>
       <c r="F193" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G193" t="s">
         <v>13</v>
@@ -5837,7 +5837,7 @@
         <v>53</v>
       </c>
       <c r="F194" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G194" t="s">
         <v>10</v>
@@ -5866,7 +5866,7 @@
         <v>54</v>
       </c>
       <c r="F195" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G195" t="s">
         <v>10</v>
@@ -7005,7 +7005,7 @@
         <v>42</v>
       </c>
       <c r="F235" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G235" t="s">
         <v>10</v>
@@ -7034,7 +7034,7 @@
         <v>43</v>
       </c>
       <c r="F236" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G236" t="s">
         <v>13</v>
@@ -7063,7 +7063,7 @@
         <v>44</v>
       </c>
       <c r="F237" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G237" t="s">
         <v>10</v>
@@ -7092,7 +7092,7 @@
         <v>45</v>
       </c>
       <c r="F238" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G238" t="s">
         <v>10</v>
@@ -7121,7 +7121,7 @@
         <v>61</v>
       </c>
       <c r="F239" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G239" t="s">
         <v>10</v>
@@ -7150,7 +7150,7 @@
         <v>60</v>
       </c>
       <c r="F240" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G240" t="s">
         <v>13</v>
@@ -7179,7 +7179,7 @@
         <v>46</v>
       </c>
       <c r="F241" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G241" t="s">
         <v>10</v>
@@ -7208,7 +7208,7 @@
         <v>47</v>
       </c>
       <c r="F242" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G242" t="s">
         <v>10</v>
@@ -7237,7 +7237,7 @@
         <v>62</v>
       </c>
       <c r="F243" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G243" t="s">
         <v>10</v>
@@ -7266,7 +7266,7 @@
         <v>57</v>
       </c>
       <c r="F244" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G244" t="s">
         <v>10</v>
@@ -7295,7 +7295,7 @@
         <v>49</v>
       </c>
       <c r="F245" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G245" t="s">
         <v>10</v>
@@ -7324,7 +7324,7 @@
         <v>52</v>
       </c>
       <c r="F246" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G246" t="s">
         <v>13</v>
@@ -7353,7 +7353,7 @@
         <v>53</v>
       </c>
       <c r="F247" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G247" t="s">
         <v>12</v>
@@ -7390,7 +7390,7 @@
         <v>54</v>
       </c>
       <c r="F249" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G249" t="s">
         <v>10</v>
@@ -10803,10 +10803,10 @@
         <v>31</v>
       </c>
       <c r="G376" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H376" s="2">
-        <v>0</v>
+        <v>8.518518518518519E-3</v>
       </c>
       <c r="I376" s="1">
         <v>46237.802083333336</v>
@@ -49939,6 +49939,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -50231,6 +50232,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -50541,6 +50544,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -50665,6 +50669,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -50676,6 +50681,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -50824,29 +50830,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -50857,35 +50869,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -50896,30 +50917,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -50930,42 +50958,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -50976,14 +51014,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -50994,26 +51035,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -51023,86 +51070,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -51112,6 +51180,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -51122,101 +51191,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -51226,49 +51321,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -51283,59 +51391,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -51345,31 +51467,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -51379,99 +51508,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -51480,80 +51633,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -51563,67 +51735,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -51633,31 +51821,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -51667,6 +51862,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -51677,19 +51873,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -51699,90 +51899,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -51792,51 +52014,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
